--- a/docs/reference/kontenplan-korigiran.xlsx
+++ b/docs/reference/kontenplan-korigiran.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Контен план" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Контен план'!$A$1:$F$1884</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Контен план'!$A$1:$F$2287</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1884"/>
+  <dimension ref="A1:F2287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -40205,8 +40205,8064 @@
       <c r="E1884" s="13" t="inlineStr"/>
       <c r="F1884" s="13" t="inlineStr"/>
     </row>
+    <row r="1885">
+      <c r="A1885" s="11" t="inlineStr">
+        <is>
+          <t>7441</t>
+        </is>
+      </c>
+      <c r="B1885" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од продажба на недвижности, постројки и опрема кои се чуваат за продажба</t>
+        </is>
+      </c>
+      <c r="C1885" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1885" s="13" t="inlineStr"/>
+      <c r="E1885" s="13" t="inlineStr"/>
+      <c r="F1885" s="13" t="inlineStr"/>
+    </row>
+    <row r="1886">
+      <c r="A1886" s="11" t="inlineStr">
+        <is>
+          <t>7442</t>
+        </is>
+      </c>
+      <c r="B1886" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од продажба на алат, погонски инвентар и транспортни средства кои се чуваат за продажба</t>
+        </is>
+      </c>
+      <c r="C1886" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1886" s="13" t="inlineStr"/>
+      <c r="E1886" s="13" t="inlineStr"/>
+      <c r="F1886" s="13" t="inlineStr"/>
+    </row>
+    <row r="1887">
+      <c r="A1887" s="11" t="inlineStr">
+        <is>
+          <t>7443</t>
+        </is>
+      </c>
+      <c r="B1887" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од продажба на биолошки средства кои се чуваат за продажба</t>
+        </is>
+      </c>
+      <c r="C1887" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1887" s="13" t="inlineStr"/>
+      <c r="E1887" s="13" t="inlineStr"/>
+      <c r="F1887" s="13" t="inlineStr"/>
+    </row>
+    <row r="1888">
+      <c r="A1888" s="11" t="inlineStr">
+        <is>
+          <t>7444</t>
+        </is>
+      </c>
+      <c r="B1888" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од продажба на останати нетековни средства кои се чуваат за продажба</t>
+        </is>
+      </c>
+      <c r="C1888" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1888" s="13" t="inlineStr"/>
+      <c r="E1888" s="13" t="inlineStr"/>
+      <c r="F1888" s="13" t="inlineStr"/>
+    </row>
+    <row r="1889">
+      <c r="A1889" s="11" t="inlineStr">
+        <is>
+          <t>7449</t>
+        </is>
+      </c>
+      <c r="B1889" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од продажба на средства од прекинато работење</t>
+        </is>
+      </c>
+      <c r="C1889" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1889" s="13" t="inlineStr"/>
+      <c r="E1889" s="13" t="inlineStr"/>
+      <c r="F1889" s="13" t="inlineStr"/>
+    </row>
+    <row r="1890">
+      <c r="A1890" s="8" t="inlineStr">
+        <is>
+          <t>745</t>
+        </is>
+      </c>
+      <c r="B1890" s="9" t="inlineStr">
+        <is>
+          <t>Приходи врз основа на употреба на сопствени добра (производи, стоки) и услуги</t>
+        </is>
+      </c>
+      <c r="C1890" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D1890" s="10" t="inlineStr"/>
+      <c r="E1890" s="10" t="inlineStr"/>
+      <c r="F1890" s="10" t="inlineStr"/>
+    </row>
+    <row r="1891">
+      <c r="A1891" s="11" t="inlineStr">
+        <is>
+          <t>7450</t>
+        </is>
+      </c>
+      <c r="B1891" s="12" t="inlineStr">
+        <is>
+          <t>Приходи врз основа на употреба на сопствени материјали и други добра за изработка на материјални средства за сопствени потреби (објекти, алат, опрема и сл.)</t>
+        </is>
+      </c>
+      <c r="C1891" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1891" s="13" t="inlineStr"/>
+      <c r="E1891" s="13" t="inlineStr"/>
+      <c r="F1891" s="13" t="inlineStr"/>
+    </row>
+    <row r="1892">
+      <c r="A1892" s="11" t="inlineStr">
+        <is>
+          <t>7451</t>
+        </is>
+      </c>
+      <c r="B1892" s="12" t="inlineStr">
+        <is>
+          <t>Приходи врз основа на сопствени стоки за користење на сопствени потреби</t>
+        </is>
+      </c>
+      <c r="C1892" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1892" s="13" t="inlineStr"/>
+      <c r="E1892" s="13" t="inlineStr"/>
+      <c r="F1892" s="13" t="inlineStr"/>
+    </row>
+    <row r="1893">
+      <c r="A1893" s="11" t="inlineStr">
+        <is>
+          <t>7455</t>
+        </is>
+      </c>
+      <c r="B1893" s="12" t="inlineStr">
+        <is>
+          <t>Приходи врз основа на производи и услуги за прираст на основно стадо</t>
+        </is>
+      </c>
+      <c r="C1893" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1893" s="13" t="inlineStr"/>
+      <c r="E1893" s="13" t="inlineStr"/>
+      <c r="F1893" s="13" t="inlineStr"/>
+    </row>
+    <row r="1894">
+      <c r="A1894" s="8" t="inlineStr">
+        <is>
+          <t>746</t>
+        </is>
+      </c>
+      <c r="B1894" s="9" t="inlineStr">
+        <is>
+          <t>Приходи од специфично работење на неповрзани друштва</t>
+        </is>
+      </c>
+      <c r="C1894" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D1894" s="10" t="inlineStr"/>
+      <c r="E1894" s="10" t="inlineStr"/>
+      <c r="F1894" s="10" t="inlineStr"/>
+    </row>
+    <row r="1895">
+      <c r="A1895" s="11" t="inlineStr">
+        <is>
+          <t>7460</t>
+        </is>
+      </c>
+      <c r="B1895" s="12" t="inlineStr">
+        <is>
+          <t>Приходи врз основа на побарувања од извозници</t>
+        </is>
+      </c>
+      <c r="C1895" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1895" s="13" t="inlineStr"/>
+      <c r="E1895" s="13" t="inlineStr"/>
+      <c r="F1895" s="13" t="inlineStr"/>
+    </row>
+    <row r="1896">
+      <c r="A1896" s="11" t="inlineStr">
+        <is>
+          <t>7461</t>
+        </is>
+      </c>
+      <c r="B1896" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од продажба на добра врз основа на увоз за туѓа сметка</t>
+        </is>
+      </c>
+      <c r="C1896" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1896" s="13" t="inlineStr"/>
+      <c r="E1896" s="13" t="inlineStr"/>
+      <c r="F1896" s="13" t="inlineStr"/>
+    </row>
+    <row r="1897">
+      <c r="A1897" s="11" t="inlineStr">
+        <is>
+          <t>7462</t>
+        </is>
+      </c>
+      <c r="B1897" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од продажба на добра во комисиона и консигнациона продажба</t>
+        </is>
+      </c>
+      <c r="C1897" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1897" s="13" t="inlineStr"/>
+      <c r="E1897" s="13" t="inlineStr"/>
+      <c r="F1897" s="13" t="inlineStr"/>
+    </row>
+    <row r="1898">
+      <c r="A1898" s="11" t="inlineStr">
+        <is>
+          <t>74620</t>
+        </is>
+      </c>
+      <c r="B1898" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од продажба на производи, стоки и услуги во комисион и консигнација оданочиви по општа даночна стапка</t>
+        </is>
+      </c>
+      <c r="C1898" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1898" s="13" t="inlineStr"/>
+      <c r="E1898" s="13" t="inlineStr"/>
+      <c r="F1898" s="13" t="inlineStr"/>
+    </row>
+    <row r="1899">
+      <c r="A1899" s="11" t="inlineStr">
+        <is>
+          <t>74621</t>
+        </is>
+      </c>
+      <c r="B1899" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од продажба на производи, стоки и услуги во комисион и консигнација оданочиви по повластена даночна стапка</t>
+        </is>
+      </c>
+      <c r="C1899" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1899" s="13" t="inlineStr"/>
+      <c r="E1899" s="13" t="inlineStr"/>
+      <c r="F1899" s="13" t="inlineStr"/>
+    </row>
+    <row r="1900">
+      <c r="A1900" s="11" t="inlineStr">
+        <is>
+          <t>74622</t>
+        </is>
+      </c>
+      <c r="B1900" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од продажба на производи, стоки и услуги во комисион и консигнација ослободени од данок со право на одбивка на предходен данок</t>
+        </is>
+      </c>
+      <c r="C1900" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1900" s="13" t="inlineStr"/>
+      <c r="E1900" s="13" t="inlineStr"/>
+      <c r="F1900" s="13" t="inlineStr"/>
+    </row>
+    <row r="1901">
+      <c r="A1901" s="11" t="inlineStr">
+        <is>
+          <t>74623</t>
+        </is>
+      </c>
+      <c r="B1901" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од продажба на производи, стоки и услуги во комисион и консигнација ослободени од данок без право на одбивка на предходен данок</t>
+        </is>
+      </c>
+      <c r="C1901" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1901" s="13" t="inlineStr"/>
+      <c r="E1901" s="13" t="inlineStr"/>
+      <c r="F1901" s="13" t="inlineStr"/>
+    </row>
+    <row r="1902">
+      <c r="A1902" s="8" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
+      <c r="B1902" s="9" t="inlineStr">
+        <is>
+          <t>Приходи од наемнини</t>
+        </is>
+      </c>
+      <c r="C1902" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D1902" s="10" t="inlineStr"/>
+      <c r="E1902" s="10" t="inlineStr"/>
+      <c r="F1902" s="10" t="inlineStr"/>
+    </row>
+    <row r="1903">
+      <c r="A1903" s="11" t="inlineStr">
+        <is>
+          <t>7470</t>
+        </is>
+      </c>
+      <c r="B1903" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од наемнина на недвижности</t>
+        </is>
+      </c>
+      <c r="C1903" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1903" s="13" t="inlineStr"/>
+      <c r="E1903" s="13" t="inlineStr"/>
+      <c r="F1903" s="13" t="inlineStr"/>
+    </row>
+    <row r="1904">
+      <c r="A1904" s="11" t="inlineStr">
+        <is>
+          <t>7471</t>
+        </is>
+      </c>
+      <c r="B1904" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од наемнина на постројки и опрема</t>
+        </is>
+      </c>
+      <c r="C1904" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1904" s="13" t="inlineStr"/>
+      <c r="E1904" s="13" t="inlineStr"/>
+      <c r="F1904" s="13" t="inlineStr"/>
+    </row>
+    <row r="1905">
+      <c r="A1905" s="11" t="inlineStr">
+        <is>
+          <t>7472</t>
+        </is>
+      </c>
+      <c r="B1905" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од наемнина на транспортни средства</t>
+        </is>
+      </c>
+      <c r="C1905" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1905" s="13" t="inlineStr"/>
+      <c r="E1905" s="13" t="inlineStr"/>
+      <c r="F1905" s="13" t="inlineStr"/>
+    </row>
+    <row r="1906">
+      <c r="A1906" s="11" t="inlineStr">
+        <is>
+          <t>7473</t>
+        </is>
+      </c>
+      <c r="B1906" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од рент-а кар</t>
+        </is>
+      </c>
+      <c r="C1906" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1906" s="13" t="inlineStr"/>
+      <c r="E1906" s="13" t="inlineStr"/>
+      <c r="F1906" s="13" t="inlineStr"/>
+    </row>
+    <row r="1907">
+      <c r="A1907" s="11" t="inlineStr">
+        <is>
+          <t>7479</t>
+        </is>
+      </c>
+      <c r="B1907" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од наемнина врз друга основа</t>
+        </is>
+      </c>
+      <c r="C1907" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1907" s="13" t="inlineStr"/>
+      <c r="E1907" s="13" t="inlineStr"/>
+      <c r="F1907" s="13" t="inlineStr"/>
+    </row>
+    <row r="1908">
+      <c r="A1908" s="8" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="B1908" s="9" t="inlineStr">
+        <is>
+          <t>Приходи од продажба на добра врз основа на финансиски наем (лизинг)</t>
+        </is>
+      </c>
+      <c r="C1908" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D1908" s="10" t="inlineStr"/>
+      <c r="E1908" s="10" t="inlineStr"/>
+      <c r="F1908" s="10" t="inlineStr"/>
+    </row>
+    <row r="1909">
+      <c r="A1909" s="8" t="inlineStr">
+        <is>
+          <t>749</t>
+        </is>
+      </c>
+      <c r="B1909" s="9" t="inlineStr">
+        <is>
+          <t>Останати приходи од продажба на неповрзани друштва</t>
+        </is>
+      </c>
+      <c r="C1909" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D1909" s="10" t="inlineStr"/>
+      <c r="E1909" s="10" t="inlineStr"/>
+      <c r="F1909" s="10" t="inlineStr"/>
+    </row>
+    <row r="1910">
+      <c r="A1910" s="11" t="inlineStr">
+        <is>
+          <t>7490</t>
+        </is>
+      </c>
+      <c r="B1910" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од продажба на патенти, лиценци, жигови и слично</t>
+        </is>
+      </c>
+      <c r="C1910" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1910" s="13" t="inlineStr"/>
+      <c r="E1910" s="13" t="inlineStr"/>
+      <c r="F1910" s="13" t="inlineStr"/>
+    </row>
+    <row r="1911">
+      <c r="A1911" s="11" t="inlineStr">
+        <is>
+          <t>7491</t>
+        </is>
+      </c>
+      <c r="B1911" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од продажба на софтвер</t>
+        </is>
+      </c>
+      <c r="C1911" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1911" s="13" t="inlineStr"/>
+      <c r="E1911" s="13" t="inlineStr"/>
+      <c r="F1911" s="13" t="inlineStr"/>
+    </row>
+    <row r="1912">
+      <c r="A1912" s="11" t="inlineStr">
+        <is>
+          <t>7492</t>
+        </is>
+      </c>
+      <c r="B1912" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од продажба на франшиза</t>
+        </is>
+      </c>
+      <c r="C1912" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1912" s="13" t="inlineStr"/>
+      <c r="E1912" s="13" t="inlineStr"/>
+      <c r="F1912" s="13" t="inlineStr"/>
+    </row>
+    <row r="1913">
+      <c r="A1913" s="11" t="inlineStr">
+        <is>
+          <t>7499</t>
+        </is>
+      </c>
+      <c r="B1913" s="12" t="inlineStr">
+        <is>
+          <t>Останати приходи од продажба</t>
+        </is>
+      </c>
+      <c r="C1913" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1913" s="13" t="inlineStr"/>
+      <c r="E1913" s="13" t="inlineStr"/>
+      <c r="F1913" s="13" t="inlineStr"/>
+    </row>
+    <row r="1914">
+      <c r="A1914" s="5" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="B1914" s="6" t="inlineStr">
+        <is>
+          <t>ПРИХОДИ ОД ВРЕДНОСНО УСОГЛАСУВАЊЕ НА НЕТЕКОВНИ И ТЕКОВНИ СРЕДСТВА</t>
+        </is>
+      </c>
+      <c r="C1914" s="7" t="inlineStr">
+        <is>
+          <t>Група</t>
+        </is>
+      </c>
+      <c r="D1914" s="7" t="inlineStr"/>
+      <c r="E1914" s="7" t="inlineStr"/>
+      <c r="F1914" s="7" t="inlineStr"/>
+    </row>
+    <row r="1915">
+      <c r="A1915" s="8" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="B1915" s="9" t="inlineStr">
+        <is>
+          <t>Приходи од вредносно усогласување на нематеријални средства</t>
+        </is>
+      </c>
+      <c r="C1915" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D1915" s="10" t="inlineStr"/>
+      <c r="E1915" s="10" t="inlineStr"/>
+      <c r="F1915" s="10" t="inlineStr"/>
+    </row>
+    <row r="1916">
+      <c r="A1916" s="11" t="inlineStr">
+        <is>
+          <t>7500</t>
+        </is>
+      </c>
+      <c r="B1916" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од вредносно усогласување на вложувања во развој</t>
+        </is>
+      </c>
+      <c r="C1916" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1916" s="13" t="inlineStr"/>
+      <c r="E1916" s="13" t="inlineStr"/>
+      <c r="F1916" s="13" t="inlineStr"/>
+    </row>
+    <row r="1917">
+      <c r="A1917" s="11" t="inlineStr">
+        <is>
+          <t>7501</t>
+        </is>
+      </c>
+      <c r="B1917" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од вредносно усогласување на концесии</t>
+        </is>
+      </c>
+      <c r="C1917" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1917" s="13" t="inlineStr"/>
+      <c r="E1917" s="13" t="inlineStr"/>
+      <c r="F1917" s="13" t="inlineStr"/>
+    </row>
+    <row r="1918">
+      <c r="A1918" s="11" t="inlineStr">
+        <is>
+          <t>7502</t>
+        </is>
+      </c>
+      <c r="B1918" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од вредносно усогласување на патенти, лиценци и слични права</t>
+        </is>
+      </c>
+      <c r="C1918" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1918" s="13" t="inlineStr"/>
+      <c r="E1918" s="13" t="inlineStr"/>
+      <c r="F1918" s="13" t="inlineStr"/>
+    </row>
+    <row r="1919">
+      <c r="A1919" s="11" t="inlineStr">
+        <is>
+          <t>7509</t>
+        </is>
+      </c>
+      <c r="B1919" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од вредносно усогласување на останати нематеријални средства</t>
+        </is>
+      </c>
+      <c r="C1919" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1919" s="13" t="inlineStr"/>
+      <c r="E1919" s="13" t="inlineStr"/>
+      <c r="F1919" s="13" t="inlineStr"/>
+    </row>
+    <row r="1920">
+      <c r="A1920" s="8" t="inlineStr">
+        <is>
+          <t>751</t>
+        </is>
+      </c>
+      <c r="B1920" s="9" t="inlineStr">
+        <is>
+          <t>Приходи од вредносно усогласување на материјални средства</t>
+        </is>
+      </c>
+      <c r="C1920" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D1920" s="10" t="inlineStr"/>
+      <c r="E1920" s="10" t="inlineStr"/>
+      <c r="F1920" s="10" t="inlineStr"/>
+    </row>
+    <row r="1921">
+      <c r="A1921" s="11" t="inlineStr">
+        <is>
+          <t>7510</t>
+        </is>
+      </c>
+      <c r="B1921" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од вредносно усогласување на недвижности</t>
+        </is>
+      </c>
+      <c r="C1921" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1921" s="13" t="inlineStr"/>
+      <c r="E1921" s="13" t="inlineStr"/>
+      <c r="F1921" s="13" t="inlineStr"/>
+    </row>
+    <row r="1922">
+      <c r="A1922" s="11" t="inlineStr">
+        <is>
+          <t>7511</t>
+        </is>
+      </c>
+      <c r="B1922" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од вредносно усогласување на постројки и опрема</t>
+        </is>
+      </c>
+      <c r="C1922" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1922" s="13" t="inlineStr"/>
+      <c r="E1922" s="13" t="inlineStr"/>
+      <c r="F1922" s="13" t="inlineStr"/>
+    </row>
+    <row r="1923">
+      <c r="A1923" s="11" t="inlineStr">
+        <is>
+          <t>7512</t>
+        </is>
+      </c>
+      <c r="B1923" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од вредносно усогласување на алат, погонски инвентар и транспортни средства</t>
+        </is>
+      </c>
+      <c r="C1923" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1923" s="13" t="inlineStr"/>
+      <c r="E1923" s="13" t="inlineStr"/>
+      <c r="F1923" s="13" t="inlineStr"/>
+    </row>
+    <row r="1924">
+      <c r="A1924" s="11" t="inlineStr">
+        <is>
+          <t>7513</t>
+        </is>
+      </c>
+      <c r="B1924" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од вредносно усогласување на биолошки средства</t>
+        </is>
+      </c>
+      <c r="C1924" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1924" s="13" t="inlineStr"/>
+      <c r="E1924" s="13" t="inlineStr"/>
+      <c r="F1924" s="13" t="inlineStr"/>
+    </row>
+    <row r="1925">
+      <c r="A1925" s="11" t="inlineStr">
+        <is>
+          <t>75130</t>
+        </is>
+      </c>
+      <c r="B1925" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од вредносно усогласување на шуми</t>
+        </is>
+      </c>
+      <c r="C1925" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1925" s="13" t="inlineStr"/>
+      <c r="E1925" s="13" t="inlineStr"/>
+      <c r="F1925" s="13" t="inlineStr"/>
+    </row>
+    <row r="1926">
+      <c r="A1926" s="11" t="inlineStr">
+        <is>
+          <t>75131</t>
+        </is>
+      </c>
+      <c r="B1926" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од вредносно усогласување на повеќегодишни насади</t>
+        </is>
+      </c>
+      <c r="C1926" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1926" s="13" t="inlineStr"/>
+      <c r="E1926" s="13" t="inlineStr"/>
+      <c r="F1926" s="13" t="inlineStr"/>
+    </row>
+    <row r="1927">
+      <c r="A1927" s="11" t="inlineStr">
+        <is>
+          <t>75132</t>
+        </is>
+      </c>
+      <c r="B1927" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од вредносно усогласување на основно стадо</t>
+        </is>
+      </c>
+      <c r="C1927" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1927" s="13" t="inlineStr"/>
+      <c r="E1927" s="13" t="inlineStr"/>
+      <c r="F1927" s="13" t="inlineStr"/>
+    </row>
+    <row r="1928">
+      <c r="A1928" s="8" t="inlineStr">
+        <is>
+          <t>752</t>
+        </is>
+      </c>
+      <c r="B1928" s="9" t="inlineStr">
+        <is>
+          <t>Приходи од вредносно усогласување на вложувања во недвижности</t>
+        </is>
+      </c>
+      <c r="C1928" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D1928" s="10" t="inlineStr"/>
+      <c r="E1928" s="10" t="inlineStr"/>
+      <c r="F1928" s="10" t="inlineStr"/>
+    </row>
+    <row r="1929">
+      <c r="A1929" s="11" t="inlineStr">
+        <is>
+          <t>7520</t>
+        </is>
+      </c>
+      <c r="B1929" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од вредносно усогласување на земјиште</t>
+        </is>
+      </c>
+      <c r="C1929" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1929" s="13" t="inlineStr"/>
+      <c r="E1929" s="13" t="inlineStr"/>
+      <c r="F1929" s="13" t="inlineStr"/>
+    </row>
+    <row r="1930">
+      <c r="A1930" s="11" t="inlineStr">
+        <is>
+          <t>7521</t>
+        </is>
+      </c>
+      <c r="B1930" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од вредносно усогласување на градежни објекти</t>
+        </is>
+      </c>
+      <c r="C1930" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1930" s="13" t="inlineStr"/>
+      <c r="E1930" s="13" t="inlineStr"/>
+      <c r="F1930" s="13" t="inlineStr"/>
+    </row>
+    <row r="1931">
+      <c r="A1931" s="8" t="inlineStr">
+        <is>
+          <t>753</t>
+        </is>
+      </c>
+      <c r="B1931" s="9" t="inlineStr">
+        <is>
+          <t>Приходи од вредносно усогласување на останати материјални средства</t>
+        </is>
+      </c>
+      <c r="C1931" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D1931" s="10" t="inlineStr"/>
+      <c r="E1931" s="10" t="inlineStr"/>
+      <c r="F1931" s="10" t="inlineStr"/>
+    </row>
+    <row r="1932">
+      <c r="A1932" s="8" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="B1932" s="9" t="inlineStr">
+        <is>
+          <t>Приходи од вредносно усогласување на долгорочни побарувања, депозити и слично</t>
+        </is>
+      </c>
+      <c r="C1932" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D1932" s="10" t="inlineStr"/>
+      <c r="E1932" s="10" t="inlineStr"/>
+      <c r="F1932" s="10" t="inlineStr"/>
+    </row>
+    <row r="1933">
+      <c r="A1933" s="11" t="inlineStr">
+        <is>
+          <t>7540</t>
+        </is>
+      </c>
+      <c r="B1933" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од вредносно усогласување на долгорочни побарувања</t>
+        </is>
+      </c>
+      <c r="C1933" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1933" s="13" t="inlineStr"/>
+      <c r="E1933" s="13" t="inlineStr"/>
+      <c r="F1933" s="13" t="inlineStr"/>
+    </row>
+    <row r="1934">
+      <c r="A1934" s="11" t="inlineStr">
+        <is>
+          <t>7541</t>
+        </is>
+      </c>
+      <c r="B1934" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од вредносно усогласување на долгорочни депозити</t>
+        </is>
+      </c>
+      <c r="C1934" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1934" s="13" t="inlineStr"/>
+      <c r="E1934" s="13" t="inlineStr"/>
+      <c r="F1934" s="13" t="inlineStr"/>
+    </row>
+    <row r="1935">
+      <c r="A1935" s="8" t="inlineStr">
+        <is>
+          <t>755</t>
+        </is>
+      </c>
+      <c r="B1935" s="9" t="inlineStr">
+        <is>
+          <t>Приходи од вредносно усогласување на краткорочни побарувања</t>
+        </is>
+      </c>
+      <c r="C1935" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D1935" s="10" t="inlineStr"/>
+      <c r="E1935" s="10" t="inlineStr"/>
+      <c r="F1935" s="10" t="inlineStr"/>
+    </row>
+    <row r="1936">
+      <c r="A1936" s="11" t="inlineStr">
+        <is>
+          <t>7550</t>
+        </is>
+      </c>
+      <c r="B1936" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од вредносно усогласување на краткорочни побарувања од поврзани друштва</t>
+        </is>
+      </c>
+      <c r="C1936" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1936" s="13" t="inlineStr"/>
+      <c r="E1936" s="13" t="inlineStr"/>
+      <c r="F1936" s="13" t="inlineStr"/>
+    </row>
+    <row r="1937">
+      <c r="A1937" s="11" t="inlineStr">
+        <is>
+          <t>7551</t>
+        </is>
+      </c>
+      <c r="B1937" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од вредносно усогласување на краткорочни побарувања од неповрзани друштва</t>
+        </is>
+      </c>
+      <c r="C1937" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1937" s="13" t="inlineStr"/>
+      <c r="E1937" s="13" t="inlineStr"/>
+      <c r="F1937" s="13" t="inlineStr"/>
+    </row>
+    <row r="1938">
+      <c r="A1938" s="8" t="inlineStr">
+        <is>
+          <t>756</t>
+        </is>
+      </c>
+      <c r="B1938" s="9" t="inlineStr">
+        <is>
+          <t>Приходи од вредносно усогласување на залихи</t>
+        </is>
+      </c>
+      <c r="C1938" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D1938" s="10" t="inlineStr"/>
+      <c r="E1938" s="10" t="inlineStr"/>
+      <c r="F1938" s="10" t="inlineStr"/>
+    </row>
+    <row r="1939">
+      <c r="A1939" s="11" t="inlineStr">
+        <is>
+          <t>7560</t>
+        </is>
+      </c>
+      <c r="B1939" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од вредносно усогласување на материјали</t>
+        </is>
+      </c>
+      <c r="C1939" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1939" s="13" t="inlineStr"/>
+      <c r="E1939" s="13" t="inlineStr"/>
+      <c r="F1939" s="13" t="inlineStr"/>
+    </row>
+    <row r="1940">
+      <c r="A1940" s="11" t="inlineStr">
+        <is>
+          <t>7561</t>
+        </is>
+      </c>
+      <c r="B1940" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од вредносно усогласување на резервни делови, ситен инвентар и автогуми</t>
+        </is>
+      </c>
+      <c r="C1940" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1940" s="13" t="inlineStr"/>
+      <c r="E1940" s="13" t="inlineStr"/>
+      <c r="F1940" s="13" t="inlineStr"/>
+    </row>
+    <row r="1941">
+      <c r="A1941" s="11" t="inlineStr">
+        <is>
+          <t>7562</t>
+        </is>
+      </c>
+      <c r="B1941" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од вредносно усогласување на залихи на стоки во магацин и продавница</t>
+        </is>
+      </c>
+      <c r="C1941" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1941" s="13" t="inlineStr"/>
+      <c r="E1941" s="13" t="inlineStr"/>
+      <c r="F1941" s="13" t="inlineStr"/>
+    </row>
+    <row r="1942">
+      <c r="A1942" s="8" t="inlineStr">
+        <is>
+          <t>757</t>
+        </is>
+      </c>
+      <c r="B1942" s="9" t="inlineStr">
+        <is>
+          <t>Приходи од вредносно усогласување на нетековни средства кои се чуваат за продажба и прекинато работење</t>
+        </is>
+      </c>
+      <c r="C1942" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D1942" s="10" t="inlineStr"/>
+      <c r="E1942" s="10" t="inlineStr"/>
+      <c r="F1942" s="10" t="inlineStr"/>
+    </row>
+    <row r="1943">
+      <c r="A1943" s="8" t="inlineStr">
+        <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="B1943" s="9" t="inlineStr">
+        <is>
+          <t>Приходи од вредносно усогласување на останати средства</t>
+        </is>
+      </c>
+      <c r="C1943" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D1943" s="10" t="inlineStr"/>
+      <c r="E1943" s="10" t="inlineStr"/>
+      <c r="F1943" s="10" t="inlineStr"/>
+    </row>
+    <row r="1944">
+      <c r="A1944" s="11" t="inlineStr">
+        <is>
+          <t>7590</t>
+        </is>
+      </c>
+      <c r="B1944" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од вредносно усогласување на аванси, депозити и кауции</t>
+        </is>
+      </c>
+      <c r="C1944" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1944" s="13" t="inlineStr"/>
+      <c r="E1944" s="13" t="inlineStr"/>
+      <c r="F1944" s="13" t="inlineStr"/>
+    </row>
+    <row r="1945">
+      <c r="A1945" s="11" t="inlineStr">
+        <is>
+          <t>7591</t>
+        </is>
+      </c>
+      <c r="B1945" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од вредносно усогласување на готовински еквиваленти</t>
+        </is>
+      </c>
+      <c r="C1945" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1945" s="13" t="inlineStr"/>
+      <c r="E1945" s="13" t="inlineStr"/>
+      <c r="F1945" s="13" t="inlineStr"/>
+    </row>
+    <row r="1946">
+      <c r="A1946" s="11" t="inlineStr">
+        <is>
+          <t>7599</t>
+        </is>
+      </c>
+      <c r="B1946" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од вредносно усогласување на останати средства</t>
+        </is>
+      </c>
+      <c r="C1946" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1946" s="13" t="inlineStr"/>
+      <c r="E1946" s="13" t="inlineStr"/>
+      <c r="F1946" s="13" t="inlineStr"/>
+    </row>
+    <row r="1947">
+      <c r="A1947" s="5" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="B1947" s="6" t="inlineStr">
+        <is>
+          <t>ОСТАНАТИ ПРИХОДИ</t>
+        </is>
+      </c>
+      <c r="C1947" s="7" t="inlineStr">
+        <is>
+          <t>Група</t>
+        </is>
+      </c>
+      <c r="D1947" s="7" t="inlineStr"/>
+      <c r="E1947" s="7" t="inlineStr"/>
+      <c r="F1947" s="7" t="inlineStr"/>
+    </row>
+    <row r="1948">
+      <c r="A1948" s="8" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="B1948" s="9" t="inlineStr">
+        <is>
+          <t>Добивки од продажба на нематеријални и материјални средства</t>
+        </is>
+      </c>
+      <c r="C1948" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D1948" s="10" t="inlineStr"/>
+      <c r="E1948" s="10" t="inlineStr"/>
+      <c r="F1948" s="10" t="inlineStr"/>
+    </row>
+    <row r="1949">
+      <c r="A1949" s="11" t="inlineStr">
+        <is>
+          <t>7600</t>
+        </is>
+      </c>
+      <c r="B1949" s="12" t="inlineStr">
+        <is>
+          <t>Добивки од продажба на нематеријални средства</t>
+        </is>
+      </c>
+      <c r="C1949" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1949" s="13" t="inlineStr"/>
+      <c r="E1949" s="13" t="inlineStr"/>
+      <c r="F1949" s="13" t="inlineStr"/>
+    </row>
+    <row r="1950">
+      <c r="A1950" s="11" t="inlineStr">
+        <is>
+          <t>7601</t>
+        </is>
+      </c>
+      <c r="B1950" s="12" t="inlineStr">
+        <is>
+          <t>Добивки од продажба на недвижности, постројки и опрема</t>
+        </is>
+      </c>
+      <c r="C1950" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1950" s="13" t="inlineStr"/>
+      <c r="E1950" s="13" t="inlineStr"/>
+      <c r="F1950" s="13" t="inlineStr"/>
+    </row>
+    <row r="1951">
+      <c r="A1951" s="11" t="inlineStr">
+        <is>
+          <t>7602</t>
+        </is>
+      </c>
+      <c r="B1951" s="12" t="inlineStr">
+        <is>
+          <t>Добивки од продажба на алат, погонски инвентар, мебел и транспортни средства</t>
+        </is>
+      </c>
+      <c r="C1951" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1951" s="13" t="inlineStr"/>
+      <c r="E1951" s="13" t="inlineStr"/>
+      <c r="F1951" s="13" t="inlineStr"/>
+    </row>
+    <row r="1952">
+      <c r="A1952" s="11" t="inlineStr">
+        <is>
+          <t>7603</t>
+        </is>
+      </c>
+      <c r="B1952" s="12" t="inlineStr">
+        <is>
+          <t>Добивки од продажба на материјални средства кои не се амортизираат</t>
+        </is>
+      </c>
+      <c r="C1952" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1952" s="13" t="inlineStr"/>
+      <c r="E1952" s="13" t="inlineStr"/>
+      <c r="F1952" s="13" t="inlineStr"/>
+    </row>
+    <row r="1953">
+      <c r="A1953" s="8" t="inlineStr">
+        <is>
+          <t>761</t>
+        </is>
+      </c>
+      <c r="B1953" s="9" t="inlineStr">
+        <is>
+          <t>Добивки од продажба на биолошки средства</t>
+        </is>
+      </c>
+      <c r="C1953" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D1953" s="10" t="inlineStr"/>
+      <c r="E1953" s="10" t="inlineStr"/>
+      <c r="F1953" s="10" t="inlineStr"/>
+    </row>
+    <row r="1954">
+      <c r="A1954" s="11" t="inlineStr">
+        <is>
+          <t>7610</t>
+        </is>
+      </c>
+      <c r="B1954" s="12" t="inlineStr">
+        <is>
+          <t>Добивки од продажба на шуми</t>
+        </is>
+      </c>
+      <c r="C1954" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1954" s="13" t="inlineStr"/>
+      <c r="E1954" s="13" t="inlineStr"/>
+      <c r="F1954" s="13" t="inlineStr"/>
+    </row>
+    <row r="1955">
+      <c r="A1955" s="11" t="inlineStr">
+        <is>
+          <t>7611</t>
+        </is>
+      </c>
+      <c r="B1955" s="12" t="inlineStr">
+        <is>
+          <t>Добивки од продажба на повеќегодишни насади</t>
+        </is>
+      </c>
+      <c r="C1955" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1955" s="13" t="inlineStr"/>
+      <c r="E1955" s="13" t="inlineStr"/>
+      <c r="F1955" s="13" t="inlineStr"/>
+    </row>
+    <row r="1956">
+      <c r="A1956" s="11" t="inlineStr">
+        <is>
+          <t>7612</t>
+        </is>
+      </c>
+      <c r="B1956" s="12" t="inlineStr">
+        <is>
+          <t>Добивки од продажба на основно стадо</t>
+        </is>
+      </c>
+      <c r="C1956" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1956" s="13" t="inlineStr"/>
+      <c r="E1956" s="13" t="inlineStr"/>
+      <c r="F1956" s="13" t="inlineStr"/>
+    </row>
+    <row r="1957">
+      <c r="A1957" s="11" t="inlineStr">
+        <is>
+          <t>7619</t>
+        </is>
+      </c>
+      <c r="B1957" s="12" t="inlineStr">
+        <is>
+          <t>Добивки од продажба на останати биолошки средства</t>
+        </is>
+      </c>
+      <c r="C1957" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1957" s="13" t="inlineStr"/>
+      <c r="E1957" s="13" t="inlineStr"/>
+      <c r="F1957" s="13" t="inlineStr"/>
+    </row>
+    <row r="1958">
+      <c r="A1958" s="8" t="inlineStr">
+        <is>
+          <t>762</t>
+        </is>
+      </c>
+      <c r="B1958" s="9" t="inlineStr">
+        <is>
+          <t>Добивки од продажба на учество во капитал и хартии од вредност</t>
+        </is>
+      </c>
+      <c r="C1958" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D1958" s="10" t="inlineStr"/>
+      <c r="E1958" s="10" t="inlineStr"/>
+      <c r="F1958" s="10" t="inlineStr"/>
+    </row>
+    <row r="1959">
+      <c r="A1959" s="11" t="inlineStr">
+        <is>
+          <t>7620</t>
+        </is>
+      </c>
+      <c r="B1959" s="12" t="inlineStr">
+        <is>
+          <t>Добивки од продажба на акции</t>
+        </is>
+      </c>
+      <c r="C1959" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1959" s="13" t="inlineStr"/>
+      <c r="E1959" s="13" t="inlineStr"/>
+      <c r="F1959" s="13" t="inlineStr"/>
+    </row>
+    <row r="1960">
+      <c r="A1960" s="11" t="inlineStr">
+        <is>
+          <t>7621</t>
+        </is>
+      </c>
+      <c r="B1960" s="12" t="inlineStr">
+        <is>
+          <t>Добивки од продажба на удел</t>
+        </is>
+      </c>
+      <c r="C1960" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1960" s="13" t="inlineStr"/>
+      <c r="E1960" s="13" t="inlineStr"/>
+      <c r="F1960" s="13" t="inlineStr"/>
+    </row>
+    <row r="1961">
+      <c r="A1961" s="11" t="inlineStr">
+        <is>
+          <t>7622</t>
+        </is>
+      </c>
+      <c r="B1961" s="12" t="inlineStr">
+        <is>
+          <t>Добивки од продажба на долгорочни обврски</t>
+        </is>
+      </c>
+      <c r="C1961" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1961" s="13" t="inlineStr"/>
+      <c r="E1961" s="13" t="inlineStr"/>
+      <c r="F1961" s="13" t="inlineStr"/>
+    </row>
+    <row r="1962">
+      <c r="A1962" s="11" t="inlineStr">
+        <is>
+          <t>7629</t>
+        </is>
+      </c>
+      <c r="B1962" s="12" t="inlineStr">
+        <is>
+          <t>Добивки од продажба на останати хартии од вредност</t>
+        </is>
+      </c>
+      <c r="C1962" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1962" s="13" t="inlineStr"/>
+      <c r="E1962" s="13" t="inlineStr"/>
+      <c r="F1962" s="13" t="inlineStr"/>
+    </row>
+    <row r="1963">
+      <c r="A1963" s="8" t="inlineStr">
+        <is>
+          <t>763</t>
+        </is>
+      </c>
+      <c r="B1963" s="9" t="inlineStr">
+        <is>
+          <t>Добивки од продажба на материјали и отпадоци</t>
+        </is>
+      </c>
+      <c r="C1963" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D1963" s="10" t="inlineStr"/>
+      <c r="E1963" s="10" t="inlineStr"/>
+      <c r="F1963" s="10" t="inlineStr"/>
+    </row>
+    <row r="1964">
+      <c r="A1964" s="11" t="inlineStr">
+        <is>
+          <t>7630</t>
+        </is>
+      </c>
+      <c r="B1964" s="12" t="inlineStr">
+        <is>
+          <t>Добивки од продажба на материјали</t>
+        </is>
+      </c>
+      <c r="C1964" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1964" s="13" t="inlineStr"/>
+      <c r="E1964" s="13" t="inlineStr"/>
+      <c r="F1964" s="13" t="inlineStr"/>
+    </row>
+    <row r="1965">
+      <c r="A1965" s="11" t="inlineStr">
+        <is>
+          <t>7631</t>
+        </is>
+      </c>
+      <c r="B1965" s="12" t="inlineStr">
+        <is>
+          <t>Добивки од продажба на отпадоци</t>
+        </is>
+      </c>
+      <c r="C1965" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1965" s="13" t="inlineStr"/>
+      <c r="E1965" s="13" t="inlineStr"/>
+      <c r="F1965" s="13" t="inlineStr"/>
+    </row>
+    <row r="1966">
+      <c r="A1966" s="8" t="inlineStr">
+        <is>
+          <t>764</t>
+        </is>
+      </c>
+      <c r="B1966" s="9" t="inlineStr">
+        <is>
+          <t>Вишоци</t>
+        </is>
+      </c>
+      <c r="C1966" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D1966" s="10" t="inlineStr"/>
+      <c r="E1966" s="10" t="inlineStr"/>
+      <c r="F1966" s="10" t="inlineStr"/>
+    </row>
+    <row r="1967">
+      <c r="A1967" s="11" t="inlineStr">
+        <is>
+          <t>7640</t>
+        </is>
+      </c>
+      <c r="B1967" s="12" t="inlineStr">
+        <is>
+          <t>Вишоци на нематеријални средства</t>
+        </is>
+      </c>
+      <c r="C1967" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1967" s="13" t="inlineStr"/>
+      <c r="E1967" s="13" t="inlineStr"/>
+      <c r="F1967" s="13" t="inlineStr"/>
+    </row>
+    <row r="1968">
+      <c r="A1968" s="11" t="inlineStr">
+        <is>
+          <t>7641</t>
+        </is>
+      </c>
+      <c r="B1968" s="12" t="inlineStr">
+        <is>
+          <t>Вишоци на недвижности, постројки и опрема</t>
+        </is>
+      </c>
+      <c r="C1968" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1968" s="13" t="inlineStr"/>
+      <c r="E1968" s="13" t="inlineStr"/>
+      <c r="F1968" s="13" t="inlineStr"/>
+    </row>
+    <row r="1969">
+      <c r="A1969" s="11" t="inlineStr">
+        <is>
+          <t>7642</t>
+        </is>
+      </c>
+      <c r="B1969" s="12" t="inlineStr">
+        <is>
+          <t>Вишоци на материјали</t>
+        </is>
+      </c>
+      <c r="C1969" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1969" s="13" t="inlineStr"/>
+      <c r="E1969" s="13" t="inlineStr"/>
+      <c r="F1969" s="13" t="inlineStr"/>
+    </row>
+    <row r="1970">
+      <c r="A1970" s="11" t="inlineStr">
+        <is>
+          <t>7643</t>
+        </is>
+      </c>
+      <c r="B1970" s="12" t="inlineStr">
+        <is>
+          <t>Вишоци на резервни делови, ситен инвентар, амбалажа и автогуми</t>
+        </is>
+      </c>
+      <c r="C1970" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1970" s="13" t="inlineStr"/>
+      <c r="E1970" s="13" t="inlineStr"/>
+      <c r="F1970" s="13" t="inlineStr"/>
+    </row>
+    <row r="1971">
+      <c r="A1971" s="11" t="inlineStr">
+        <is>
+          <t>7644</t>
+        </is>
+      </c>
+      <c r="B1971" s="12" t="inlineStr">
+        <is>
+          <t>Вишоци на стоки</t>
+        </is>
+      </c>
+      <c r="C1971" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1971" s="13" t="inlineStr"/>
+      <c r="E1971" s="13" t="inlineStr"/>
+      <c r="F1971" s="13" t="inlineStr"/>
+    </row>
+    <row r="1972">
+      <c r="A1972" s="11" t="inlineStr">
+        <is>
+          <t>7645</t>
+        </is>
+      </c>
+      <c r="B1972" s="12" t="inlineStr">
+        <is>
+          <t>Вишоци на пари и парични еквиваленти</t>
+        </is>
+      </c>
+      <c r="C1972" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1972" s="13" t="inlineStr"/>
+      <c r="E1972" s="13" t="inlineStr"/>
+      <c r="F1972" s="13" t="inlineStr"/>
+    </row>
+    <row r="1973">
+      <c r="A1973" s="11" t="inlineStr">
+        <is>
+          <t>7649</t>
+        </is>
+      </c>
+      <c r="B1973" s="12" t="inlineStr">
+        <is>
+          <t>Вишоци на останати средства</t>
+        </is>
+      </c>
+      <c r="C1973" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1973" s="13" t="inlineStr"/>
+      <c r="E1973" s="13" t="inlineStr"/>
+      <c r="F1973" s="13" t="inlineStr"/>
+    </row>
+    <row r="1974">
+      <c r="A1974" s="8" t="inlineStr">
+        <is>
+          <t>765</t>
+        </is>
+      </c>
+      <c r="B1974" s="9" t="inlineStr">
+        <is>
+          <t>Приходи од наплатени отпишани побарувања и приходи од отпис на обврските</t>
+        </is>
+      </c>
+      <c r="C1974" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D1974" s="10" t="inlineStr"/>
+      <c r="E1974" s="10" t="inlineStr"/>
+      <c r="F1974" s="10" t="inlineStr"/>
+    </row>
+    <row r="1975">
+      <c r="A1975" s="11" t="inlineStr">
+        <is>
+          <t>7650</t>
+        </is>
+      </c>
+      <c r="B1975" s="12" t="inlineStr">
+        <is>
+          <t>Наплатени отпишани побарувања од поврзани друштва</t>
+        </is>
+      </c>
+      <c r="C1975" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1975" s="13" t="inlineStr"/>
+      <c r="E1975" s="13" t="inlineStr"/>
+      <c r="F1975" s="13" t="inlineStr"/>
+    </row>
+    <row r="1976">
+      <c r="A1976" s="11" t="inlineStr">
+        <is>
+          <t>76500</t>
+        </is>
+      </c>
+      <c r="B1976" s="12" t="inlineStr">
+        <is>
+          <t>Наплатени отпишани побарувања од матични и зависни друштва</t>
+        </is>
+      </c>
+      <c r="C1976" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1976" s="13" t="inlineStr"/>
+      <c r="E1976" s="13" t="inlineStr"/>
+      <c r="F1976" s="13" t="inlineStr"/>
+    </row>
+    <row r="1977">
+      <c r="A1977" s="11" t="inlineStr">
+        <is>
+          <t>76501</t>
+        </is>
+      </c>
+      <c r="B1977" s="12" t="inlineStr">
+        <is>
+          <t>Наплатени отпишани побарувања од други поврзани друштва</t>
+        </is>
+      </c>
+      <c r="C1977" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1977" s="13" t="inlineStr"/>
+      <c r="E1977" s="13" t="inlineStr"/>
+      <c r="F1977" s="13" t="inlineStr"/>
+    </row>
+    <row r="1978">
+      <c r="A1978" s="11" t="inlineStr">
+        <is>
+          <t>7651</t>
+        </is>
+      </c>
+      <c r="B1978" s="12" t="inlineStr">
+        <is>
+          <t>Наплатени отпишани побарувања од неповрзани друштва</t>
+        </is>
+      </c>
+      <c r="C1978" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1978" s="13" t="inlineStr"/>
+      <c r="E1978" s="13" t="inlineStr"/>
+      <c r="F1978" s="13" t="inlineStr"/>
+    </row>
+    <row r="1979">
+      <c r="A1979" s="11" t="inlineStr">
+        <is>
+          <t>7652</t>
+        </is>
+      </c>
+      <c r="B1979" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од отпис на обврските од поврзани друштва</t>
+        </is>
+      </c>
+      <c r="C1979" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1979" s="13" t="inlineStr"/>
+      <c r="E1979" s="13" t="inlineStr"/>
+      <c r="F1979" s="13" t="inlineStr"/>
+    </row>
+    <row r="1980">
+      <c r="A1980" s="11" t="inlineStr">
+        <is>
+          <t>76520</t>
+        </is>
+      </c>
+      <c r="B1980" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од отпис на обврските од матични и зависни друштва</t>
+        </is>
+      </c>
+      <c r="C1980" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1980" s="13" t="inlineStr"/>
+      <c r="E1980" s="13" t="inlineStr"/>
+      <c r="F1980" s="13" t="inlineStr"/>
+    </row>
+    <row r="1981">
+      <c r="A1981" s="11" t="inlineStr">
+        <is>
+          <t>76521</t>
+        </is>
+      </c>
+      <c r="B1981" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од отпис на обврските од други поврзани друштва</t>
+        </is>
+      </c>
+      <c r="C1981" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1981" s="13" t="inlineStr"/>
+      <c r="E1981" s="13" t="inlineStr"/>
+      <c r="F1981" s="13" t="inlineStr"/>
+    </row>
+    <row r="1982">
+      <c r="A1982" s="11" t="inlineStr">
+        <is>
+          <t>7653</t>
+        </is>
+      </c>
+      <c r="B1982" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од отпис на обврските од неповрзани друштва</t>
+        </is>
+      </c>
+      <c r="C1982" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1982" s="13" t="inlineStr"/>
+      <c r="E1982" s="13" t="inlineStr"/>
+      <c r="F1982" s="13" t="inlineStr"/>
+    </row>
+    <row r="1983">
+      <c r="A1983" s="8" t="inlineStr">
+        <is>
+          <t>766</t>
+        </is>
+      </c>
+      <c r="B1983" s="9" t="inlineStr">
+        <is>
+          <t>Приходи врз основа на ефекти од договорена заштита од ризик</t>
+        </is>
+      </c>
+      <c r="C1983" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D1983" s="10" t="inlineStr"/>
+      <c r="E1983" s="10" t="inlineStr"/>
+      <c r="F1983" s="10" t="inlineStr"/>
+    </row>
+    <row r="1984">
+      <c r="A1984" s="11" t="inlineStr">
+        <is>
+          <t>7660</t>
+        </is>
+      </c>
+      <c r="B1984" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од ефектот од заштита од ризик од ревалоризирани побарувања и обврски од матични и зависни друштва</t>
+        </is>
+      </c>
+      <c r="C1984" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1984" s="13" t="inlineStr"/>
+      <c r="E1984" s="13" t="inlineStr"/>
+      <c r="F1984" s="13" t="inlineStr"/>
+    </row>
+    <row r="1985">
+      <c r="A1985" s="11" t="inlineStr">
+        <is>
+          <t>7661</t>
+        </is>
+      </c>
+      <c r="B1985" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од ефектот од заштита од ризик од ревалоризирани побарувања и обврски од други поврзани друштва</t>
+        </is>
+      </c>
+      <c r="C1985" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1985" s="13" t="inlineStr"/>
+      <c r="E1985" s="13" t="inlineStr"/>
+      <c r="F1985" s="13" t="inlineStr"/>
+    </row>
+    <row r="1986">
+      <c r="A1986" s="11" t="inlineStr">
+        <is>
+          <t>7662</t>
+        </is>
+      </c>
+      <c r="B1986" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од ефектот од заштита од ризик од ревалоризирани побарувања и обврски од неповрзани друштва</t>
+        </is>
+      </c>
+      <c r="C1986" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1986" s="13" t="inlineStr"/>
+      <c r="E1986" s="13" t="inlineStr"/>
+      <c r="F1986" s="13" t="inlineStr"/>
+    </row>
+    <row r="1987">
+      <c r="A1987" s="11" t="inlineStr">
+        <is>
+          <t>7663</t>
+        </is>
+      </c>
+      <c r="B1987" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од ефектот од заштита од ризик за побарувања и обврски врз основа на други договорени облици</t>
+        </is>
+      </c>
+      <c r="C1987" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1987" s="13" t="inlineStr"/>
+      <c r="E1987" s="13" t="inlineStr"/>
+      <c r="F1987" s="13" t="inlineStr"/>
+    </row>
+    <row r="1988">
+      <c r="A1988" s="8" t="inlineStr">
+        <is>
+          <t>767</t>
+        </is>
+      </c>
+      <c r="B1988" s="9" t="inlineStr">
+        <is>
+          <t>Приходи од премии, субвенции, дотации и донации</t>
+        </is>
+      </c>
+      <c r="C1988" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D1988" s="10" t="inlineStr"/>
+      <c r="E1988" s="10" t="inlineStr"/>
+      <c r="F1988" s="10" t="inlineStr"/>
+    </row>
+    <row r="1989">
+      <c r="A1989" s="11" t="inlineStr">
+        <is>
+          <t>7670</t>
+        </is>
+      </c>
+      <c r="B1989" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од премии</t>
+        </is>
+      </c>
+      <c r="C1989" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1989" s="13" t="inlineStr"/>
+      <c r="E1989" s="13" t="inlineStr"/>
+      <c r="F1989" s="13" t="inlineStr"/>
+    </row>
+    <row r="1990">
+      <c r="A1990" s="11" t="inlineStr">
+        <is>
+          <t>7671</t>
+        </is>
+      </c>
+      <c r="B1990" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од субвенции</t>
+        </is>
+      </c>
+      <c r="C1990" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1990" s="13" t="inlineStr"/>
+      <c r="E1990" s="13" t="inlineStr"/>
+      <c r="F1990" s="13" t="inlineStr"/>
+    </row>
+    <row r="1991">
+      <c r="A1991" s="11" t="inlineStr">
+        <is>
+          <t>7672</t>
+        </is>
+      </c>
+      <c r="B1991" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од донации и помошти (во добра и парични средства)</t>
+        </is>
+      </c>
+      <c r="C1991" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1991" s="13" t="inlineStr"/>
+      <c r="E1991" s="13" t="inlineStr"/>
+      <c r="F1991" s="13" t="inlineStr"/>
+    </row>
+    <row r="1992">
+      <c r="A1992" s="8" t="inlineStr">
+        <is>
+          <t>768</t>
+        </is>
+      </c>
+      <c r="B1992" s="9" t="inlineStr">
+        <is>
+          <t>Приходи од укинување на долгорочни резервирања</t>
+        </is>
+      </c>
+      <c r="C1992" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D1992" s="10" t="inlineStr"/>
+      <c r="E1992" s="10" t="inlineStr"/>
+      <c r="F1992" s="10" t="inlineStr"/>
+    </row>
+    <row r="1993">
+      <c r="A1993" s="11" t="inlineStr">
+        <is>
+          <t>7680</t>
+        </is>
+      </c>
+      <c r="B1993" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од укинување на долгорочни резервирања за обновување на природни богатства</t>
+        </is>
+      </c>
+      <c r="C1993" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1993" s="13" t="inlineStr"/>
+      <c r="E1993" s="13" t="inlineStr"/>
+      <c r="F1993" s="13" t="inlineStr"/>
+    </row>
+    <row r="1994">
+      <c r="A1994" s="11" t="inlineStr">
+        <is>
+          <t>7681</t>
+        </is>
+      </c>
+      <c r="B1994" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од укинување на долгорочни резервирања за користи на вработените</t>
+        </is>
+      </c>
+      <c r="C1994" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1994" s="13" t="inlineStr"/>
+      <c r="E1994" s="13" t="inlineStr"/>
+      <c r="F1994" s="13" t="inlineStr"/>
+    </row>
+    <row r="1995">
+      <c r="A1995" s="11" t="inlineStr">
+        <is>
+          <t>7682</t>
+        </is>
+      </c>
+      <c r="B1995" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од укинување на долгорочни резервирања за преструктуирање</t>
+        </is>
+      </c>
+      <c r="C1995" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1995" s="13" t="inlineStr"/>
+      <c r="E1995" s="13" t="inlineStr"/>
+      <c r="F1995" s="13" t="inlineStr"/>
+    </row>
+    <row r="1996">
+      <c r="A1996" s="11" t="inlineStr">
+        <is>
+          <t>7683</t>
+        </is>
+      </c>
+      <c r="B1996" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од укинување на долгорочни резервирања за гарантен рок</t>
+        </is>
+      </c>
+      <c r="C1996" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1996" s="13" t="inlineStr"/>
+      <c r="E1996" s="13" t="inlineStr"/>
+      <c r="F1996" s="13" t="inlineStr"/>
+    </row>
+    <row r="1997">
+      <c r="A1997" s="11" t="inlineStr">
+        <is>
+          <t>7684</t>
+        </is>
+      </c>
+      <c r="B1997" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од укинување на долгорочни резервирања за кауции и депозити</t>
+        </is>
+      </c>
+      <c r="C1997" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1997" s="13" t="inlineStr"/>
+      <c r="E1997" s="13" t="inlineStr"/>
+      <c r="F1997" s="13" t="inlineStr"/>
+    </row>
+    <row r="1998">
+      <c r="A1998" s="11" t="inlineStr">
+        <is>
+          <t>7689</t>
+        </is>
+      </c>
+      <c r="B1998" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од укинување на останати долгорочни резервирања</t>
+        </is>
+      </c>
+      <c r="C1998" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1998" s="13" t="inlineStr"/>
+      <c r="E1998" s="13" t="inlineStr"/>
+      <c r="F1998" s="13" t="inlineStr"/>
+    </row>
+    <row r="1999">
+      <c r="A1999" s="11" t="inlineStr">
+        <is>
+          <t>76890</t>
+        </is>
+      </c>
+      <c r="B1999" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од укинување на долгорочни резервирања за неповолни договори и започнати судски спорови</t>
+        </is>
+      </c>
+      <c r="C1999" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D1999" s="13" t="inlineStr"/>
+      <c r="E1999" s="13" t="inlineStr"/>
+      <c r="F1999" s="13" t="inlineStr"/>
+    </row>
+    <row r="2000">
+      <c r="A2000" s="11" t="inlineStr">
+        <is>
+          <t>76899</t>
+        </is>
+      </c>
+      <c r="B2000" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од укинување на останати долгорочни резервирања</t>
+        </is>
+      </c>
+      <c r="C2000" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2000" s="13" t="inlineStr"/>
+      <c r="E2000" s="13" t="inlineStr"/>
+      <c r="F2000" s="13" t="inlineStr"/>
+    </row>
+    <row r="2001">
+      <c r="A2001" s="8" t="inlineStr">
+        <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="B2001" s="9" t="inlineStr">
+        <is>
+          <t>Останати приходи од работењето</t>
+        </is>
+      </c>
+      <c r="C2001" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2001" s="10" t="inlineStr"/>
+      <c r="E2001" s="10" t="inlineStr"/>
+      <c r="F2001" s="10" t="inlineStr"/>
+    </row>
+    <row r="2002">
+      <c r="A2002" s="11" t="inlineStr">
+        <is>
+          <t>7690</t>
+        </is>
+      </c>
+      <c r="B2002" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од чланарини</t>
+        </is>
+      </c>
+      <c r="C2002" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2002" s="13" t="inlineStr"/>
+      <c r="E2002" s="13" t="inlineStr"/>
+      <c r="F2002" s="13" t="inlineStr"/>
+    </row>
+    <row r="2003">
+      <c r="A2003" s="11" t="inlineStr">
+        <is>
+          <t>7691</t>
+        </is>
+      </c>
+      <c r="B2003" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од наплатени пенали, казни и штети</t>
+        </is>
+      </c>
+      <c r="C2003" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2003" s="13" t="inlineStr"/>
+      <c r="E2003" s="13" t="inlineStr"/>
+      <c r="F2003" s="13" t="inlineStr"/>
+    </row>
+    <row r="2004">
+      <c r="A2004" s="11" t="inlineStr">
+        <is>
+          <t>7692</t>
+        </is>
+      </c>
+      <c r="B2004" s="12" t="inlineStr">
+        <is>
+          <t>Приходи за надомест на штета од осигурителни друштва</t>
+        </is>
+      </c>
+      <c r="C2004" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2004" s="13" t="inlineStr"/>
+      <c r="E2004" s="13" t="inlineStr"/>
+      <c r="F2004" s="13" t="inlineStr"/>
+    </row>
+    <row r="2005">
+      <c r="A2005" s="11" t="inlineStr">
+        <is>
+          <t>7693</t>
+        </is>
+      </c>
+      <c r="B2005" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од вратени премии за осигурување врз други основи</t>
+        </is>
+      </c>
+      <c r="C2005" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2005" s="13" t="inlineStr"/>
+      <c r="E2005" s="13" t="inlineStr"/>
+      <c r="F2005" s="13" t="inlineStr"/>
+    </row>
+    <row r="2006">
+      <c r="A2006" s="11" t="inlineStr">
+        <is>
+          <t>7694</t>
+        </is>
+      </c>
+      <c r="B2006" s="12" t="inlineStr">
+        <is>
+          <t>Приходи врз основа на реклама, пропаганда и спонзорство</t>
+        </is>
+      </c>
+      <c r="C2006" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2006" s="13" t="inlineStr"/>
+      <c r="E2006" s="13" t="inlineStr"/>
+      <c r="F2006" s="13" t="inlineStr"/>
+    </row>
+    <row r="2007">
+      <c r="A2007" s="11" t="inlineStr">
+        <is>
+          <t>7695</t>
+        </is>
+      </c>
+      <c r="B2007" s="12" t="inlineStr">
+        <is>
+          <t>Приходи врз основа на повеќе платени даноци и придонеси</t>
+        </is>
+      </c>
+      <c r="C2007" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2007" s="13" t="inlineStr"/>
+      <c r="E2007" s="13" t="inlineStr"/>
+      <c r="F2007" s="13" t="inlineStr"/>
+    </row>
+    <row r="2008">
+      <c r="A2008" s="11" t="inlineStr">
+        <is>
+          <t>7696</t>
+        </is>
+      </c>
+      <c r="B2008" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од наплатени кауции, капари, тендери и слично</t>
+        </is>
+      </c>
+      <c r="C2008" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2008" s="13" t="inlineStr"/>
+      <c r="E2008" s="13" t="inlineStr"/>
+      <c r="F2008" s="13" t="inlineStr"/>
+    </row>
+    <row r="2009">
+      <c r="A2009" s="11" t="inlineStr">
+        <is>
+          <t>7697</t>
+        </is>
+      </c>
+      <c r="B2009" s="12" t="inlineStr">
+        <is>
+          <t>Приходи врз основа на дополнително одобрени попусти, рабат, рекламации и слично</t>
+        </is>
+      </c>
+      <c r="C2009" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2009" s="13" t="inlineStr"/>
+      <c r="E2009" s="13" t="inlineStr"/>
+      <c r="F2009" s="13" t="inlineStr"/>
+    </row>
+    <row r="2010">
+      <c r="A2010" s="11" t="inlineStr">
+        <is>
+          <t>7698</t>
+        </is>
+      </c>
+      <c r="B2010" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од рефундации за плата и други надоместоци</t>
+        </is>
+      </c>
+      <c r="C2010" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2010" s="13" t="inlineStr"/>
+      <c r="E2010" s="13" t="inlineStr"/>
+      <c r="F2010" s="13" t="inlineStr"/>
+    </row>
+    <row r="2011">
+      <c r="A2011" s="11" t="inlineStr">
+        <is>
+          <t>7699</t>
+        </is>
+      </c>
+      <c r="B2011" s="12" t="inlineStr">
+        <is>
+          <t>Останати приходи</t>
+        </is>
+      </c>
+      <c r="C2011" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2011" s="13" t="inlineStr"/>
+      <c r="E2011" s="13" t="inlineStr"/>
+      <c r="F2011" s="13" t="inlineStr"/>
+    </row>
+    <row r="2012">
+      <c r="A2012" s="11" t="inlineStr">
+        <is>
+          <t>76990</t>
+        </is>
+      </c>
+      <c r="B2012" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од наплата по судски одлуки</t>
+        </is>
+      </c>
+      <c r="C2012" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2012" s="13" t="inlineStr"/>
+      <c r="E2012" s="13" t="inlineStr"/>
+      <c r="F2012" s="13" t="inlineStr"/>
+    </row>
+    <row r="2013">
+      <c r="A2013" s="11" t="inlineStr">
+        <is>
+          <t>76991</t>
+        </is>
+      </c>
+      <c r="B2013" s="12" t="inlineStr">
+        <is>
+          <t>Дополнително утврдени приходи од претходни години кои не се материјално значајни</t>
+        </is>
+      </c>
+      <c r="C2013" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2013" s="13" t="inlineStr"/>
+      <c r="E2013" s="13" t="inlineStr"/>
+      <c r="F2013" s="13" t="inlineStr"/>
+    </row>
+    <row r="2014">
+      <c r="A2014" s="11" t="inlineStr">
+        <is>
+          <t>76992</t>
+        </is>
+      </c>
+      <c r="B2014" s="12" t="inlineStr">
+        <is>
+          <t>Ефекти од промена на сметководствената политика која не е материјално значајна</t>
+        </is>
+      </c>
+      <c r="C2014" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2014" s="13" t="inlineStr"/>
+      <c r="E2014" s="13" t="inlineStr"/>
+      <c r="F2014" s="13" t="inlineStr"/>
+    </row>
+    <row r="2015">
+      <c r="A2015" s="11" t="inlineStr">
+        <is>
+          <t>76993</t>
+        </is>
+      </c>
+      <c r="B2015" s="12" t="inlineStr">
+        <is>
+          <t>Исправка на грешка од предходна година која не е материјално значајна</t>
+        </is>
+      </c>
+      <c r="C2015" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2015" s="13" t="inlineStr"/>
+      <c r="E2015" s="13" t="inlineStr"/>
+      <c r="F2015" s="13" t="inlineStr"/>
+    </row>
+    <row r="2016">
+      <c r="A2016" s="11" t="inlineStr">
+        <is>
+          <t>76999</t>
+        </is>
+      </c>
+      <c r="B2016" s="12" t="inlineStr">
+        <is>
+          <t>Останати приходи од работењето</t>
+        </is>
+      </c>
+      <c r="C2016" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2016" s="13" t="inlineStr"/>
+      <c r="E2016" s="13" t="inlineStr"/>
+      <c r="F2016" s="13" t="inlineStr"/>
+    </row>
+    <row r="2017">
+      <c r="A2017" s="5" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="B2017" s="6" t="inlineStr">
+        <is>
+          <t>ФИНАНСИСКИ ПРИХОДИ</t>
+        </is>
+      </c>
+      <c r="C2017" s="7" t="inlineStr">
+        <is>
+          <t>Група</t>
+        </is>
+      </c>
+      <c r="D2017" s="7" t="inlineStr"/>
+      <c r="E2017" s="7" t="inlineStr"/>
+      <c r="F2017" s="7" t="inlineStr"/>
+    </row>
+    <row r="2018">
+      <c r="A2018" s="8" t="inlineStr">
+        <is>
+          <t>770</t>
+        </is>
+      </c>
+      <c r="B2018" s="9" t="inlineStr">
+        <is>
+          <t>Приходи врз основа на камати од работењето со поврзани друштва</t>
+        </is>
+      </c>
+      <c r="C2018" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2018" s="10" t="inlineStr"/>
+      <c r="E2018" s="10" t="inlineStr"/>
+      <c r="F2018" s="10" t="inlineStr"/>
+    </row>
+    <row r="2019">
+      <c r="A2019" s="11" t="inlineStr">
+        <is>
+          <t>7700</t>
+        </is>
+      </c>
+      <c r="B2019" s="12" t="inlineStr">
+        <is>
+          <t>Приходи врз основа на камати од матични и зависни друштва во земјата</t>
+        </is>
+      </c>
+      <c r="C2019" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2019" s="13" t="inlineStr"/>
+      <c r="E2019" s="13" t="inlineStr"/>
+      <c r="F2019" s="13" t="inlineStr"/>
+    </row>
+    <row r="2020">
+      <c r="A2020" s="11" t="inlineStr">
+        <is>
+          <t>7701</t>
+        </is>
+      </c>
+      <c r="B2020" s="12" t="inlineStr">
+        <is>
+          <t>Приходи врз основа на камати од матични и зависни друштва од странство</t>
+        </is>
+      </c>
+      <c r="C2020" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2020" s="13" t="inlineStr"/>
+      <c r="E2020" s="13" t="inlineStr"/>
+      <c r="F2020" s="13" t="inlineStr"/>
+    </row>
+    <row r="2021">
+      <c r="A2021" s="11" t="inlineStr">
+        <is>
+          <t>7702</t>
+        </is>
+      </c>
+      <c r="B2021" s="12" t="inlineStr">
+        <is>
+          <t>Приходи врз основа на камати од други поврзани друштва во земјата</t>
+        </is>
+      </c>
+      <c r="C2021" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2021" s="13" t="inlineStr"/>
+      <c r="E2021" s="13" t="inlineStr"/>
+      <c r="F2021" s="13" t="inlineStr"/>
+    </row>
+    <row r="2022">
+      <c r="A2022" s="11" t="inlineStr">
+        <is>
+          <t>7703</t>
+        </is>
+      </c>
+      <c r="B2022" s="12" t="inlineStr">
+        <is>
+          <t>Приходи врз основа на камати од други поврзани друштва од странство</t>
+        </is>
+      </c>
+      <c r="C2022" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2022" s="13" t="inlineStr"/>
+      <c r="E2022" s="13" t="inlineStr"/>
+      <c r="F2022" s="13" t="inlineStr"/>
+    </row>
+    <row r="2023">
+      <c r="A2023" s="8" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="B2023" s="9" t="inlineStr">
+        <is>
+          <t>Приходи врз основа на позитивни курсни разлики од работењето со поврзани друштва</t>
+        </is>
+      </c>
+      <c r="C2023" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2023" s="10" t="inlineStr"/>
+      <c r="E2023" s="10" t="inlineStr"/>
+      <c r="F2023" s="10" t="inlineStr"/>
+    </row>
+    <row r="2024">
+      <c r="A2024" s="11" t="inlineStr">
+        <is>
+          <t>7710</t>
+        </is>
+      </c>
+      <c r="B2024" s="12" t="inlineStr">
+        <is>
+          <t>Приходи врз основа на позитивни курсни разлики од матични и зависни друштва</t>
+        </is>
+      </c>
+      <c r="C2024" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2024" s="13" t="inlineStr"/>
+      <c r="E2024" s="13" t="inlineStr"/>
+      <c r="F2024" s="13" t="inlineStr"/>
+    </row>
+    <row r="2025">
+      <c r="A2025" s="11" t="inlineStr">
+        <is>
+          <t>7711</t>
+        </is>
+      </c>
+      <c r="B2025" s="12" t="inlineStr">
+        <is>
+          <t>Приходи врз основа на позитивни курсни разлики од други поврзани друштва</t>
+        </is>
+      </c>
+      <c r="C2025" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2025" s="13" t="inlineStr"/>
+      <c r="E2025" s="13" t="inlineStr"/>
+      <c r="F2025" s="13" t="inlineStr"/>
+    </row>
+    <row r="2026">
+      <c r="A2026" s="8" t="inlineStr">
+        <is>
+          <t>772</t>
+        </is>
+      </c>
+      <c r="B2026" s="9" t="inlineStr">
+        <is>
+          <t>Останати финансиски приходи од поврзани друштва</t>
+        </is>
+      </c>
+      <c r="C2026" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2026" s="10" t="inlineStr"/>
+      <c r="E2026" s="10" t="inlineStr"/>
+      <c r="F2026" s="10" t="inlineStr"/>
+    </row>
+    <row r="2027">
+      <c r="A2027" s="11" t="inlineStr">
+        <is>
+          <t>7720</t>
+        </is>
+      </c>
+      <c r="B2027" s="12" t="inlineStr">
+        <is>
+          <t>Останати финансиски приходи од поврзани друштва</t>
+        </is>
+      </c>
+      <c r="C2027" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2027" s="13" t="inlineStr"/>
+      <c r="E2027" s="13" t="inlineStr"/>
+      <c r="F2027" s="13" t="inlineStr"/>
+    </row>
+    <row r="2028">
+      <c r="A2028" s="11" t="inlineStr">
+        <is>
+          <t>77200</t>
+        </is>
+      </c>
+      <c r="B2028" s="12" t="inlineStr">
+        <is>
+          <t>Приходи врз основа на ефекти од валутна клаузула од матични и зависни друштва</t>
+        </is>
+      </c>
+      <c r="C2028" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2028" s="13" t="inlineStr"/>
+      <c r="E2028" s="13" t="inlineStr"/>
+      <c r="F2028" s="13" t="inlineStr"/>
+    </row>
+    <row r="2029">
+      <c r="A2029" s="11" t="inlineStr">
+        <is>
+          <t>77201</t>
+        </is>
+      </c>
+      <c r="B2029" s="12" t="inlineStr">
+        <is>
+          <t>Приходи врз основа на ефекти од валутна клаузула од други поврзани друштва</t>
+        </is>
+      </c>
+      <c r="C2029" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2029" s="13" t="inlineStr"/>
+      <c r="E2029" s="13" t="inlineStr"/>
+      <c r="F2029" s="13" t="inlineStr"/>
+    </row>
+    <row r="2030">
+      <c r="A2030" s="11" t="inlineStr">
+        <is>
+          <t>77202</t>
+        </is>
+      </c>
+      <c r="B2030" s="12" t="inlineStr">
+        <is>
+          <t>Останати финансиски приходи од поврзани друштва</t>
+        </is>
+      </c>
+      <c r="C2030" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2030" s="13" t="inlineStr"/>
+      <c r="E2030" s="13" t="inlineStr"/>
+      <c r="F2030" s="13" t="inlineStr"/>
+    </row>
+    <row r="2031">
+      <c r="A2031" s="8" t="inlineStr">
+        <is>
+          <t>773</t>
+        </is>
+      </c>
+      <c r="B2031" s="9" t="inlineStr">
+        <is>
+          <t>Приходи од вложувања во поврзани друштва</t>
+        </is>
+      </c>
+      <c r="C2031" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2031" s="10" t="inlineStr"/>
+      <c r="E2031" s="10" t="inlineStr"/>
+      <c r="F2031" s="10" t="inlineStr"/>
+    </row>
+    <row r="2032">
+      <c r="A2032" s="11" t="inlineStr">
+        <is>
+          <t>7730</t>
+        </is>
+      </c>
+      <c r="B2032" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од вложувања во поврзани друштва</t>
+        </is>
+      </c>
+      <c r="C2032" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2032" s="13" t="inlineStr"/>
+      <c r="E2032" s="13" t="inlineStr"/>
+      <c r="F2032" s="13" t="inlineStr"/>
+    </row>
+    <row r="2033">
+      <c r="A2033" s="11" t="inlineStr">
+        <is>
+          <t>77300</t>
+        </is>
+      </c>
+      <c r="B2033" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од учество во добивка (дивиденда) или удел во добивката од зависни друштва во земјата</t>
+        </is>
+      </c>
+      <c r="C2033" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2033" s="13" t="inlineStr"/>
+      <c r="E2033" s="13" t="inlineStr"/>
+      <c r="F2033" s="13" t="inlineStr"/>
+    </row>
+    <row r="2034">
+      <c r="A2034" s="11" t="inlineStr">
+        <is>
+          <t>77301</t>
+        </is>
+      </c>
+      <c r="B2034" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од учество во добивка (дивиденда) или удел во добивката од зависни друштва од странство</t>
+        </is>
+      </c>
+      <c r="C2034" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2034" s="13" t="inlineStr"/>
+      <c r="E2034" s="13" t="inlineStr"/>
+      <c r="F2034" s="13" t="inlineStr"/>
+    </row>
+    <row r="2035">
+      <c r="A2035" s="11" t="inlineStr">
+        <is>
+          <t>77302</t>
+        </is>
+      </c>
+      <c r="B2035" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од учество во добивка (дивиденда) или удел во добивката од други поврзани друштва во земјата</t>
+        </is>
+      </c>
+      <c r="C2035" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2035" s="13" t="inlineStr"/>
+      <c r="E2035" s="13" t="inlineStr"/>
+      <c r="F2035" s="13" t="inlineStr"/>
+    </row>
+    <row r="2036">
+      <c r="A2036" s="11" t="inlineStr">
+        <is>
+          <t>77303</t>
+        </is>
+      </c>
+      <c r="B2036" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од учество во добивка (дивиденда) или удел во добивката од други поврзани друштва од странство</t>
+        </is>
+      </c>
+      <c r="C2036" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2036" s="13" t="inlineStr"/>
+      <c r="E2036" s="13" t="inlineStr"/>
+      <c r="F2036" s="13" t="inlineStr"/>
+    </row>
+    <row r="2037">
+      <c r="A2037" s="8" t="inlineStr">
+        <is>
+          <t>774</t>
+        </is>
+      </c>
+      <c r="B2037" s="9" t="inlineStr">
+        <is>
+          <t>Приходи врз основа на камати од работењето со неповрзани друштва</t>
+        </is>
+      </c>
+      <c r="C2037" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2037" s="10" t="inlineStr"/>
+      <c r="E2037" s="10" t="inlineStr"/>
+      <c r="F2037" s="10" t="inlineStr"/>
+    </row>
+    <row r="2038">
+      <c r="A2038" s="11" t="inlineStr">
+        <is>
+          <t>7740</t>
+        </is>
+      </c>
+      <c r="B2038" s="12" t="inlineStr">
+        <is>
+          <t>Приходи врз основа на камати од краткорочни и долгорочни кредити</t>
+        </is>
+      </c>
+      <c r="C2038" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2038" s="13" t="inlineStr"/>
+      <c r="E2038" s="13" t="inlineStr"/>
+      <c r="F2038" s="13" t="inlineStr"/>
+    </row>
+    <row r="2039">
+      <c r="A2039" s="11" t="inlineStr">
+        <is>
+          <t>77400</t>
+        </is>
+      </c>
+      <c r="B2039" s="12" t="inlineStr">
+        <is>
+          <t>Приходи врз основа на камати од краткорочни и долгорочни кредити во земјата</t>
+        </is>
+      </c>
+      <c r="C2039" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2039" s="13" t="inlineStr"/>
+      <c r="E2039" s="13" t="inlineStr"/>
+      <c r="F2039" s="13" t="inlineStr"/>
+    </row>
+    <row r="2040">
+      <c r="A2040" s="11" t="inlineStr">
+        <is>
+          <t>77401</t>
+        </is>
+      </c>
+      <c r="B2040" s="12" t="inlineStr">
+        <is>
+          <t>Приходи врз основа на камати од краткорочни и долгорочни кредити од странство</t>
+        </is>
+      </c>
+      <c r="C2040" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2040" s="13" t="inlineStr"/>
+      <c r="E2040" s="13" t="inlineStr"/>
+      <c r="F2040" s="13" t="inlineStr"/>
+    </row>
+    <row r="2041">
+      <c r="A2041" s="11" t="inlineStr">
+        <is>
+          <t>7741</t>
+        </is>
+      </c>
+      <c r="B2041" s="12" t="inlineStr">
+        <is>
+          <t>Приходи врз основа на камати содржани во издадени меници</t>
+        </is>
+      </c>
+      <c r="C2041" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2041" s="13" t="inlineStr"/>
+      <c r="E2041" s="13" t="inlineStr"/>
+      <c r="F2041" s="13" t="inlineStr"/>
+    </row>
+    <row r="2042">
+      <c r="A2042" s="11" t="inlineStr">
+        <is>
+          <t>7742</t>
+        </is>
+      </c>
+      <c r="B2042" s="12" t="inlineStr">
+        <is>
+          <t>Приходи врз основа на камати во хартии од вредност</t>
+        </is>
+      </c>
+      <c r="C2042" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2042" s="13" t="inlineStr"/>
+      <c r="E2042" s="13" t="inlineStr"/>
+      <c r="F2042" s="13" t="inlineStr"/>
+    </row>
+    <row r="2043">
+      <c r="A2043" s="11" t="inlineStr">
+        <is>
+          <t>7743</t>
+        </is>
+      </c>
+      <c r="B2043" s="12" t="inlineStr">
+        <is>
+          <t>Приходи врз основа на камати од други финансиски пласмани</t>
+        </is>
+      </c>
+      <c r="C2043" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2043" s="13" t="inlineStr"/>
+      <c r="E2043" s="13" t="inlineStr"/>
+      <c r="F2043" s="13" t="inlineStr"/>
+    </row>
+    <row r="2044">
+      <c r="A2044" s="11" t="inlineStr">
+        <is>
+          <t>7744</t>
+        </is>
+      </c>
+      <c r="B2044" s="12" t="inlineStr">
+        <is>
+          <t>Приходи врз основа на камати од купопродажни односи</t>
+        </is>
+      </c>
+      <c r="C2044" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2044" s="13" t="inlineStr"/>
+      <c r="E2044" s="13" t="inlineStr"/>
+      <c r="F2044" s="13" t="inlineStr"/>
+    </row>
+    <row r="2045">
+      <c r="A2045" s="11" t="inlineStr">
+        <is>
+          <t>77440</t>
+        </is>
+      </c>
+      <c r="B2045" s="12" t="inlineStr">
+        <is>
+          <t>Приходи врз основа на камати од купопродажни односи во земјата</t>
+        </is>
+      </c>
+      <c r="C2045" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2045" s="13" t="inlineStr"/>
+      <c r="E2045" s="13" t="inlineStr"/>
+      <c r="F2045" s="13" t="inlineStr"/>
+    </row>
+    <row r="2046">
+      <c r="A2046" s="11" t="inlineStr">
+        <is>
+          <t>77441</t>
+        </is>
+      </c>
+      <c r="B2046" s="12" t="inlineStr">
+        <is>
+          <t>Приходи врз основа на камати од купопродажни односи со странство</t>
+        </is>
+      </c>
+      <c r="C2046" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2046" s="13" t="inlineStr"/>
+      <c r="E2046" s="13" t="inlineStr"/>
+      <c r="F2046" s="13" t="inlineStr"/>
+    </row>
+    <row r="2047">
+      <c r="A2047" s="11" t="inlineStr">
+        <is>
+          <t>7745</t>
+        </is>
+      </c>
+      <c r="B2047" s="12" t="inlineStr">
+        <is>
+          <t>Приходи врз основа на камати од финансиски лизинг</t>
+        </is>
+      </c>
+      <c r="C2047" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2047" s="13" t="inlineStr"/>
+      <c r="E2047" s="13" t="inlineStr"/>
+      <c r="F2047" s="13" t="inlineStr"/>
+    </row>
+    <row r="2048">
+      <c r="A2048" s="11" t="inlineStr">
+        <is>
+          <t>7746</t>
+        </is>
+      </c>
+      <c r="B2048" s="12" t="inlineStr">
+        <is>
+          <t>Казнени камати</t>
+        </is>
+      </c>
+      <c r="C2048" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2048" s="13" t="inlineStr"/>
+      <c r="E2048" s="13" t="inlineStr"/>
+      <c r="F2048" s="13" t="inlineStr"/>
+    </row>
+    <row r="2049">
+      <c r="A2049" s="11" t="inlineStr">
+        <is>
+          <t>77460</t>
+        </is>
+      </c>
+      <c r="B2049" s="12" t="inlineStr">
+        <is>
+          <t>Казнени камати во земјата</t>
+        </is>
+      </c>
+      <c r="C2049" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2049" s="13" t="inlineStr"/>
+      <c r="E2049" s="13" t="inlineStr"/>
+      <c r="F2049" s="13" t="inlineStr"/>
+    </row>
+    <row r="2050">
+      <c r="A2050" s="11" t="inlineStr">
+        <is>
+          <t>77461</t>
+        </is>
+      </c>
+      <c r="B2050" s="12" t="inlineStr">
+        <is>
+          <t>Казнени камати од странство</t>
+        </is>
+      </c>
+      <c r="C2050" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2050" s="13" t="inlineStr"/>
+      <c r="E2050" s="13" t="inlineStr"/>
+      <c r="F2050" s="13" t="inlineStr"/>
+    </row>
+    <row r="2051">
+      <c r="A2051" s="11" t="inlineStr">
+        <is>
+          <t>7749</t>
+        </is>
+      </c>
+      <c r="B2051" s="12" t="inlineStr">
+        <is>
+          <t>Приходи врз основа на останати финансиски побарувања и пласмани</t>
+        </is>
+      </c>
+      <c r="C2051" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2051" s="13" t="inlineStr"/>
+      <c r="E2051" s="13" t="inlineStr"/>
+      <c r="F2051" s="13" t="inlineStr"/>
+    </row>
+    <row r="2052">
+      <c r="A2052" s="8" t="inlineStr">
+        <is>
+          <t>775</t>
+        </is>
+      </c>
+      <c r="B2052" s="9" t="inlineStr">
+        <is>
+          <t>Приходи врз основа на позитивни курсни разлики од работењето со неповрзани друштва</t>
+        </is>
+      </c>
+      <c r="C2052" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2052" s="10" t="inlineStr"/>
+      <c r="E2052" s="10" t="inlineStr"/>
+      <c r="F2052" s="10" t="inlineStr"/>
+    </row>
+    <row r="2053">
+      <c r="A2053" s="11" t="inlineStr">
+        <is>
+          <t>7750</t>
+        </is>
+      </c>
+      <c r="B2053" s="12" t="inlineStr">
+        <is>
+          <t>Позитивни курсни разлики врз основа на побарувања, финансиски обврски и пласмани во странска валута</t>
+        </is>
+      </c>
+      <c r="C2053" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2053" s="13" t="inlineStr"/>
+      <c r="E2053" s="13" t="inlineStr"/>
+      <c r="F2053" s="13" t="inlineStr"/>
+    </row>
+    <row r="2054">
+      <c r="A2054" s="11" t="inlineStr">
+        <is>
+          <t>7751</t>
+        </is>
+      </c>
+      <c r="B2054" s="12" t="inlineStr">
+        <is>
+          <t>Позитивни курсни разлики по финансиски пласмани, побарувања и обврски во странска валута на денот на составување на Извештајот за финансиската состојба</t>
+        </is>
+      </c>
+      <c r="C2054" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2054" s="13" t="inlineStr"/>
+      <c r="E2054" s="13" t="inlineStr"/>
+      <c r="F2054" s="13" t="inlineStr"/>
+    </row>
+    <row r="2055">
+      <c r="A2055" s="11" t="inlineStr">
+        <is>
+          <t>7752</t>
+        </is>
+      </c>
+      <c r="B2055" s="12" t="inlineStr">
+        <is>
+          <t>Позитивни курсни разлики пресметани по среден курс на НБРМ на парични средства во странска валута (девизна сметка, девизна благајна, хартии од вредност, готовински еквиваленти)</t>
+        </is>
+      </c>
+      <c r="C2055" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2055" s="13" t="inlineStr"/>
+      <c r="E2055" s="13" t="inlineStr"/>
+      <c r="F2055" s="13" t="inlineStr"/>
+    </row>
+    <row r="2056">
+      <c r="A2056" s="11" t="inlineStr">
+        <is>
+          <t>7759</t>
+        </is>
+      </c>
+      <c r="B2056" s="12" t="inlineStr">
+        <is>
+          <t>Останати курсни разлики</t>
+        </is>
+      </c>
+      <c r="C2056" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2056" s="13" t="inlineStr"/>
+      <c r="E2056" s="13" t="inlineStr"/>
+      <c r="F2056" s="13" t="inlineStr"/>
+    </row>
+    <row r="2057">
+      <c r="A2057" s="8" t="inlineStr">
+        <is>
+          <t>776</t>
+        </is>
+      </c>
+      <c r="B2057" s="9" t="inlineStr">
+        <is>
+          <t>Приходи од вложувања во неповрзани друштва</t>
+        </is>
+      </c>
+      <c r="C2057" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2057" s="10" t="inlineStr"/>
+      <c r="E2057" s="10" t="inlineStr"/>
+      <c r="F2057" s="10" t="inlineStr"/>
+    </row>
+    <row r="2058">
+      <c r="A2058" s="11" t="inlineStr">
+        <is>
+          <t>7760</t>
+        </is>
+      </c>
+      <c r="B2058" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од дивиденди или удел во добивката од неповрзани друштва</t>
+        </is>
+      </c>
+      <c r="C2058" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2058" s="13" t="inlineStr"/>
+      <c r="E2058" s="13" t="inlineStr"/>
+      <c r="F2058" s="13" t="inlineStr"/>
+    </row>
+    <row r="2059">
+      <c r="A2059" s="11" t="inlineStr">
+        <is>
+          <t>7761</t>
+        </is>
+      </c>
+      <c r="B2059" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од учество во инвестициони фондови во земјата и странство</t>
+        </is>
+      </c>
+      <c r="C2059" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2059" s="13" t="inlineStr"/>
+      <c r="E2059" s="13" t="inlineStr"/>
+      <c r="F2059" s="13" t="inlineStr"/>
+    </row>
+    <row r="2060">
+      <c r="A2060" s="11" t="inlineStr">
+        <is>
+          <t>7762</t>
+        </is>
+      </c>
+      <c r="B2060" s="12" t="inlineStr">
+        <is>
+          <t>Останати финансиски приходи од неповрзани друштва</t>
+        </is>
+      </c>
+      <c r="C2060" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2060" s="13" t="inlineStr"/>
+      <c r="E2060" s="13" t="inlineStr"/>
+      <c r="F2060" s="13" t="inlineStr"/>
+    </row>
+    <row r="2061">
+      <c r="A2061" s="8" t="inlineStr">
+        <is>
+          <t>777</t>
+        </is>
+      </c>
+      <c r="B2061" s="9" t="inlineStr">
+        <is>
+          <t>Нереализирани добивки (приходи) од финансиски средства</t>
+        </is>
+      </c>
+      <c r="C2061" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2061" s="10" t="inlineStr"/>
+      <c r="E2061" s="10" t="inlineStr"/>
+      <c r="F2061" s="10" t="inlineStr"/>
+    </row>
+    <row r="2062">
+      <c r="A2062" s="11" t="inlineStr">
+        <is>
+          <t>7770</t>
+        </is>
+      </c>
+      <c r="B2062" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од вредносно усогласување на хартии од вредност кои се чуваат за трговање</t>
+        </is>
+      </c>
+      <c r="C2062" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2062" s="13" t="inlineStr"/>
+      <c r="E2062" s="13" t="inlineStr"/>
+      <c r="F2062" s="13" t="inlineStr"/>
+    </row>
+    <row r="2063">
+      <c r="A2063" s="11" t="inlineStr">
+        <is>
+          <t>7771</t>
+        </is>
+      </c>
+      <c r="B2063" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од вредносно усогласување на долгорочни финансиски пласмани и други хартии од вредност расположиви за продажба</t>
+        </is>
+      </c>
+      <c r="C2063" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2063" s="13" t="inlineStr"/>
+      <c r="E2063" s="13" t="inlineStr"/>
+      <c r="F2063" s="13" t="inlineStr"/>
+    </row>
+    <row r="2064">
+      <c r="A2064" s="11" t="inlineStr">
+        <is>
+          <t>7779</t>
+        </is>
+      </c>
+      <c r="B2064" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од други останати финансиски средства</t>
+        </is>
+      </c>
+      <c r="C2064" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2064" s="13" t="inlineStr"/>
+      <c r="E2064" s="13" t="inlineStr"/>
+      <c r="F2064" s="13" t="inlineStr"/>
+    </row>
+    <row r="2065">
+      <c r="A2065" s="8" t="inlineStr">
+        <is>
+          <t>779</t>
+        </is>
+      </c>
+      <c r="B2065" s="9" t="inlineStr">
+        <is>
+          <t>Останати финансиски приходи</t>
+        </is>
+      </c>
+      <c r="C2065" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2065" s="10" t="inlineStr"/>
+      <c r="E2065" s="10" t="inlineStr"/>
+      <c r="F2065" s="10" t="inlineStr"/>
+    </row>
+    <row r="2066">
+      <c r="A2066" s="11" t="inlineStr">
+        <is>
+          <t>7790</t>
+        </is>
+      </c>
+      <c r="B2066" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од ефекти од валутна клаузула врз основа на побарувања</t>
+        </is>
+      </c>
+      <c r="C2066" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2066" s="13" t="inlineStr"/>
+      <c r="E2066" s="13" t="inlineStr"/>
+      <c r="F2066" s="13" t="inlineStr"/>
+    </row>
+    <row r="2067">
+      <c r="A2067" s="11" t="inlineStr">
+        <is>
+          <t>7791</t>
+        </is>
+      </c>
+      <c r="B2067" s="12" t="inlineStr">
+        <is>
+          <t>Приходи врз основа на есконтирање на чекови и меници</t>
+        </is>
+      </c>
+      <c r="C2067" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2067" s="13" t="inlineStr"/>
+      <c r="E2067" s="13" t="inlineStr"/>
+      <c r="F2067" s="13" t="inlineStr"/>
+    </row>
+    <row r="2068">
+      <c r="A2068" s="11" t="inlineStr">
+        <is>
+          <t>7792</t>
+        </is>
+      </c>
+      <c r="B2068" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од факторинг и слично</t>
+        </is>
+      </c>
+      <c r="C2068" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2068" s="13" t="inlineStr"/>
+      <c r="E2068" s="13" t="inlineStr"/>
+      <c r="F2068" s="13" t="inlineStr"/>
+    </row>
+    <row r="2069">
+      <c r="A2069" s="11" t="inlineStr">
+        <is>
+          <t>7793</t>
+        </is>
+      </c>
+      <c r="B2069" s="12" t="inlineStr">
+        <is>
+          <t>Приходи од берзански услуги, емисија на хартии од вредност и слично</t>
+        </is>
+      </c>
+      <c r="C2069" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2069" s="13" t="inlineStr"/>
+      <c r="E2069" s="13" t="inlineStr"/>
+      <c r="F2069" s="13" t="inlineStr"/>
+    </row>
+    <row r="2070">
+      <c r="A2070" s="11" t="inlineStr">
+        <is>
+          <t>7799</t>
+        </is>
+      </c>
+      <c r="B2070" s="12" t="inlineStr">
+        <is>
+          <t>Останати финансиски приходи</t>
+        </is>
+      </c>
+      <c r="C2070" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2070" s="13" t="inlineStr"/>
+      <c r="E2070" s="13" t="inlineStr"/>
+      <c r="F2070" s="13" t="inlineStr"/>
+    </row>
+    <row r="2071">
+      <c r="A2071" s="5" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="B2071" s="6" t="inlineStr">
+        <is>
+          <t>УДЕЛ ВО ДОБИВКАТА НА ПРИДРУЖНО ДРУШТВО И НЕТО ДОБИВКА ОД ПРЕКИНАТО РАБОТЕЊЕ</t>
+        </is>
+      </c>
+      <c r="C2071" s="7" t="inlineStr">
+        <is>
+          <t>Група</t>
+        </is>
+      </c>
+      <c r="D2071" s="7" t="inlineStr"/>
+      <c r="E2071" s="7" t="inlineStr"/>
+      <c r="F2071" s="7" t="inlineStr"/>
+    </row>
+    <row r="2072">
+      <c r="A2072" s="8" t="inlineStr">
+        <is>
+          <t>780</t>
+        </is>
+      </c>
+      <c r="B2072" s="9" t="inlineStr">
+        <is>
+          <t>Удел во добивката на придружно друштво</t>
+        </is>
+      </c>
+      <c r="C2072" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2072" s="10" t="inlineStr"/>
+      <c r="E2072" s="10" t="inlineStr"/>
+      <c r="F2072" s="10" t="inlineStr"/>
+    </row>
+    <row r="2073">
+      <c r="A2073" s="8" t="inlineStr">
+        <is>
+          <t>781</t>
+        </is>
+      </c>
+      <c r="B2073" s="9" t="inlineStr">
+        <is>
+          <t>Нето добивка од прекинато работење</t>
+        </is>
+      </c>
+      <c r="C2073" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2073" s="10" t="inlineStr"/>
+      <c r="E2073" s="10" t="inlineStr"/>
+      <c r="F2073" s="10" t="inlineStr"/>
+    </row>
+    <row r="2074">
+      <c r="A2074" s="5" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="B2074" s="6" t="inlineStr">
+        <is>
+          <t>РАЗЛИКА НА ПРИХОДИ И РАСХОДИ</t>
+        </is>
+      </c>
+      <c r="C2074" s="7" t="inlineStr">
+        <is>
+          <t>Група</t>
+        </is>
+      </c>
+      <c r="D2074" s="7" t="inlineStr"/>
+      <c r="E2074" s="7" t="inlineStr"/>
+      <c r="F2074" s="7" t="inlineStr"/>
+    </row>
+    <row r="2075">
+      <c r="A2075" s="8" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="B2075" s="9" t="inlineStr">
+        <is>
+          <t>Разлика на приходи и расходи од вкупното работење</t>
+        </is>
+      </c>
+      <c r="C2075" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2075" s="10" t="inlineStr"/>
+      <c r="E2075" s="10" t="inlineStr"/>
+      <c r="F2075" s="10" t="inlineStr"/>
+    </row>
+    <row r="2076">
+      <c r="A2076" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B2076" s="3" t="inlineStr">
+        <is>
+          <t>РЕЗУЛТАТИ ОД РАБОТЕЊЕТО</t>
+        </is>
+      </c>
+      <c r="C2076" s="4" t="inlineStr">
+        <is>
+          <t>Класа</t>
+        </is>
+      </c>
+      <c r="D2076" s="4" t="inlineStr"/>
+      <c r="E2076" s="4" t="inlineStr"/>
+      <c r="F2076" s="4" t="inlineStr"/>
+    </row>
+    <row r="2077">
+      <c r="A2077" s="5" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B2077" s="6" t="inlineStr">
+        <is>
+          <t>ДОБИВКА/ЗАГУБА ПРЕД ОДАНОЧУВАЊЕ</t>
+        </is>
+      </c>
+      <c r="C2077" s="7" t="inlineStr">
+        <is>
+          <t>Група</t>
+        </is>
+      </c>
+      <c r="D2077" s="7" t="inlineStr"/>
+      <c r="E2077" s="7" t="inlineStr"/>
+      <c r="F2077" s="7" t="inlineStr"/>
+    </row>
+    <row r="2078">
+      <c r="A2078" s="8" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="B2078" s="9" t="inlineStr">
+        <is>
+          <t>Добивка пред оданочување</t>
+        </is>
+      </c>
+      <c r="C2078" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2078" s="10" t="inlineStr"/>
+      <c r="E2078" s="10" t="inlineStr"/>
+      <c r="F2078" s="10" t="inlineStr"/>
+    </row>
+    <row r="2079">
+      <c r="A2079" s="8" t="inlineStr">
+        <is>
+          <t>801</t>
+        </is>
+      </c>
+      <c r="B2079" s="9" t="inlineStr">
+        <is>
+          <t>Загуба пред оданочување</t>
+        </is>
+      </c>
+      <c r="C2079" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2079" s="10" t="inlineStr"/>
+      <c r="E2079" s="10" t="inlineStr"/>
+      <c r="F2079" s="10" t="inlineStr"/>
+    </row>
+    <row r="2080">
+      <c r="A2080" s="5" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="B2080" s="6" t="inlineStr">
+        <is>
+          <t>ДАНОК НА ДОБИВКА И ДРУГИ ДАВАЧКИ</t>
+        </is>
+      </c>
+      <c r="C2080" s="7" t="inlineStr">
+        <is>
+          <t>Група</t>
+        </is>
+      </c>
+      <c r="D2080" s="7" t="inlineStr"/>
+      <c r="E2080" s="7" t="inlineStr"/>
+      <c r="F2080" s="7" t="inlineStr"/>
+    </row>
+    <row r="2081">
+      <c r="A2081" s="8" t="inlineStr">
+        <is>
+          <t>810</t>
+        </is>
+      </c>
+      <c r="B2081" s="9" t="inlineStr">
+        <is>
+          <t>Данок на добивка</t>
+        </is>
+      </c>
+      <c r="C2081" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2081" s="10" t="inlineStr"/>
+      <c r="E2081" s="10" t="inlineStr"/>
+      <c r="F2081" s="10" t="inlineStr"/>
+    </row>
+    <row r="2082">
+      <c r="A2082" s="8" t="inlineStr">
+        <is>
+          <t>811</t>
+        </is>
+      </c>
+      <c r="B2082" s="9" t="inlineStr">
+        <is>
+          <t>Одложени даночни приходи</t>
+        </is>
+      </c>
+      <c r="C2082" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2082" s="10" t="inlineStr"/>
+      <c r="E2082" s="10" t="inlineStr"/>
+      <c r="F2082" s="10" t="inlineStr"/>
+    </row>
+    <row r="2083">
+      <c r="A2083" s="8" t="inlineStr">
+        <is>
+          <t>812</t>
+        </is>
+      </c>
+      <c r="B2083" s="9" t="inlineStr">
+        <is>
+          <t>Одложени даночни расходи</t>
+        </is>
+      </c>
+      <c r="C2083" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2083" s="10" t="inlineStr"/>
+      <c r="E2083" s="10" t="inlineStr"/>
+      <c r="F2083" s="10" t="inlineStr"/>
+    </row>
+    <row r="2084">
+      <c r="A2084" s="8" t="inlineStr">
+        <is>
+          <t>813</t>
+        </is>
+      </c>
+      <c r="B2084" s="9" t="inlineStr">
+        <is>
+          <t>Други давачки</t>
+        </is>
+      </c>
+      <c r="C2084" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2084" s="10" t="inlineStr"/>
+      <c r="E2084" s="10" t="inlineStr"/>
+      <c r="F2084" s="10" t="inlineStr"/>
+    </row>
+    <row r="2085">
+      <c r="A2085" s="5" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="B2085" s="6" t="inlineStr">
+        <is>
+          <t>НЕТО ДОБИВКА/ЗАГУБА ЗА ПЕРИОДОТ</t>
+        </is>
+      </c>
+      <c r="C2085" s="7" t="inlineStr">
+        <is>
+          <t>Група</t>
+        </is>
+      </c>
+      <c r="D2085" s="7" t="inlineStr"/>
+      <c r="E2085" s="7" t="inlineStr"/>
+      <c r="F2085" s="7" t="inlineStr"/>
+    </row>
+    <row r="2086">
+      <c r="A2086" s="8" t="inlineStr">
+        <is>
+          <t>820</t>
+        </is>
+      </c>
+      <c r="B2086" s="9" t="inlineStr">
+        <is>
+          <t>Нето добивка за периодот</t>
+        </is>
+      </c>
+      <c r="C2086" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2086" s="10" t="inlineStr"/>
+      <c r="E2086" s="10" t="inlineStr"/>
+      <c r="F2086" s="10" t="inlineStr"/>
+    </row>
+    <row r="2087">
+      <c r="A2087" s="11" t="inlineStr">
+        <is>
+          <t>8200</t>
+        </is>
+      </c>
+      <c r="B2087" s="12" t="inlineStr"/>
+      <c r="C2087" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2087" s="13" t="inlineStr"/>
+      <c r="E2087" s="13" t="inlineStr"/>
+      <c r="F2087" s="13" t="inlineStr"/>
+    </row>
+    <row r="2088">
+      <c r="A2088" s="8" t="inlineStr">
+        <is>
+          <t>821</t>
+        </is>
+      </c>
+      <c r="B2088" s="9" t="inlineStr">
+        <is>
+          <t>Нето загуба за периодот</t>
+        </is>
+      </c>
+      <c r="C2088" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2088" s="10" t="inlineStr"/>
+      <c r="E2088" s="10" t="inlineStr"/>
+      <c r="F2088" s="10" t="inlineStr"/>
+    </row>
+    <row r="2089">
+      <c r="A2089" s="5" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="B2089" s="6" t="inlineStr">
+        <is>
+          <t>ДОБИВКА/ЗАГУБА ЗА ПЕРИОДОТ КОЈА ПРИПАЃА НА ДРУГИ</t>
+        </is>
+      </c>
+      <c r="C2089" s="7" t="inlineStr">
+        <is>
+          <t>Група</t>
+        </is>
+      </c>
+      <c r="D2089" s="7" t="inlineStr"/>
+      <c r="E2089" s="7" t="inlineStr"/>
+      <c r="F2089" s="7" t="inlineStr"/>
+    </row>
+    <row r="2090">
+      <c r="A2090" s="8" t="inlineStr">
+        <is>
+          <t>830</t>
+        </is>
+      </c>
+      <c r="B2090" s="9" t="inlineStr">
+        <is>
+          <t>Добивка која припаѓа на сопствениците на матичното друштво</t>
+        </is>
+      </c>
+      <c r="C2090" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2090" s="10" t="inlineStr"/>
+      <c r="E2090" s="10" t="inlineStr"/>
+      <c r="F2090" s="10" t="inlineStr"/>
+    </row>
+    <row r="2091">
+      <c r="A2091" s="8" t="inlineStr">
+        <is>
+          <t>831</t>
+        </is>
+      </c>
+      <c r="B2091" s="9" t="inlineStr">
+        <is>
+          <t>Добивка која припаѓа на учество кое нема контрола</t>
+        </is>
+      </c>
+      <c r="C2091" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2091" s="10" t="inlineStr"/>
+      <c r="E2091" s="10" t="inlineStr"/>
+      <c r="F2091" s="10" t="inlineStr"/>
+    </row>
+    <row r="2092">
+      <c r="A2092" s="8" t="inlineStr">
+        <is>
+          <t>832</t>
+        </is>
+      </c>
+      <c r="B2092" s="9" t="inlineStr">
+        <is>
+          <t>Загуба која припаѓа на сопствениците на матичното друштво</t>
+        </is>
+      </c>
+      <c r="C2092" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2092" s="10" t="inlineStr"/>
+      <c r="E2092" s="10" t="inlineStr"/>
+      <c r="F2092" s="10" t="inlineStr"/>
+    </row>
+    <row r="2093">
+      <c r="A2093" s="8" t="inlineStr">
+        <is>
+          <t>833</t>
+        </is>
+      </c>
+      <c r="B2093" s="9" t="inlineStr">
+        <is>
+          <t>Загуба која припаѓа на учество кое нема контрола</t>
+        </is>
+      </c>
+      <c r="C2093" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2093" s="10" t="inlineStr"/>
+      <c r="E2093" s="10" t="inlineStr"/>
+      <c r="F2093" s="10" t="inlineStr"/>
+    </row>
+    <row r="2094">
+      <c r="A2094" s="5" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="B2094" s="6" t="inlineStr">
+        <is>
+          <t>ОСТАНАТА СЕОПФАТНА ДОБИВКА/ЗАГУБА</t>
+        </is>
+      </c>
+      <c r="C2094" s="7" t="inlineStr">
+        <is>
+          <t>Група</t>
+        </is>
+      </c>
+      <c r="D2094" s="7" t="inlineStr"/>
+      <c r="E2094" s="7" t="inlineStr"/>
+      <c r="F2094" s="7" t="inlineStr"/>
+    </row>
+    <row r="2095">
+      <c r="A2095" s="8" t="inlineStr">
+        <is>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="B2095" s="9" t="inlineStr">
+        <is>
+          <t>Добивка која произлегува од преведување на странско работење</t>
+        </is>
+      </c>
+      <c r="C2095" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2095" s="10" t="inlineStr"/>
+      <c r="E2095" s="10" t="inlineStr"/>
+      <c r="F2095" s="10" t="inlineStr"/>
+    </row>
+    <row r="2096">
+      <c r="A2096" s="8" t="inlineStr">
+        <is>
+          <t>841</t>
+        </is>
+      </c>
+      <c r="B2096" s="9" t="inlineStr">
+        <is>
+          <t>Загуба која произлегува од преведување на странско работење</t>
+        </is>
+      </c>
+      <c r="C2096" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2096" s="10" t="inlineStr"/>
+      <c r="E2096" s="10" t="inlineStr"/>
+      <c r="F2096" s="10" t="inlineStr"/>
+    </row>
+    <row r="2097">
+      <c r="A2097" s="8" t="inlineStr">
+        <is>
+          <t>842</t>
+        </is>
+      </c>
+      <c r="B2097" s="9" t="inlineStr">
+        <is>
+          <t>Добивка од повторно мерење на финансиски средства расположиви за продажба</t>
+        </is>
+      </c>
+      <c r="C2097" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2097" s="10" t="inlineStr"/>
+      <c r="E2097" s="10" t="inlineStr"/>
+      <c r="F2097" s="10" t="inlineStr"/>
+    </row>
+    <row r="2098">
+      <c r="A2098" s="8" t="inlineStr">
+        <is>
+          <t>843</t>
+        </is>
+      </c>
+      <c r="B2098" s="9" t="inlineStr">
+        <is>
+          <t>Загуба од повторно мерење на финансиски средства расположиви за продажба</t>
+        </is>
+      </c>
+      <c r="C2098" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2098" s="10" t="inlineStr"/>
+      <c r="E2098" s="10" t="inlineStr"/>
+      <c r="F2098" s="10" t="inlineStr"/>
+    </row>
+    <row r="2099">
+      <c r="A2099" s="8" t="inlineStr">
+        <is>
+          <t>844</t>
+        </is>
+      </c>
+      <c r="B2099" s="9" t="inlineStr">
+        <is>
+          <t>Добивка од ефектот од хеџинг инструменти за хеџирање на парични текови</t>
+        </is>
+      </c>
+      <c r="C2099" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2099" s="10" t="inlineStr"/>
+      <c r="E2099" s="10" t="inlineStr"/>
+      <c r="F2099" s="10" t="inlineStr"/>
+    </row>
+    <row r="2100">
+      <c r="A2100" s="8" t="inlineStr">
+        <is>
+          <t>845</t>
+        </is>
+      </c>
+      <c r="B2100" s="9" t="inlineStr">
+        <is>
+          <t>Загуба од ефектот од хеџинг инструменти за хеџирање на парични текови</t>
+        </is>
+      </c>
+      <c r="C2100" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2100" s="10" t="inlineStr"/>
+      <c r="E2100" s="10" t="inlineStr"/>
+      <c r="F2100" s="10" t="inlineStr"/>
+    </row>
+    <row r="2101">
+      <c r="A2101" s="8" t="inlineStr">
+        <is>
+          <t>846</t>
+        </is>
+      </c>
+      <c r="B2101" s="9" t="inlineStr">
+        <is>
+          <t>Позитивни ефекти од ревалоризација на нематеријалните и материјалните средства</t>
+        </is>
+      </c>
+      <c r="C2101" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2101" s="10" t="inlineStr"/>
+      <c r="E2101" s="10" t="inlineStr"/>
+      <c r="F2101" s="10" t="inlineStr"/>
+    </row>
+    <row r="2102">
+      <c r="A2102" s="8" t="inlineStr">
+        <is>
+          <t>847</t>
+        </is>
+      </c>
+      <c r="B2102" s="9" t="inlineStr">
+        <is>
+          <t>Негативни ефекти од ревалоризација на нематеријалните и материјалните средства</t>
+        </is>
+      </c>
+      <c r="C2102" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2102" s="10" t="inlineStr"/>
+      <c r="E2102" s="10" t="inlineStr"/>
+      <c r="F2102" s="10" t="inlineStr"/>
+    </row>
+    <row r="2103">
+      <c r="A2103" s="8" t="inlineStr">
+        <is>
+          <t>848</t>
+        </is>
+      </c>
+      <c r="B2103" s="9" t="inlineStr">
+        <is>
+          <t>Актуарски добивки на дефинирани планови за користи на вработените</t>
+        </is>
+      </c>
+      <c r="C2103" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2103" s="10" t="inlineStr"/>
+      <c r="E2103" s="10" t="inlineStr"/>
+      <c r="F2103" s="10" t="inlineStr"/>
+    </row>
+    <row r="2104">
+      <c r="A2104" s="8" t="inlineStr">
+        <is>
+          <t>849</t>
+        </is>
+      </c>
+      <c r="B2104" s="9" t="inlineStr">
+        <is>
+          <t>Актуарски загуби на дефинирани планови за користи на вработените</t>
+        </is>
+      </c>
+      <c r="C2104" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2104" s="10" t="inlineStr"/>
+      <c r="E2104" s="10" t="inlineStr"/>
+      <c r="F2104" s="10" t="inlineStr"/>
+    </row>
+    <row r="2105">
+      <c r="A2105" s="5" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="B2105" s="6" t="inlineStr">
+        <is>
+          <t>УДЕЛ ВО ОСТАНАТА СЕОПФАТНА ДОБИВКА/ ЗАГУБА НА ПРИДРУЖНИ ДРУШТВА (САМО ЗА ПОТРЕБИТЕ НА КОНСОЛИДАЦИЈА)</t>
+        </is>
+      </c>
+      <c r="C2105" s="7" t="inlineStr">
+        <is>
+          <t>Група</t>
+        </is>
+      </c>
+      <c r="D2105" s="7" t="inlineStr"/>
+      <c r="E2105" s="7" t="inlineStr"/>
+      <c r="F2105" s="7" t="inlineStr"/>
+    </row>
+    <row r="2106">
+      <c r="A2106" s="8" t="inlineStr">
+        <is>
+          <t>850</t>
+        </is>
+      </c>
+      <c r="B2106" s="9" t="inlineStr">
+        <is>
+          <t>Удел во останата сеопфатна добивка на придружни друштва</t>
+        </is>
+      </c>
+      <c r="C2106" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2106" s="10" t="inlineStr"/>
+      <c r="E2106" s="10" t="inlineStr"/>
+      <c r="F2106" s="10" t="inlineStr"/>
+    </row>
+    <row r="2107">
+      <c r="A2107" s="8" t="inlineStr">
+        <is>
+          <t>851</t>
+        </is>
+      </c>
+      <c r="B2107" s="9" t="inlineStr">
+        <is>
+          <t>Удел во останата сеопфатна загуба на придружни друштва</t>
+        </is>
+      </c>
+      <c r="C2107" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2107" s="10" t="inlineStr"/>
+      <c r="E2107" s="10" t="inlineStr"/>
+      <c r="F2107" s="10" t="inlineStr"/>
+    </row>
+    <row r="2108">
+      <c r="A2108" s="5" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="B2108" s="6" t="inlineStr">
+        <is>
+          <t>ДАНОК НА ДОБИВКА НА КОМПОНЕНТИ НА ОСТАНАТА СЕОПФАТНА ДОБИВКА</t>
+        </is>
+      </c>
+      <c r="C2108" s="7" t="inlineStr">
+        <is>
+          <t>Група</t>
+        </is>
+      </c>
+      <c r="D2108" s="7" t="inlineStr"/>
+      <c r="E2108" s="7" t="inlineStr"/>
+      <c r="F2108" s="7" t="inlineStr"/>
+    </row>
+    <row r="2109">
+      <c r="A2109" s="8" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="B2109" s="9" t="inlineStr">
+        <is>
+          <t>Данок на добивка на компоненти на останата сеопфатна добивка</t>
+        </is>
+      </c>
+      <c r="C2109" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2109" s="10" t="inlineStr"/>
+      <c r="E2109" s="10" t="inlineStr"/>
+      <c r="F2109" s="10" t="inlineStr"/>
+    </row>
+    <row r="2110">
+      <c r="A2110" s="5" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="B2110" s="6" t="inlineStr">
+        <is>
+          <t>НЕТО ОСТАНАТА СЕОПФАТНА ДОБИВКА/ЗАГУБА</t>
+        </is>
+      </c>
+      <c r="C2110" s="7" t="inlineStr">
+        <is>
+          <t>Група</t>
+        </is>
+      </c>
+      <c r="D2110" s="7" t="inlineStr"/>
+      <c r="E2110" s="7" t="inlineStr"/>
+      <c r="F2110" s="7" t="inlineStr"/>
+    </row>
+    <row r="2111">
+      <c r="A2111" s="8" t="inlineStr">
+        <is>
+          <t>870</t>
+        </is>
+      </c>
+      <c r="B2111" s="9" t="inlineStr">
+        <is>
+          <t>Нето останата сеопфатна добивка</t>
+        </is>
+      </c>
+      <c r="C2111" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2111" s="10" t="inlineStr"/>
+      <c r="E2111" s="10" t="inlineStr"/>
+      <c r="F2111" s="10" t="inlineStr"/>
+    </row>
+    <row r="2112">
+      <c r="A2112" s="8" t="inlineStr">
+        <is>
+          <t>871</t>
+        </is>
+      </c>
+      <c r="B2112" s="9" t="inlineStr">
+        <is>
+          <t>Нето останата сеопфатна загуба</t>
+        </is>
+      </c>
+      <c r="C2112" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2112" s="10" t="inlineStr"/>
+      <c r="E2112" s="10" t="inlineStr"/>
+      <c r="F2112" s="10" t="inlineStr"/>
+    </row>
+    <row r="2113">
+      <c r="A2113" s="5" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="B2113" s="6" t="inlineStr">
+        <is>
+          <t>ВКУПНА СЕОПФАТНА ДОБИВКА/ЗАГУБА ЗА ПЕРИОДОТ</t>
+        </is>
+      </c>
+      <c r="C2113" s="7" t="inlineStr">
+        <is>
+          <t>Група</t>
+        </is>
+      </c>
+      <c r="D2113" s="7" t="inlineStr"/>
+      <c r="E2113" s="7" t="inlineStr"/>
+      <c r="F2113" s="7" t="inlineStr"/>
+    </row>
+    <row r="2114">
+      <c r="A2114" s="8" t="inlineStr">
+        <is>
+          <t>880</t>
+        </is>
+      </c>
+      <c r="B2114" s="9" t="inlineStr">
+        <is>
+          <t>Сеопфатна добивка која им припаѓа на сопствениците на матичното друштво</t>
+        </is>
+      </c>
+      <c r="C2114" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2114" s="10" t="inlineStr"/>
+      <c r="E2114" s="10" t="inlineStr"/>
+      <c r="F2114" s="10" t="inlineStr"/>
+    </row>
+    <row r="2115">
+      <c r="A2115" s="8" t="inlineStr">
+        <is>
+          <t>881</t>
+        </is>
+      </c>
+      <c r="B2115" s="9" t="inlineStr">
+        <is>
+          <t>Сеопфатна добивка која им припаѓа на учество кое нема контрола</t>
+        </is>
+      </c>
+      <c r="C2115" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2115" s="10" t="inlineStr"/>
+      <c r="E2115" s="10" t="inlineStr"/>
+      <c r="F2115" s="10" t="inlineStr"/>
+    </row>
+    <row r="2116">
+      <c r="A2116" s="8" t="inlineStr">
+        <is>
+          <t>882</t>
+        </is>
+      </c>
+      <c r="B2116" s="9" t="inlineStr">
+        <is>
+          <t>Сеопфатна загуба која им припаѓа на сопствениците на матичното друштво</t>
+        </is>
+      </c>
+      <c r="C2116" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2116" s="10" t="inlineStr"/>
+      <c r="E2116" s="10" t="inlineStr"/>
+      <c r="F2116" s="10" t="inlineStr"/>
+    </row>
+    <row r="2117">
+      <c r="A2117" s="8" t="inlineStr">
+        <is>
+          <t>883</t>
+        </is>
+      </c>
+      <c r="B2117" s="9" t="inlineStr">
+        <is>
+          <t>Сеопфатна загуба која им припаѓа на учество кое нема контрола</t>
+        </is>
+      </c>
+      <c r="C2117" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2117" s="10" t="inlineStr"/>
+      <c r="E2117" s="10" t="inlineStr"/>
+      <c r="F2117" s="10" t="inlineStr"/>
+    </row>
+    <row r="2118">
+      <c r="A2118" s="5" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="B2118" s="6" t="inlineStr">
+        <is>
+          <t>РАСПОРЕДУВАЊЕ НА ДОБИВКАТА</t>
+        </is>
+      </c>
+      <c r="C2118" s="7" t="inlineStr">
+        <is>
+          <t>Група</t>
+        </is>
+      </c>
+      <c r="D2118" s="7" t="inlineStr"/>
+      <c r="E2118" s="7" t="inlineStr"/>
+      <c r="F2118" s="7" t="inlineStr"/>
+    </row>
+    <row r="2119">
+      <c r="A2119" s="8" t="inlineStr">
+        <is>
+          <t>890</t>
+        </is>
+      </c>
+      <c r="B2119" s="9" t="inlineStr">
+        <is>
+          <t>Покривање на загубата од претходни години</t>
+        </is>
+      </c>
+      <c r="C2119" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2119" s="10" t="inlineStr"/>
+      <c r="E2119" s="10" t="inlineStr"/>
+      <c r="F2119" s="10" t="inlineStr"/>
+    </row>
+    <row r="2120">
+      <c r="A2120" s="8" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="B2120" s="9" t="inlineStr">
+        <is>
+          <t>Зголемување на капиталот (капитал на сопствениците)</t>
+        </is>
+      </c>
+      <c r="C2120" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2120" s="10" t="inlineStr"/>
+      <c r="E2120" s="10" t="inlineStr"/>
+      <c r="F2120" s="10" t="inlineStr"/>
+    </row>
+    <row r="2121">
+      <c r="A2121" s="8" t="inlineStr">
+        <is>
+          <t>892</t>
+        </is>
+      </c>
+      <c r="B2121" s="9" t="inlineStr">
+        <is>
+          <t>Дивиденди или удел во добивката и друго</t>
+        </is>
+      </c>
+      <c r="C2121" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2121" s="10" t="inlineStr"/>
+      <c r="E2121" s="10" t="inlineStr"/>
+      <c r="F2121" s="10" t="inlineStr"/>
+    </row>
+    <row r="2122">
+      <c r="A2122" s="11" t="inlineStr">
+        <is>
+          <t>8920</t>
+        </is>
+      </c>
+      <c r="B2122" s="12" t="inlineStr">
+        <is>
+          <t>Дивиденди или удел во добивката на домашни правни лица</t>
+        </is>
+      </c>
+      <c r="C2122" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2122" s="13" t="inlineStr"/>
+      <c r="E2122" s="13" t="inlineStr"/>
+      <c r="F2122" s="13" t="inlineStr"/>
+    </row>
+    <row r="2123">
+      <c r="A2123" s="11" t="inlineStr">
+        <is>
+          <t>8921</t>
+        </is>
+      </c>
+      <c r="B2123" s="12" t="inlineStr">
+        <is>
+          <t>Дивиденди или удел во добивката на странски правни лица</t>
+        </is>
+      </c>
+      <c r="C2123" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2123" s="13" t="inlineStr"/>
+      <c r="E2123" s="13" t="inlineStr"/>
+      <c r="F2123" s="13" t="inlineStr"/>
+    </row>
+    <row r="2124">
+      <c r="A2124" s="11" t="inlineStr">
+        <is>
+          <t>8922</t>
+        </is>
+      </c>
+      <c r="B2124" s="12" t="inlineStr">
+        <is>
+          <t>Дивиденди или удел во добивката на физички лица</t>
+        </is>
+      </c>
+      <c r="C2124" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2124" s="13" t="inlineStr"/>
+      <c r="E2124" s="13" t="inlineStr"/>
+      <c r="F2124" s="13" t="inlineStr"/>
+    </row>
+    <row r="2125">
+      <c r="A2125" s="11" t="inlineStr">
+        <is>
+          <t>8923</t>
+        </is>
+      </c>
+      <c r="B2125" s="12" t="inlineStr">
+        <is>
+          <t>Лични примања на сопствениците (награди, трошоци за лекување, рекреација и слично)</t>
+        </is>
+      </c>
+      <c r="C2125" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2125" s="13" t="inlineStr"/>
+      <c r="E2125" s="13" t="inlineStr"/>
+      <c r="F2125" s="13" t="inlineStr"/>
+    </row>
+    <row r="2126">
+      <c r="A2126" s="11" t="inlineStr">
+        <is>
+          <t>8924</t>
+        </is>
+      </c>
+      <c r="B2126" s="12" t="inlineStr">
+        <is>
+          <t>Останати примања од добивката за членови на управниот одбор, надзорен одбор, одбор на директори и управители</t>
+        </is>
+      </c>
+      <c r="C2126" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2126" s="13" t="inlineStr"/>
+      <c r="E2126" s="13" t="inlineStr"/>
+      <c r="F2126" s="13" t="inlineStr"/>
+    </row>
+    <row r="2127">
+      <c r="A2127" s="11" t="inlineStr">
+        <is>
+          <t>8925</t>
+        </is>
+      </c>
+      <c r="B2127" s="12" t="inlineStr">
+        <is>
+          <t>Бруто плата од добивката</t>
+        </is>
+      </c>
+      <c r="C2127" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2127" s="13" t="inlineStr"/>
+      <c r="E2127" s="13" t="inlineStr"/>
+      <c r="F2127" s="13" t="inlineStr"/>
+    </row>
+    <row r="2128">
+      <c r="A2128" s="8" t="inlineStr">
+        <is>
+          <t>893</t>
+        </is>
+      </c>
+      <c r="B2128" s="9" t="inlineStr">
+        <is>
+          <t>Резерви</t>
+        </is>
+      </c>
+      <c r="C2128" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2128" s="10" t="inlineStr"/>
+      <c r="E2128" s="10" t="inlineStr"/>
+      <c r="F2128" s="10" t="inlineStr"/>
+    </row>
+    <row r="2129">
+      <c r="A2129" s="11" t="inlineStr">
+        <is>
+          <t>8930</t>
+        </is>
+      </c>
+      <c r="B2129" s="12" t="inlineStr">
+        <is>
+          <t>Законски резерви</t>
+        </is>
+      </c>
+      <c r="C2129" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2129" s="13" t="inlineStr"/>
+      <c r="E2129" s="13" t="inlineStr"/>
+      <c r="F2129" s="13" t="inlineStr"/>
+    </row>
+    <row r="2130">
+      <c r="A2130" s="11" t="inlineStr">
+        <is>
+          <t>8931</t>
+        </is>
+      </c>
+      <c r="B2130" s="12" t="inlineStr">
+        <is>
+          <t>Статутарни резерви</t>
+        </is>
+      </c>
+      <c r="C2130" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2130" s="13" t="inlineStr"/>
+      <c r="E2130" s="13" t="inlineStr"/>
+      <c r="F2130" s="13" t="inlineStr"/>
+    </row>
+    <row r="2131">
+      <c r="A2131" s="11" t="inlineStr">
+        <is>
+          <t>8932</t>
+        </is>
+      </c>
+      <c r="B2131" s="12" t="inlineStr">
+        <is>
+          <t>Останати резерви</t>
+        </is>
+      </c>
+      <c r="C2131" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2131" s="13" t="inlineStr"/>
+      <c r="E2131" s="13" t="inlineStr"/>
+      <c r="F2131" s="13" t="inlineStr"/>
+    </row>
+    <row r="2132">
+      <c r="A2132" s="8" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="B2132" s="9" t="inlineStr">
+        <is>
+          <t>Нераспоредена добивка</t>
+        </is>
+      </c>
+      <c r="C2132" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2132" s="10" t="inlineStr"/>
+      <c r="E2132" s="10" t="inlineStr"/>
+      <c r="F2132" s="10" t="inlineStr"/>
+    </row>
+    <row r="2133">
+      <c r="A2133" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B2133" s="3" t="inlineStr">
+        <is>
+          <t>КАПИТАЛ, РЕЗЕРВИ И ВОНБИЛАНСНА ЕВИДЕНЦИЈА</t>
+        </is>
+      </c>
+      <c r="C2133" s="4" t="inlineStr">
+        <is>
+          <t>Класа</t>
+        </is>
+      </c>
+      <c r="D2133" s="4" t="inlineStr"/>
+      <c r="E2133" s="4" t="inlineStr"/>
+      <c r="F2133" s="4" t="inlineStr"/>
+    </row>
+    <row r="2134">
+      <c r="A2134" s="5" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B2134" s="6" t="inlineStr">
+        <is>
+          <t>ОСНОВНА ГЛАВНИНА - ЗАПИШАН КАПИТАЛ</t>
+        </is>
+      </c>
+      <c r="C2134" s="7" t="inlineStr">
+        <is>
+          <t>Група</t>
+        </is>
+      </c>
+      <c r="D2134" s="7" t="inlineStr"/>
+      <c r="E2134" s="7" t="inlineStr"/>
+      <c r="F2134" s="7" t="inlineStr"/>
+    </row>
+    <row r="2135">
+      <c r="A2135" s="8" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="B2135" s="9" t="inlineStr">
+        <is>
+          <t>Основна главнина - запишан и уплатен капитал</t>
+        </is>
+      </c>
+      <c r="C2135" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2135" s="10" t="inlineStr"/>
+      <c r="E2135" s="10" t="inlineStr"/>
+      <c r="F2135" s="10" t="inlineStr"/>
+    </row>
+    <row r="2136">
+      <c r="A2136" s="11" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="B2136" s="12" t="inlineStr">
+        <is>
+          <t>Основна главнина - обични акции</t>
+        </is>
+      </c>
+      <c r="C2136" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2136" s="13" t="inlineStr"/>
+      <c r="E2136" s="13" t="inlineStr"/>
+      <c r="F2136" s="13" t="inlineStr"/>
+    </row>
+    <row r="2137">
+      <c r="A2137" s="11" t="inlineStr">
+        <is>
+          <t>9001</t>
+        </is>
+      </c>
+      <c r="B2137" s="12" t="inlineStr">
+        <is>
+          <t>Основна главнина - приоритетни акции</t>
+        </is>
+      </c>
+      <c r="C2137" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2137" s="13" t="inlineStr"/>
+      <c r="E2137" s="13" t="inlineStr"/>
+      <c r="F2137" s="13" t="inlineStr"/>
+    </row>
+    <row r="2138">
+      <c r="A2138" s="11" t="inlineStr">
+        <is>
+          <t>9002</t>
+        </is>
+      </c>
+      <c r="B2138" s="12" t="inlineStr">
+        <is>
+          <t>Основна главнина - учество кое нема контрола</t>
+        </is>
+      </c>
+      <c r="C2138" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2138" s="13" t="inlineStr"/>
+      <c r="E2138" s="13" t="inlineStr"/>
+      <c r="F2138" s="13" t="inlineStr"/>
+    </row>
+    <row r="2139">
+      <c r="A2139" s="11" t="inlineStr">
+        <is>
+          <t>9003</t>
+        </is>
+      </c>
+      <c r="B2139" s="12" t="inlineStr">
+        <is>
+          <t>Основна главнина - удели на содружници</t>
+        </is>
+      </c>
+      <c r="C2139" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2139" s="13" t="inlineStr"/>
+      <c r="E2139" s="13" t="inlineStr"/>
+      <c r="F2139" s="13" t="inlineStr"/>
+    </row>
+    <row r="2140">
+      <c r="A2140" s="11" t="inlineStr">
+        <is>
+          <t>9004</t>
+        </is>
+      </c>
+      <c r="B2140" s="12" t="inlineStr">
+        <is>
+          <t>Основна главнина - удели во командитно друштво</t>
+        </is>
+      </c>
+      <c r="C2140" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2140" s="13" t="inlineStr"/>
+      <c r="E2140" s="13" t="inlineStr"/>
+      <c r="F2140" s="13" t="inlineStr"/>
+    </row>
+    <row r="2141">
+      <c r="A2141" s="11" t="inlineStr">
+        <is>
+          <t>9005</t>
+        </is>
+      </c>
+      <c r="B2141" s="12" t="inlineStr">
+        <is>
+          <t>Основна главнина на јавно трговско друштво</t>
+        </is>
+      </c>
+      <c r="C2141" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2141" s="13" t="inlineStr"/>
+      <c r="E2141" s="13" t="inlineStr"/>
+      <c r="F2141" s="13" t="inlineStr"/>
+    </row>
+    <row r="2142">
+      <c r="A2142" s="11" t="inlineStr">
+        <is>
+          <t>9006</t>
+        </is>
+      </c>
+      <c r="B2142" s="12" t="inlineStr">
+        <is>
+          <t>Основна главнина - државен капитал</t>
+        </is>
+      </c>
+      <c r="C2142" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2142" s="13" t="inlineStr"/>
+      <c r="E2142" s="13" t="inlineStr"/>
+      <c r="F2142" s="13" t="inlineStr"/>
+    </row>
+    <row r="2143">
+      <c r="A2143" s="11" t="inlineStr">
+        <is>
+          <t>9007</t>
+        </is>
+      </c>
+      <c r="B2143" s="12" t="inlineStr">
+        <is>
+          <t>Основна главнина - останат капитал</t>
+        </is>
+      </c>
+      <c r="C2143" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2143" s="13" t="inlineStr"/>
+      <c r="E2143" s="13" t="inlineStr"/>
+      <c r="F2143" s="13" t="inlineStr"/>
+    </row>
+    <row r="2144">
+      <c r="A2144" s="11" t="inlineStr">
+        <is>
+          <t>9008</t>
+        </is>
+      </c>
+      <c r="B2144" s="12" t="inlineStr">
+        <is>
+          <t>Зголемување на основната главнина</t>
+        </is>
+      </c>
+      <c r="C2144" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2144" s="13" t="inlineStr"/>
+      <c r="E2144" s="13" t="inlineStr"/>
+      <c r="F2144" s="13" t="inlineStr"/>
+    </row>
+    <row r="2145">
+      <c r="A2145" s="8" t="inlineStr">
+        <is>
+          <t>901</t>
+        </is>
+      </c>
+      <c r="B2145" s="9" t="inlineStr">
+        <is>
+          <t>Запишана, а неуплатена основна главнина</t>
+        </is>
+      </c>
+      <c r="C2145" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2145" s="10" t="inlineStr"/>
+      <c r="E2145" s="10" t="inlineStr"/>
+      <c r="F2145" s="10" t="inlineStr"/>
+    </row>
+    <row r="2146">
+      <c r="A2146" s="11" t="inlineStr">
+        <is>
+          <t>9010</t>
+        </is>
+      </c>
+      <c r="B2146" s="12" t="inlineStr">
+        <is>
+          <t>Запишани, а неуплатени акции</t>
+        </is>
+      </c>
+      <c r="C2146" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2146" s="13" t="inlineStr"/>
+      <c r="E2146" s="13" t="inlineStr"/>
+      <c r="F2146" s="13" t="inlineStr"/>
+    </row>
+    <row r="2147">
+      <c r="A2147" s="11" t="inlineStr">
+        <is>
+          <t>9011</t>
+        </is>
+      </c>
+      <c r="B2147" s="12" t="inlineStr">
+        <is>
+          <t>Запишани, а неуплатени удели</t>
+        </is>
+      </c>
+      <c r="C2147" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2147" s="13" t="inlineStr"/>
+      <c r="E2147" s="13" t="inlineStr"/>
+      <c r="F2147" s="13" t="inlineStr"/>
+    </row>
+    <row r="2148">
+      <c r="A2148" s="8" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="B2148" s="9" t="inlineStr">
+        <is>
+          <t>Сопствени акции и удели</t>
+        </is>
+      </c>
+      <c r="C2148" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2148" s="10" t="inlineStr"/>
+      <c r="E2148" s="10" t="inlineStr"/>
+      <c r="F2148" s="10" t="inlineStr"/>
+    </row>
+    <row r="2149">
+      <c r="A2149" s="11" t="inlineStr">
+        <is>
+          <t>9020</t>
+        </is>
+      </c>
+      <c r="B2149" s="12" t="inlineStr">
+        <is>
+          <t>Откупени сопствени акции</t>
+        </is>
+      </c>
+      <c r="C2149" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2149" s="13" t="inlineStr"/>
+      <c r="E2149" s="13" t="inlineStr"/>
+      <c r="F2149" s="13" t="inlineStr"/>
+    </row>
+    <row r="2150">
+      <c r="A2150" s="11" t="inlineStr">
+        <is>
+          <t>9021</t>
+        </is>
+      </c>
+      <c r="B2150" s="12" t="inlineStr">
+        <is>
+          <t>Откупени сопствени удели</t>
+        </is>
+      </c>
+      <c r="C2150" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2150" s="13" t="inlineStr"/>
+      <c r="E2150" s="13" t="inlineStr"/>
+      <c r="F2150" s="13" t="inlineStr"/>
+    </row>
+    <row r="2151">
+      <c r="A2151" s="5" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="B2151" s="6" t="inlineStr">
+        <is>
+          <t>ПРЕМИИ НА ЕМИТИРАНИ АКЦИИ</t>
+        </is>
+      </c>
+      <c r="C2151" s="7" t="inlineStr">
+        <is>
+          <t>Група</t>
+        </is>
+      </c>
+      <c r="D2151" s="7" t="inlineStr"/>
+      <c r="E2151" s="7" t="inlineStr"/>
+      <c r="F2151" s="7" t="inlineStr"/>
+    </row>
+    <row r="2152">
+      <c r="A2152" s="8" t="inlineStr">
+        <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="B2152" s="9" t="inlineStr">
+        <is>
+          <t>Премии врз основа на продажба на обични акции</t>
+        </is>
+      </c>
+      <c r="C2152" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2152" s="10" t="inlineStr"/>
+      <c r="E2152" s="10" t="inlineStr"/>
+      <c r="F2152" s="10" t="inlineStr"/>
+    </row>
+    <row r="2153">
+      <c r="A2153" s="8" t="inlineStr">
+        <is>
+          <t>911</t>
+        </is>
+      </c>
+      <c r="B2153" s="9" t="inlineStr">
+        <is>
+          <t>Премии врз основа на продажба на приоритетни акции</t>
+        </is>
+      </c>
+      <c r="C2153" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2153" s="10" t="inlineStr"/>
+      <c r="E2153" s="10" t="inlineStr"/>
+      <c r="F2153" s="10" t="inlineStr"/>
+    </row>
+    <row r="2154">
+      <c r="A2154" s="8" t="inlineStr">
+        <is>
+          <t>912</t>
+        </is>
+      </c>
+      <c r="B2154" s="9" t="inlineStr">
+        <is>
+          <t>Премии врз основа на конверзија на приоритетни акции во обични акции</t>
+        </is>
+      </c>
+      <c r="C2154" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2154" s="10" t="inlineStr"/>
+      <c r="E2154" s="10" t="inlineStr"/>
+      <c r="F2154" s="10" t="inlineStr"/>
+    </row>
+    <row r="2155">
+      <c r="A2155" s="5" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="B2155" s="6" t="inlineStr">
+        <is>
+          <t>РЕВАЛОРИЗАЦИОНИ РЕЗЕРВИ И РАЗЛИКИ ОД ВРЕДНУВАЊЕ НА КОМПОНЕНТИ НА ОСТАНАТА СЕОПФАТНА ДОБИВКА</t>
+        </is>
+      </c>
+      <c r="C2155" s="7" t="inlineStr">
+        <is>
+          <t>Група</t>
+        </is>
+      </c>
+      <c r="D2155" s="7" t="inlineStr"/>
+      <c r="E2155" s="7" t="inlineStr"/>
+      <c r="F2155" s="7" t="inlineStr"/>
+    </row>
+    <row r="2156">
+      <c r="A2156" s="8" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="B2156" s="9" t="inlineStr">
+        <is>
+          <t>Ревалоризациони резерви на нематеријални и материјални средства</t>
+        </is>
+      </c>
+      <c r="C2156" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2156" s="10" t="inlineStr"/>
+      <c r="E2156" s="10" t="inlineStr"/>
+      <c r="F2156" s="10" t="inlineStr"/>
+    </row>
+    <row r="2157">
+      <c r="A2157" s="11" t="inlineStr">
+        <is>
+          <t>9300</t>
+        </is>
+      </c>
+      <c r="B2157" s="12" t="inlineStr">
+        <is>
+          <t>Ревалоризациони резерви за нематеријални средства</t>
+        </is>
+      </c>
+      <c r="C2157" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2157" s="13" t="inlineStr"/>
+      <c r="E2157" s="13" t="inlineStr"/>
+      <c r="F2157" s="13" t="inlineStr"/>
+    </row>
+    <row r="2158">
+      <c r="A2158" s="11" t="inlineStr">
+        <is>
+          <t>9301</t>
+        </is>
+      </c>
+      <c r="B2158" s="12" t="inlineStr">
+        <is>
+          <t>Ревалоризациони резерви на земјиште</t>
+        </is>
+      </c>
+      <c r="C2158" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2158" s="13" t="inlineStr"/>
+      <c r="E2158" s="13" t="inlineStr"/>
+      <c r="F2158" s="13" t="inlineStr"/>
+    </row>
+    <row r="2159">
+      <c r="A2159" s="11" t="inlineStr">
+        <is>
+          <t>9302</t>
+        </is>
+      </c>
+      <c r="B2159" s="12" t="inlineStr">
+        <is>
+          <t>Ревалоризациони резерви на градежни објекти</t>
+        </is>
+      </c>
+      <c r="C2159" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2159" s="13" t="inlineStr"/>
+      <c r="E2159" s="13" t="inlineStr"/>
+      <c r="F2159" s="13" t="inlineStr"/>
+    </row>
+    <row r="2160">
+      <c r="A2160" s="11" t="inlineStr">
+        <is>
+          <t>9303</t>
+        </is>
+      </c>
+      <c r="B2160" s="12" t="inlineStr">
+        <is>
+          <t>Ревалоризациони резерви за постројки</t>
+        </is>
+      </c>
+      <c r="C2160" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2160" s="13" t="inlineStr"/>
+      <c r="E2160" s="13" t="inlineStr"/>
+      <c r="F2160" s="13" t="inlineStr"/>
+    </row>
+    <row r="2161">
+      <c r="A2161" s="11" t="inlineStr">
+        <is>
+          <t>9304</t>
+        </is>
+      </c>
+      <c r="B2161" s="12" t="inlineStr">
+        <is>
+          <t>Ревалоризациони резерви за опрема</t>
+        </is>
+      </c>
+      <c r="C2161" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2161" s="13" t="inlineStr"/>
+      <c r="E2161" s="13" t="inlineStr"/>
+      <c r="F2161" s="13" t="inlineStr"/>
+    </row>
+    <row r="2162">
+      <c r="A2162" s="11" t="inlineStr">
+        <is>
+          <t>9305</t>
+        </is>
+      </c>
+      <c r="B2162" s="12" t="inlineStr">
+        <is>
+          <t>Ревалоризациони резерви за останати материјални средства</t>
+        </is>
+      </c>
+      <c r="C2162" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2162" s="13" t="inlineStr"/>
+      <c r="E2162" s="13" t="inlineStr"/>
+      <c r="F2162" s="13" t="inlineStr"/>
+    </row>
+    <row r="2163">
+      <c r="A2163" s="8" t="inlineStr">
+        <is>
+          <t>931</t>
+        </is>
+      </c>
+      <c r="B2163" s="9" t="inlineStr">
+        <is>
+          <t>Ревалоризациони резерви врз основа на преведување на странско работење</t>
+        </is>
+      </c>
+      <c r="C2163" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2163" s="10" t="inlineStr"/>
+      <c r="E2163" s="10" t="inlineStr"/>
+      <c r="F2163" s="10" t="inlineStr"/>
+    </row>
+    <row r="2164">
+      <c r="A2164" s="8" t="inlineStr">
+        <is>
+          <t>932</t>
+        </is>
+      </c>
+      <c r="B2164" s="9" t="inlineStr">
+        <is>
+          <t>Ревалоризациони резерви врз основа на финансиски средства расположиви за продажба</t>
+        </is>
+      </c>
+      <c r="C2164" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2164" s="10" t="inlineStr"/>
+      <c r="E2164" s="10" t="inlineStr"/>
+      <c r="F2164" s="10" t="inlineStr"/>
+    </row>
+    <row r="2165">
+      <c r="A2165" s="8" t="inlineStr">
+        <is>
+          <t>933</t>
+        </is>
+      </c>
+      <c r="B2165" s="9" t="inlineStr">
+        <is>
+          <t>Добивки/загуби од заштита на паричниот тек до рекласификација</t>
+        </is>
+      </c>
+      <c r="C2165" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2165" s="10" t="inlineStr"/>
+      <c r="E2165" s="10" t="inlineStr"/>
+      <c r="F2165" s="10" t="inlineStr"/>
+    </row>
+    <row r="2166">
+      <c r="A2166" s="8" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="B2166" s="9" t="inlineStr">
+        <is>
+          <t>Добивки/загуби на дефинирани планови за користи на вработените</t>
+        </is>
+      </c>
+      <c r="C2166" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2166" s="10" t="inlineStr"/>
+      <c r="E2166" s="10" t="inlineStr"/>
+      <c r="F2166" s="10" t="inlineStr"/>
+    </row>
+    <row r="2167">
+      <c r="A2167" s="8" t="inlineStr">
+        <is>
+          <t>935</t>
+        </is>
+      </c>
+      <c r="B2167" s="9" t="inlineStr">
+        <is>
+          <t>Останати ревалоризациони резерви</t>
+        </is>
+      </c>
+      <c r="C2167" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2167" s="10" t="inlineStr"/>
+      <c r="E2167" s="10" t="inlineStr"/>
+      <c r="F2167" s="10" t="inlineStr"/>
+    </row>
+    <row r="2168">
+      <c r="A2168" s="5" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="B2168" s="6" t="inlineStr">
+        <is>
+          <t>РЕЗЕРВИ</t>
+        </is>
+      </c>
+      <c r="C2168" s="7" t="inlineStr">
+        <is>
+          <t>Група</t>
+        </is>
+      </c>
+      <c r="D2168" s="7" t="inlineStr"/>
+      <c r="E2168" s="7" t="inlineStr"/>
+      <c r="F2168" s="7" t="inlineStr"/>
+    </row>
+    <row r="2169">
+      <c r="A2169" s="8" t="inlineStr">
+        <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="B2169" s="9" t="inlineStr">
+        <is>
+          <t>Законски резерви</t>
+        </is>
+      </c>
+      <c r="C2169" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2169" s="10" t="inlineStr"/>
+      <c r="E2169" s="10" t="inlineStr"/>
+      <c r="F2169" s="10" t="inlineStr"/>
+    </row>
+    <row r="2170">
+      <c r="A2170" s="11" t="inlineStr">
+        <is>
+          <t>9400</t>
+        </is>
+      </c>
+      <c r="B2170" s="12" t="inlineStr">
+        <is>
+          <t>Резерви согласно ЗТД</t>
+        </is>
+      </c>
+      <c r="C2170" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2170" s="13" t="inlineStr"/>
+      <c r="E2170" s="13" t="inlineStr"/>
+      <c r="F2170" s="13" t="inlineStr"/>
+    </row>
+    <row r="2171">
+      <c r="A2171" s="11" t="inlineStr">
+        <is>
+          <t>9401</t>
+        </is>
+      </c>
+      <c r="B2171" s="12" t="inlineStr">
+        <is>
+          <t>Резерви за зголемување на капитал</t>
+        </is>
+      </c>
+      <c r="C2171" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2171" s="13" t="inlineStr"/>
+      <c r="E2171" s="13" t="inlineStr"/>
+      <c r="F2171" s="13" t="inlineStr"/>
+    </row>
+    <row r="2172">
+      <c r="A2172" s="11" t="inlineStr">
+        <is>
+          <t>9402</t>
+        </is>
+      </c>
+      <c r="B2172" s="12" t="inlineStr">
+        <is>
+          <t>Резерви за откуп на сопствени акции</t>
+        </is>
+      </c>
+      <c r="C2172" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2172" s="13" t="inlineStr"/>
+      <c r="E2172" s="13" t="inlineStr"/>
+      <c r="F2172" s="13" t="inlineStr"/>
+    </row>
+    <row r="2173">
+      <c r="A2173" s="11" t="inlineStr">
+        <is>
+          <t>9403</t>
+        </is>
+      </c>
+      <c r="B2173" s="12" t="inlineStr">
+        <is>
+          <t>Резерви за откуп на сопствени удели</t>
+        </is>
+      </c>
+      <c r="C2173" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2173" s="13" t="inlineStr"/>
+      <c r="E2173" s="13" t="inlineStr"/>
+      <c r="F2173" s="13" t="inlineStr"/>
+    </row>
+    <row r="2174">
+      <c r="A2174" s="8" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+      <c r="B2174" s="9" t="inlineStr">
+        <is>
+          <t>Статутарни резерви</t>
+        </is>
+      </c>
+      <c r="C2174" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2174" s="10" t="inlineStr"/>
+      <c r="E2174" s="10" t="inlineStr"/>
+      <c r="F2174" s="10" t="inlineStr"/>
+    </row>
+    <row r="2175">
+      <c r="A2175" s="11" t="inlineStr">
+        <is>
+          <t>9410</t>
+        </is>
+      </c>
+      <c r="B2175" s="12" t="inlineStr">
+        <is>
+          <t>Резерви за одржување на финансиска стабилност</t>
+        </is>
+      </c>
+      <c r="C2175" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2175" s="13" t="inlineStr"/>
+      <c r="E2175" s="13" t="inlineStr"/>
+      <c r="F2175" s="13" t="inlineStr"/>
+    </row>
+    <row r="2176">
+      <c r="A2176" s="11" t="inlineStr">
+        <is>
+          <t>9411</t>
+        </is>
+      </c>
+      <c r="B2176" s="12" t="inlineStr">
+        <is>
+          <t>Резерви за преструктуирање</t>
+        </is>
+      </c>
+      <c r="C2176" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2176" s="13" t="inlineStr"/>
+      <c r="E2176" s="13" t="inlineStr"/>
+      <c r="F2176" s="13" t="inlineStr"/>
+    </row>
+    <row r="2177">
+      <c r="A2177" s="11" t="inlineStr">
+        <is>
+          <t>9412</t>
+        </is>
+      </c>
+      <c r="B2177" s="12" t="inlineStr">
+        <is>
+          <t>Резерви за покривање на загуба</t>
+        </is>
+      </c>
+      <c r="C2177" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2177" s="13" t="inlineStr"/>
+      <c r="E2177" s="13" t="inlineStr"/>
+      <c r="F2177" s="13" t="inlineStr"/>
+    </row>
+    <row r="2178">
+      <c r="A2178" s="8" t="inlineStr">
+        <is>
+          <t>942</t>
+        </is>
+      </c>
+      <c r="B2178" s="9" t="inlineStr">
+        <is>
+          <t>Останати резерви</t>
+        </is>
+      </c>
+      <c r="C2178" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2178" s="10" t="inlineStr"/>
+      <c r="E2178" s="10" t="inlineStr"/>
+      <c r="F2178" s="10" t="inlineStr"/>
+    </row>
+    <row r="2179">
+      <c r="A2179" s="11" t="inlineStr">
+        <is>
+          <t>9420</t>
+        </is>
+      </c>
+      <c r="B2179" s="12" t="inlineStr">
+        <is>
+          <t>Резерви за награди</t>
+        </is>
+      </c>
+      <c r="C2179" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2179" s="13" t="inlineStr"/>
+      <c r="E2179" s="13" t="inlineStr"/>
+      <c r="F2179" s="13" t="inlineStr"/>
+    </row>
+    <row r="2180">
+      <c r="A2180" s="11" t="inlineStr">
+        <is>
+          <t>9421</t>
+        </is>
+      </c>
+      <c r="B2180" s="12" t="inlineStr">
+        <is>
+          <t>Резерви за останати намени</t>
+        </is>
+      </c>
+      <c r="C2180" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2180" s="13" t="inlineStr"/>
+      <c r="E2180" s="13" t="inlineStr"/>
+      <c r="F2180" s="13" t="inlineStr"/>
+    </row>
+    <row r="2181">
+      <c r="A2181" s="5" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="B2181" s="6" t="inlineStr">
+        <is>
+          <t>ЗАДРЖАНА (АКУМУЛИРАНА) ДОБИВКА И ДОБИВКА ЗА ТЕКОВНА ГОДИНА</t>
+        </is>
+      </c>
+      <c r="C2181" s="7" t="inlineStr">
+        <is>
+          <t>Група</t>
+        </is>
+      </c>
+      <c r="D2181" s="7" t="inlineStr"/>
+      <c r="E2181" s="7" t="inlineStr"/>
+      <c r="F2181" s="7" t="inlineStr"/>
+    </row>
+    <row r="2182">
+      <c r="A2182" s="8" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="B2182" s="9" t="inlineStr">
+        <is>
+          <t>Задржана (акумулирана) добивка од претходни години</t>
+        </is>
+      </c>
+      <c r="C2182" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2182" s="10" t="inlineStr"/>
+      <c r="E2182" s="10" t="inlineStr"/>
+      <c r="F2182" s="10" t="inlineStr"/>
+    </row>
+    <row r="2183">
+      <c r="A2183" s="11" t="inlineStr">
+        <is>
+          <t>9500</t>
+        </is>
+      </c>
+      <c r="B2183" s="12" t="inlineStr">
+        <is>
+          <t>Акумулирана добивка</t>
+        </is>
+      </c>
+      <c r="C2183" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2183" s="13" t="inlineStr"/>
+      <c r="E2183" s="13" t="inlineStr"/>
+      <c r="F2183" s="13" t="inlineStr"/>
+    </row>
+    <row r="2184">
+      <c r="A2184" s="8" t="inlineStr">
+        <is>
+          <t>951</t>
+        </is>
+      </c>
+      <c r="B2184" s="9" t="inlineStr">
+        <is>
+          <t>Добивка од тековната година</t>
+        </is>
+      </c>
+      <c r="C2184" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2184" s="10" t="inlineStr"/>
+      <c r="E2184" s="10" t="inlineStr"/>
+      <c r="F2184" s="10" t="inlineStr"/>
+    </row>
+    <row r="2185">
+      <c r="A2185" s="11" t="inlineStr">
+        <is>
+          <t>9510</t>
+        </is>
+      </c>
+      <c r="B2185" s="12" t="inlineStr">
+        <is>
+          <t>Акумулирана добивка од тековната година</t>
+        </is>
+      </c>
+      <c r="C2185" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2185" s="13" t="inlineStr"/>
+      <c r="E2185" s="13" t="inlineStr"/>
+      <c r="F2185" s="13" t="inlineStr"/>
+    </row>
+    <row r="2186">
+      <c r="A2186" s="5" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="B2186" s="6" t="inlineStr">
+        <is>
+          <t>ПРЕНЕСЕНА ЗАГУБА И ЗАГУБА ЗА ТЕКОВНА ГОДИНА</t>
+        </is>
+      </c>
+      <c r="C2186" s="7" t="inlineStr">
+        <is>
+          <t>Група</t>
+        </is>
+      </c>
+      <c r="D2186" s="7" t="inlineStr"/>
+      <c r="E2186" s="7" t="inlineStr"/>
+      <c r="F2186" s="7" t="inlineStr"/>
+    </row>
+    <row r="2187">
+      <c r="A2187" s="8" t="inlineStr">
+        <is>
+          <t>960</t>
+        </is>
+      </c>
+      <c r="B2187" s="9" t="inlineStr">
+        <is>
+          <t>Пренесена загуба од претходни години</t>
+        </is>
+      </c>
+      <c r="C2187" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2187" s="10" t="inlineStr"/>
+      <c r="E2187" s="10" t="inlineStr"/>
+      <c r="F2187" s="10" t="inlineStr"/>
+    </row>
+    <row r="2188">
+      <c r="A2188" s="8" t="inlineStr">
+        <is>
+          <t>961</t>
+        </is>
+      </c>
+      <c r="B2188" s="9" t="inlineStr">
+        <is>
+          <t>Загуба за тековната година</t>
+        </is>
+      </c>
+      <c r="C2188" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2188" s="10" t="inlineStr"/>
+      <c r="E2188" s="10" t="inlineStr"/>
+      <c r="F2188" s="10" t="inlineStr"/>
+    </row>
+    <row r="2189">
+      <c r="A2189" s="5" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="B2189" s="6" t="inlineStr">
+        <is>
+          <t>УЧЕСТВО ВО КАПИТАЛОТ КОЕ НЕМА КОНТРОЛА</t>
+        </is>
+      </c>
+      <c r="C2189" s="7" t="inlineStr">
+        <is>
+          <t>Група</t>
+        </is>
+      </c>
+      <c r="D2189" s="7" t="inlineStr"/>
+      <c r="E2189" s="7" t="inlineStr"/>
+      <c r="F2189" s="7" t="inlineStr"/>
+    </row>
+    <row r="2190">
+      <c r="A2190" s="5" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="B2190" s="6" t="inlineStr">
+        <is>
+          <t>ВОНБИЛАНСНА ЕВИДЕНЦИЈА - АКТИВА (СМЕТКИ ОД 990 ДО 994)</t>
+        </is>
+      </c>
+      <c r="C2190" s="7" t="inlineStr">
+        <is>
+          <t>Група</t>
+        </is>
+      </c>
+      <c r="D2190" s="7" t="inlineStr"/>
+      <c r="E2190" s="7" t="inlineStr"/>
+      <c r="F2190" s="7" t="inlineStr"/>
+    </row>
+    <row r="2191">
+      <c r="A2191" s="8" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="B2191" s="9" t="inlineStr">
+        <is>
+          <t>Примени туѓи недвижности, постројки и опрема</t>
+        </is>
+      </c>
+      <c r="C2191" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2191" s="10" t="inlineStr"/>
+      <c r="E2191" s="10" t="inlineStr"/>
+      <c r="F2191" s="10" t="inlineStr"/>
+    </row>
+    <row r="2192">
+      <c r="A2192" s="11" t="inlineStr">
+        <is>
+          <t>9900</t>
+        </is>
+      </c>
+      <c r="B2192" s="12" t="inlineStr">
+        <is>
+          <t>Примени постројки и опрема на испитување, контрола и поправка</t>
+        </is>
+      </c>
+      <c r="C2192" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2192" s="13" t="inlineStr"/>
+      <c r="E2192" s="13" t="inlineStr"/>
+      <c r="F2192" s="13" t="inlineStr"/>
+    </row>
+    <row r="2193">
+      <c r="A2193" s="11" t="inlineStr">
+        <is>
+          <t>9901</t>
+        </is>
+      </c>
+      <c r="B2193" s="12" t="inlineStr">
+        <is>
+          <t>Примени недвижности, постројки и опрема земени под закуп</t>
+        </is>
+      </c>
+      <c r="C2193" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2193" s="13" t="inlineStr"/>
+      <c r="E2193" s="13" t="inlineStr"/>
+      <c r="F2193" s="13" t="inlineStr"/>
+    </row>
+    <row r="2194">
+      <c r="A2194" s="11" t="inlineStr">
+        <is>
+          <t>9902</t>
+        </is>
+      </c>
+      <c r="B2194" s="12" t="inlineStr">
+        <is>
+          <t>Примени постројки и опрема на чување</t>
+        </is>
+      </c>
+      <c r="C2194" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2194" s="13" t="inlineStr"/>
+      <c r="E2194" s="13" t="inlineStr"/>
+      <c r="F2194" s="13" t="inlineStr"/>
+    </row>
+    <row r="2195">
+      <c r="A2195" s="8" t="inlineStr">
+        <is>
+          <t>991</t>
+        </is>
+      </c>
+      <c r="B2195" s="9" t="inlineStr">
+        <is>
+          <t>Примени туѓи материјали, полупроизводи, производи и стоки</t>
+        </is>
+      </c>
+      <c r="C2195" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2195" s="10" t="inlineStr"/>
+      <c r="E2195" s="10" t="inlineStr"/>
+      <c r="F2195" s="10" t="inlineStr"/>
+    </row>
+    <row r="2196">
+      <c r="A2196" s="11" t="inlineStr">
+        <is>
+          <t>9910</t>
+        </is>
+      </c>
+      <c r="B2196" s="12" t="inlineStr">
+        <is>
+          <t>Примени материјали</t>
+        </is>
+      </c>
+      <c r="C2196" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2196" s="13" t="inlineStr"/>
+      <c r="E2196" s="13" t="inlineStr"/>
+      <c r="F2196" s="13" t="inlineStr"/>
+    </row>
+    <row r="2197">
+      <c r="A2197" s="11" t="inlineStr">
+        <is>
+          <t>99100</t>
+        </is>
+      </c>
+      <c r="B2197" s="12" t="inlineStr">
+        <is>
+          <t>Примени материјали во доработка и обработка</t>
+        </is>
+      </c>
+      <c r="C2197" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2197" s="13" t="inlineStr"/>
+      <c r="E2197" s="13" t="inlineStr"/>
+      <c r="F2197" s="13" t="inlineStr"/>
+    </row>
+    <row r="2198">
+      <c r="A2198" s="11" t="inlineStr">
+        <is>
+          <t>99101</t>
+        </is>
+      </c>
+      <c r="B2198" s="12" t="inlineStr">
+        <is>
+          <t>Примени материјали од увоз за туѓа сметка</t>
+        </is>
+      </c>
+      <c r="C2198" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2198" s="13" t="inlineStr"/>
+      <c r="E2198" s="13" t="inlineStr"/>
+      <c r="F2198" s="13" t="inlineStr"/>
+    </row>
+    <row r="2199">
+      <c r="A2199" s="11" t="inlineStr">
+        <is>
+          <t>99102</t>
+        </is>
+      </c>
+      <c r="B2199" s="12" t="inlineStr">
+        <is>
+          <t>Примени материјали за заедничко работење</t>
+        </is>
+      </c>
+      <c r="C2199" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2199" s="13" t="inlineStr"/>
+      <c r="E2199" s="13" t="inlineStr"/>
+      <c r="F2199" s="13" t="inlineStr"/>
+    </row>
+    <row r="2200">
+      <c r="A2200" s="11" t="inlineStr">
+        <is>
+          <t>99103</t>
+        </is>
+      </c>
+      <c r="B2200" s="12" t="inlineStr">
+        <is>
+          <t>Примени материјали за лон работење</t>
+        </is>
+      </c>
+      <c r="C2200" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2200" s="13" t="inlineStr"/>
+      <c r="E2200" s="13" t="inlineStr"/>
+      <c r="F2200" s="13" t="inlineStr"/>
+    </row>
+    <row r="2201">
+      <c r="A2201" s="11" t="inlineStr">
+        <is>
+          <t>99104</t>
+        </is>
+      </c>
+      <c r="B2201" s="12" t="inlineStr">
+        <is>
+          <t>Примени материјали за чување</t>
+        </is>
+      </c>
+      <c r="C2201" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2201" s="13" t="inlineStr"/>
+      <c r="E2201" s="13" t="inlineStr"/>
+      <c r="F2201" s="13" t="inlineStr"/>
+    </row>
+    <row r="2202">
+      <c r="A2202" s="11" t="inlineStr">
+        <is>
+          <t>99105</t>
+        </is>
+      </c>
+      <c r="B2202" s="12" t="inlineStr">
+        <is>
+          <t>Примена туѓа повратна амбалажа</t>
+        </is>
+      </c>
+      <c r="C2202" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2202" s="13" t="inlineStr"/>
+      <c r="E2202" s="13" t="inlineStr"/>
+      <c r="F2202" s="13" t="inlineStr"/>
+    </row>
+    <row r="2203">
+      <c r="A2203" s="11" t="inlineStr">
+        <is>
+          <t>9911</t>
+        </is>
+      </c>
+      <c r="B2203" s="12" t="inlineStr">
+        <is>
+          <t>Примени полупроизводи</t>
+        </is>
+      </c>
+      <c r="C2203" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2203" s="13" t="inlineStr"/>
+      <c r="E2203" s="13" t="inlineStr"/>
+      <c r="F2203" s="13" t="inlineStr"/>
+    </row>
+    <row r="2204">
+      <c r="A2204" s="11" t="inlineStr">
+        <is>
+          <t>99110</t>
+        </is>
+      </c>
+      <c r="B2204" s="12" t="inlineStr">
+        <is>
+          <t>Примени полупроизводи во доработка и обработка</t>
+        </is>
+      </c>
+      <c r="C2204" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2204" s="13" t="inlineStr"/>
+      <c r="E2204" s="13" t="inlineStr"/>
+      <c r="F2204" s="13" t="inlineStr"/>
+    </row>
+    <row r="2205">
+      <c r="A2205" s="11" t="inlineStr">
+        <is>
+          <t>99111</t>
+        </is>
+      </c>
+      <c r="B2205" s="12" t="inlineStr">
+        <is>
+          <t>Примени полупроизводи за производство на заеднички производ</t>
+        </is>
+      </c>
+      <c r="C2205" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2205" s="13" t="inlineStr"/>
+      <c r="E2205" s="13" t="inlineStr"/>
+      <c r="F2205" s="13" t="inlineStr"/>
+    </row>
+    <row r="2206">
+      <c r="A2206" s="11" t="inlineStr">
+        <is>
+          <t>99112</t>
+        </is>
+      </c>
+      <c r="B2206" s="12" t="inlineStr">
+        <is>
+          <t>Примени полупроизводи за лон работење</t>
+        </is>
+      </c>
+      <c r="C2206" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2206" s="13" t="inlineStr"/>
+      <c r="E2206" s="13" t="inlineStr"/>
+      <c r="F2206" s="13" t="inlineStr"/>
+    </row>
+    <row r="2207">
+      <c r="A2207" s="11" t="inlineStr">
+        <is>
+          <t>99113</t>
+        </is>
+      </c>
+      <c r="B2207" s="12" t="inlineStr">
+        <is>
+          <t>Примени полупроизводи за чување</t>
+        </is>
+      </c>
+      <c r="C2207" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2207" s="13" t="inlineStr"/>
+      <c r="E2207" s="13" t="inlineStr"/>
+      <c r="F2207" s="13" t="inlineStr"/>
+    </row>
+    <row r="2208">
+      <c r="A2208" s="11" t="inlineStr">
+        <is>
+          <t>9912</t>
+        </is>
+      </c>
+      <c r="B2208" s="12" t="inlineStr">
+        <is>
+          <t>Примени производи</t>
+        </is>
+      </c>
+      <c r="C2208" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2208" s="13" t="inlineStr"/>
+      <c r="E2208" s="13" t="inlineStr"/>
+      <c r="F2208" s="13" t="inlineStr"/>
+    </row>
+    <row r="2209">
+      <c r="A2209" s="11" t="inlineStr">
+        <is>
+          <t>99120</t>
+        </is>
+      </c>
+      <c r="B2209" s="12" t="inlineStr">
+        <is>
+          <t>Примени производи во доработка и обработка</t>
+        </is>
+      </c>
+      <c r="C2209" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2209" s="13" t="inlineStr"/>
+      <c r="E2209" s="13" t="inlineStr"/>
+      <c r="F2209" s="13" t="inlineStr"/>
+    </row>
+    <row r="2210">
+      <c r="A2210" s="11" t="inlineStr">
+        <is>
+          <t>99121</t>
+        </is>
+      </c>
+      <c r="B2210" s="12" t="inlineStr">
+        <is>
+          <t>Примени производи на поправка</t>
+        </is>
+      </c>
+      <c r="C2210" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2210" s="13" t="inlineStr"/>
+      <c r="E2210" s="13" t="inlineStr"/>
+      <c r="F2210" s="13" t="inlineStr"/>
+    </row>
+    <row r="2211">
+      <c r="A2211" s="11" t="inlineStr">
+        <is>
+          <t>99122</t>
+        </is>
+      </c>
+      <c r="B2211" s="12" t="inlineStr">
+        <is>
+          <t>Примени производи на чување</t>
+        </is>
+      </c>
+      <c r="C2211" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2211" s="13" t="inlineStr"/>
+      <c r="E2211" s="13" t="inlineStr"/>
+      <c r="F2211" s="13" t="inlineStr"/>
+    </row>
+    <row r="2212">
+      <c r="A2212" s="11" t="inlineStr">
+        <is>
+          <t>9913</t>
+        </is>
+      </c>
+      <c r="B2212" s="12" t="inlineStr">
+        <is>
+          <t>Примени стоки</t>
+        </is>
+      </c>
+      <c r="C2212" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2212" s="13" t="inlineStr"/>
+      <c r="E2212" s="13" t="inlineStr"/>
+      <c r="F2212" s="13" t="inlineStr"/>
+    </row>
+    <row r="2213">
+      <c r="A2213" s="11" t="inlineStr">
+        <is>
+          <t>99130</t>
+        </is>
+      </c>
+      <c r="B2213" s="12" t="inlineStr">
+        <is>
+          <t>Примена стока во јавен склад</t>
+        </is>
+      </c>
+      <c r="C2213" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2213" s="13" t="inlineStr"/>
+      <c r="E2213" s="13" t="inlineStr"/>
+      <c r="F2213" s="13" t="inlineStr"/>
+    </row>
+    <row r="2214">
+      <c r="A2214" s="11" t="inlineStr">
+        <is>
+          <t>99131</t>
+        </is>
+      </c>
+      <c r="B2214" s="12" t="inlineStr">
+        <is>
+          <t>Примена стока во консигнација и комисион</t>
+        </is>
+      </c>
+      <c r="C2214" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2214" s="13" t="inlineStr"/>
+      <c r="E2214" s="13" t="inlineStr"/>
+      <c r="F2214" s="13" t="inlineStr"/>
+    </row>
+    <row r="2215">
+      <c r="A2215" s="11" t="inlineStr">
+        <is>
+          <t>99132</t>
+        </is>
+      </c>
+      <c r="B2215" s="12" t="inlineStr">
+        <is>
+          <t>Примена стока за увоз за туѓа сметка</t>
+        </is>
+      </c>
+      <c r="C2215" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2215" s="13" t="inlineStr"/>
+      <c r="E2215" s="13" t="inlineStr"/>
+      <c r="F2215" s="13" t="inlineStr"/>
+    </row>
+    <row r="2216">
+      <c r="A2216" s="11" t="inlineStr">
+        <is>
+          <t>99133</t>
+        </is>
+      </c>
+      <c r="B2216" s="12" t="inlineStr">
+        <is>
+          <t>Примена стока за извоз за туѓа сметка</t>
+        </is>
+      </c>
+      <c r="C2216" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2216" s="13" t="inlineStr"/>
+      <c r="E2216" s="13" t="inlineStr"/>
+      <c r="F2216" s="13" t="inlineStr"/>
+    </row>
+    <row r="2217">
+      <c r="A2217" s="11" t="inlineStr">
+        <is>
+          <t>99134</t>
+        </is>
+      </c>
+      <c r="B2217" s="12" t="inlineStr">
+        <is>
+          <t>Примена стока за заедничко работење</t>
+        </is>
+      </c>
+      <c r="C2217" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2217" s="13" t="inlineStr"/>
+      <c r="E2217" s="13" t="inlineStr"/>
+      <c r="F2217" s="13" t="inlineStr"/>
+    </row>
+    <row r="2218">
+      <c r="A2218" s="11" t="inlineStr">
+        <is>
+          <t>99135</t>
+        </is>
+      </c>
+      <c r="B2218" s="12" t="inlineStr">
+        <is>
+          <t>Примена стока на доработка и обработка</t>
+        </is>
+      </c>
+      <c r="C2218" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2218" s="13" t="inlineStr"/>
+      <c r="E2218" s="13" t="inlineStr"/>
+      <c r="F2218" s="13" t="inlineStr"/>
+    </row>
+    <row r="2219">
+      <c r="A2219" s="8" t="inlineStr">
+        <is>
+          <t>992</t>
+        </is>
+      </c>
+      <c r="B2219" s="9" t="inlineStr">
+        <is>
+          <t>Хартии од вредност и други вредносници</t>
+        </is>
+      </c>
+      <c r="C2219" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2219" s="10" t="inlineStr"/>
+      <c r="E2219" s="10" t="inlineStr"/>
+      <c r="F2219" s="10" t="inlineStr"/>
+    </row>
+    <row r="2220">
+      <c r="A2220" s="11" t="inlineStr">
+        <is>
+          <t>9920</t>
+        </is>
+      </c>
+      <c r="B2220" s="12" t="inlineStr">
+        <is>
+          <t>Меници за потрошувачки кредит</t>
+        </is>
+      </c>
+      <c r="C2220" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2220" s="13" t="inlineStr"/>
+      <c r="E2220" s="13" t="inlineStr"/>
+      <c r="F2220" s="13" t="inlineStr"/>
+    </row>
+    <row r="2221">
+      <c r="A2221" s="11" t="inlineStr">
+        <is>
+          <t>9921</t>
+        </is>
+      </c>
+      <c r="B2221" s="12" t="inlineStr">
+        <is>
+          <t>Меници за долгорочен кредит</t>
+        </is>
+      </c>
+      <c r="C2221" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2221" s="13" t="inlineStr"/>
+      <c r="E2221" s="13" t="inlineStr"/>
+      <c r="F2221" s="13" t="inlineStr"/>
+    </row>
+    <row r="2222">
+      <c r="A2222" s="11" t="inlineStr">
+        <is>
+          <t>9922</t>
+        </is>
+      </c>
+      <c r="B2222" s="12" t="inlineStr">
+        <is>
+          <t>Бланко акцептирани меници</t>
+        </is>
+      </c>
+      <c r="C2222" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2222" s="13" t="inlineStr"/>
+      <c r="E2222" s="13" t="inlineStr"/>
+      <c r="F2222" s="13" t="inlineStr"/>
+    </row>
+    <row r="2223">
+      <c r="A2223" s="11" t="inlineStr">
+        <is>
+          <t>9923</t>
+        </is>
+      </c>
+      <c r="B2223" s="12" t="inlineStr">
+        <is>
+          <t>Бланко авалирани меници</t>
+        </is>
+      </c>
+      <c r="C2223" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2223" s="13" t="inlineStr"/>
+      <c r="E2223" s="13" t="inlineStr"/>
+      <c r="F2223" s="13" t="inlineStr"/>
+    </row>
+    <row r="2224">
+      <c r="A2224" s="11" t="inlineStr">
+        <is>
+          <t>9924</t>
+        </is>
+      </c>
+      <c r="B2224" s="12" t="inlineStr">
+        <is>
+          <t>Примени авали на меници</t>
+        </is>
+      </c>
+      <c r="C2224" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2224" s="13" t="inlineStr"/>
+      <c r="E2224" s="13" t="inlineStr"/>
+      <c r="F2224" s="13" t="inlineStr"/>
+    </row>
+    <row r="2225">
+      <c r="A2225" s="11" t="inlineStr">
+        <is>
+          <t>9925</t>
+        </is>
+      </c>
+      <c r="B2225" s="12" t="inlineStr">
+        <is>
+          <t>Примени гаранции</t>
+        </is>
+      </c>
+      <c r="C2225" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2225" s="13" t="inlineStr"/>
+      <c r="E2225" s="13" t="inlineStr"/>
+      <c r="F2225" s="13" t="inlineStr"/>
+    </row>
+    <row r="2226">
+      <c r="A2226" s="11" t="inlineStr">
+        <is>
+          <t>9926</t>
+        </is>
+      </c>
+      <c r="B2226" s="12" t="inlineStr">
+        <is>
+          <t>Примени обврзници за заеми</t>
+        </is>
+      </c>
+      <c r="C2226" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2226" s="13" t="inlineStr"/>
+      <c r="E2226" s="13" t="inlineStr"/>
+      <c r="F2226" s="13" t="inlineStr"/>
+    </row>
+    <row r="2227">
+      <c r="A2227" s="11" t="inlineStr">
+        <is>
+          <t>9927</t>
+        </is>
+      </c>
+      <c r="B2227" s="12" t="inlineStr">
+        <is>
+          <t>Влезници за културни, спортски и слични манифестации</t>
+        </is>
+      </c>
+      <c r="C2227" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2227" s="13" t="inlineStr"/>
+      <c r="E2227" s="13" t="inlineStr"/>
+      <c r="F2227" s="13" t="inlineStr"/>
+    </row>
+    <row r="2228">
+      <c r="A2228" s="8" t="inlineStr">
+        <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="B2228" s="9" t="inlineStr">
+        <is>
+          <t>Права</t>
+        </is>
+      </c>
+      <c r="C2228" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2228" s="10" t="inlineStr"/>
+      <c r="E2228" s="10" t="inlineStr"/>
+      <c r="F2228" s="10" t="inlineStr"/>
+    </row>
+    <row r="2229">
+      <c r="A2229" s="11" t="inlineStr">
+        <is>
+          <t>9930</t>
+        </is>
+      </c>
+      <c r="B2229" s="12" t="inlineStr">
+        <is>
+          <t>Право на лоро акредитив (домашен и странски)</t>
+        </is>
+      </c>
+      <c r="C2229" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2229" s="13" t="inlineStr"/>
+      <c r="E2229" s="13" t="inlineStr"/>
+      <c r="F2229" s="13" t="inlineStr"/>
+    </row>
+    <row r="2230">
+      <c r="A2230" s="11" t="inlineStr">
+        <is>
+          <t>9931</t>
+        </is>
+      </c>
+      <c r="B2230" s="12" t="inlineStr">
+        <is>
+          <t>Право на користење на патенти, лиценци и слични права</t>
+        </is>
+      </c>
+      <c r="C2230" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2230" s="13" t="inlineStr"/>
+      <c r="E2230" s="13" t="inlineStr"/>
+      <c r="F2230" s="13" t="inlineStr"/>
+    </row>
+    <row r="2231">
+      <c r="A2231" s="11" t="inlineStr">
+        <is>
+          <t>9932</t>
+        </is>
+      </c>
+      <c r="B2231" s="12" t="inlineStr">
+        <is>
+          <t>Укнижување на хипотека на недвижности</t>
+        </is>
+      </c>
+      <c r="C2231" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2231" s="13" t="inlineStr"/>
+      <c r="E2231" s="13" t="inlineStr"/>
+      <c r="F2231" s="13" t="inlineStr"/>
+    </row>
+    <row r="2232">
+      <c r="A2232" s="11" t="inlineStr">
+        <is>
+          <t>9933</t>
+        </is>
+      </c>
+      <c r="B2232" s="12" t="inlineStr">
+        <is>
+          <t>Укнижување на залог</t>
+        </is>
+      </c>
+      <c r="C2232" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2232" s="13" t="inlineStr"/>
+      <c r="E2232" s="13" t="inlineStr"/>
+      <c r="F2232" s="13" t="inlineStr"/>
+    </row>
+    <row r="2233">
+      <c r="A2233" s="11" t="inlineStr">
+        <is>
+          <t>9934</t>
+        </is>
+      </c>
+      <c r="B2233" s="12" t="inlineStr">
+        <is>
+          <t>Договорени неискористени кредити</t>
+        </is>
+      </c>
+      <c r="C2233" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2233" s="13" t="inlineStr"/>
+      <c r="E2233" s="13" t="inlineStr"/>
+      <c r="F2233" s="13" t="inlineStr"/>
+    </row>
+    <row r="2234">
+      <c r="A2234" s="8" t="inlineStr">
+        <is>
+          <t>994</t>
+        </is>
+      </c>
+      <c r="B2234" s="9" t="inlineStr">
+        <is>
+          <t>Останата активна вонбилансна евиденција</t>
+        </is>
+      </c>
+      <c r="C2234" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2234" s="10" t="inlineStr"/>
+      <c r="E2234" s="10" t="inlineStr"/>
+      <c r="F2234" s="10" t="inlineStr"/>
+    </row>
+    <row r="2235">
+      <c r="A2235" s="11" t="inlineStr">
+        <is>
+          <t>9940</t>
+        </is>
+      </c>
+      <c r="B2235" s="12" t="inlineStr">
+        <is>
+          <t>Дадени аванси за туѓи меници</t>
+        </is>
+      </c>
+      <c r="C2235" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2235" s="13" t="inlineStr"/>
+      <c r="E2235" s="13" t="inlineStr"/>
+      <c r="F2235" s="13" t="inlineStr"/>
+    </row>
+    <row r="2236">
+      <c r="A2236" s="11" t="inlineStr">
+        <is>
+          <t>9941</t>
+        </is>
+      </c>
+      <c r="B2236" s="12" t="inlineStr">
+        <is>
+          <t>Дадени гаранции за туѓи обврски</t>
+        </is>
+      </c>
+      <c r="C2236" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2236" s="13" t="inlineStr"/>
+      <c r="E2236" s="13" t="inlineStr"/>
+      <c r="F2236" s="13" t="inlineStr"/>
+    </row>
+    <row r="2237">
+      <c r="A2237" s="11" t="inlineStr">
+        <is>
+          <t>9949</t>
+        </is>
+      </c>
+      <c r="B2237" s="12" t="inlineStr">
+        <is>
+          <t>Останата вонбилансна евиденција</t>
+        </is>
+      </c>
+      <c r="C2237" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2237" s="13" t="inlineStr"/>
+      <c r="E2237" s="13" t="inlineStr"/>
+      <c r="F2237" s="13" t="inlineStr"/>
+    </row>
+    <row r="2238">
+      <c r="A2238" s="8" t="inlineStr">
+        <is>
+          <t>995</t>
+        </is>
+      </c>
+      <c r="B2238" s="9" t="inlineStr">
+        <is>
+          <t>Обврски за примени туѓи недвижности, постројки и опрема</t>
+        </is>
+      </c>
+      <c r="C2238" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2238" s="10" t="inlineStr"/>
+      <c r="E2238" s="10" t="inlineStr"/>
+      <c r="F2238" s="10" t="inlineStr"/>
+    </row>
+    <row r="2239">
+      <c r="A2239" s="11" t="inlineStr">
+        <is>
+          <t>9950</t>
+        </is>
+      </c>
+      <c r="B2239" s="12" t="inlineStr">
+        <is>
+          <t>Обврски за примени постројки и опрема на испитување, контрола и поправка</t>
+        </is>
+      </c>
+      <c r="C2239" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2239" s="13" t="inlineStr"/>
+      <c r="E2239" s="13" t="inlineStr"/>
+      <c r="F2239" s="13" t="inlineStr"/>
+    </row>
+    <row r="2240">
+      <c r="A2240" s="11" t="inlineStr">
+        <is>
+          <t>9951</t>
+        </is>
+      </c>
+      <c r="B2240" s="12" t="inlineStr">
+        <is>
+          <t>Обврски за примени недвижности, постројки и опрема земена под закуп</t>
+        </is>
+      </c>
+      <c r="C2240" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2240" s="13" t="inlineStr"/>
+      <c r="E2240" s="13" t="inlineStr"/>
+      <c r="F2240" s="13" t="inlineStr"/>
+    </row>
+    <row r="2241">
+      <c r="A2241" s="11" t="inlineStr">
+        <is>
+          <t>9952</t>
+        </is>
+      </c>
+      <c r="B2241" s="12" t="inlineStr">
+        <is>
+          <t>Обврски за примени постројки и опрема за чување</t>
+        </is>
+      </c>
+      <c r="C2241" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2241" s="13" t="inlineStr"/>
+      <c r="E2241" s="13" t="inlineStr"/>
+      <c r="F2241" s="13" t="inlineStr"/>
+    </row>
+    <row r="2242">
+      <c r="A2242" s="8" t="inlineStr">
+        <is>
+          <t>996</t>
+        </is>
+      </c>
+      <c r="B2242" s="9" t="inlineStr">
+        <is>
+          <t>Обврски за примени туѓи материјали, полупроизводи, производи и стоки</t>
+        </is>
+      </c>
+      <c r="C2242" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2242" s="10" t="inlineStr"/>
+      <c r="E2242" s="10" t="inlineStr"/>
+      <c r="F2242" s="10" t="inlineStr"/>
+    </row>
+    <row r="2243">
+      <c r="A2243" s="11" t="inlineStr">
+        <is>
+          <t>9960</t>
+        </is>
+      </c>
+      <c r="B2243" s="12" t="inlineStr">
+        <is>
+          <t>Обврски за примени материјали</t>
+        </is>
+      </c>
+      <c r="C2243" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2243" s="13" t="inlineStr"/>
+      <c r="E2243" s="13" t="inlineStr"/>
+      <c r="F2243" s="13" t="inlineStr"/>
+    </row>
+    <row r="2244">
+      <c r="A2244" s="11" t="inlineStr">
+        <is>
+          <t>99600</t>
+        </is>
+      </c>
+      <c r="B2244" s="12" t="inlineStr">
+        <is>
+          <t>Обврски за примени материјали во доработка и обработка</t>
+        </is>
+      </c>
+      <c r="C2244" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2244" s="13" t="inlineStr"/>
+      <c r="E2244" s="13" t="inlineStr"/>
+      <c r="F2244" s="13" t="inlineStr"/>
+    </row>
+    <row r="2245">
+      <c r="A2245" s="11" t="inlineStr">
+        <is>
+          <t>99601</t>
+        </is>
+      </c>
+      <c r="B2245" s="12" t="inlineStr">
+        <is>
+          <t>Обврски за примени материјали за увоз на туѓа сметка</t>
+        </is>
+      </c>
+      <c r="C2245" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2245" s="13" t="inlineStr"/>
+      <c r="E2245" s="13" t="inlineStr"/>
+      <c r="F2245" s="13" t="inlineStr"/>
+    </row>
+    <row r="2246">
+      <c r="A2246" s="11" t="inlineStr">
+        <is>
+          <t>99602</t>
+        </is>
+      </c>
+      <c r="B2246" s="12" t="inlineStr">
+        <is>
+          <t>Обврски за примени материјали за заедничко работење</t>
+        </is>
+      </c>
+      <c r="C2246" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2246" s="13" t="inlineStr"/>
+      <c r="E2246" s="13" t="inlineStr"/>
+      <c r="F2246" s="13" t="inlineStr"/>
+    </row>
+    <row r="2247">
+      <c r="A2247" s="11" t="inlineStr">
+        <is>
+          <t>99603</t>
+        </is>
+      </c>
+      <c r="B2247" s="12" t="inlineStr">
+        <is>
+          <t>Обврски за примени материјали за лон работење</t>
+        </is>
+      </c>
+      <c r="C2247" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2247" s="13" t="inlineStr"/>
+      <c r="E2247" s="13" t="inlineStr"/>
+      <c r="F2247" s="13" t="inlineStr"/>
+    </row>
+    <row r="2248">
+      <c r="A2248" s="11" t="inlineStr">
+        <is>
+          <t>99604</t>
+        </is>
+      </c>
+      <c r="B2248" s="12" t="inlineStr">
+        <is>
+          <t>Обврски за примени материјали за чување</t>
+        </is>
+      </c>
+      <c r="C2248" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2248" s="13" t="inlineStr"/>
+      <c r="E2248" s="13" t="inlineStr"/>
+      <c r="F2248" s="13" t="inlineStr"/>
+    </row>
+    <row r="2249">
+      <c r="A2249" s="11" t="inlineStr">
+        <is>
+          <t>99605</t>
+        </is>
+      </c>
+      <c r="B2249" s="12" t="inlineStr">
+        <is>
+          <t>Обврски за примена туѓа повратна амбалажа</t>
+        </is>
+      </c>
+      <c r="C2249" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2249" s="13" t="inlineStr"/>
+      <c r="E2249" s="13" t="inlineStr"/>
+      <c r="F2249" s="13" t="inlineStr"/>
+    </row>
+    <row r="2250">
+      <c r="A2250" s="11" t="inlineStr">
+        <is>
+          <t>9961</t>
+        </is>
+      </c>
+      <c r="B2250" s="12" t="inlineStr">
+        <is>
+          <t>Обврски за примени полупроизводи</t>
+        </is>
+      </c>
+      <c r="C2250" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2250" s="13" t="inlineStr"/>
+      <c r="E2250" s="13" t="inlineStr"/>
+      <c r="F2250" s="13" t="inlineStr"/>
+    </row>
+    <row r="2251">
+      <c r="A2251" s="11" t="inlineStr">
+        <is>
+          <t>99610</t>
+        </is>
+      </c>
+      <c r="B2251" s="12" t="inlineStr">
+        <is>
+          <t>Обврски за примени полупроизводи во доработка и обработка</t>
+        </is>
+      </c>
+      <c r="C2251" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2251" s="13" t="inlineStr"/>
+      <c r="E2251" s="13" t="inlineStr"/>
+      <c r="F2251" s="13" t="inlineStr"/>
+    </row>
+    <row r="2252">
+      <c r="A2252" s="11" t="inlineStr">
+        <is>
+          <t>99611</t>
+        </is>
+      </c>
+      <c r="B2252" s="12" t="inlineStr">
+        <is>
+          <t>Обврски за примени полупроизводи за производство на заеднички производ</t>
+        </is>
+      </c>
+      <c r="C2252" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2252" s="13" t="inlineStr"/>
+      <c r="E2252" s="13" t="inlineStr"/>
+      <c r="F2252" s="13" t="inlineStr"/>
+    </row>
+    <row r="2253">
+      <c r="A2253" s="11" t="inlineStr">
+        <is>
+          <t>99612</t>
+        </is>
+      </c>
+      <c r="B2253" s="12" t="inlineStr">
+        <is>
+          <t>Обврски за примени полупроизводи за лон работење</t>
+        </is>
+      </c>
+      <c r="C2253" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2253" s="13" t="inlineStr"/>
+      <c r="E2253" s="13" t="inlineStr"/>
+      <c r="F2253" s="13" t="inlineStr"/>
+    </row>
+    <row r="2254">
+      <c r="A2254" s="11" t="inlineStr">
+        <is>
+          <t>99613</t>
+        </is>
+      </c>
+      <c r="B2254" s="12" t="inlineStr">
+        <is>
+          <t>Обврски за примени полупроизводи на чување</t>
+        </is>
+      </c>
+      <c r="C2254" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2254" s="13" t="inlineStr"/>
+      <c r="E2254" s="13" t="inlineStr"/>
+      <c r="F2254" s="13" t="inlineStr"/>
+    </row>
+    <row r="2255">
+      <c r="A2255" s="11" t="inlineStr">
+        <is>
+          <t>9962</t>
+        </is>
+      </c>
+      <c r="B2255" s="12" t="inlineStr">
+        <is>
+          <t>Обврски за примени туѓи производи</t>
+        </is>
+      </c>
+      <c r="C2255" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2255" s="13" t="inlineStr"/>
+      <c r="E2255" s="13" t="inlineStr"/>
+      <c r="F2255" s="13" t="inlineStr"/>
+    </row>
+    <row r="2256">
+      <c r="A2256" s="11" t="inlineStr">
+        <is>
+          <t>99620</t>
+        </is>
+      </c>
+      <c r="B2256" s="12" t="inlineStr">
+        <is>
+          <t>Обврски за примени производи во доработка и обработка</t>
+        </is>
+      </c>
+      <c r="C2256" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2256" s="13" t="inlineStr"/>
+      <c r="E2256" s="13" t="inlineStr"/>
+      <c r="F2256" s="13" t="inlineStr"/>
+    </row>
+    <row r="2257">
+      <c r="A2257" s="11" t="inlineStr">
+        <is>
+          <t>99621</t>
+        </is>
+      </c>
+      <c r="B2257" s="12" t="inlineStr">
+        <is>
+          <t>Обврски за примени производи за поправка</t>
+        </is>
+      </c>
+      <c r="C2257" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2257" s="13" t="inlineStr"/>
+      <c r="E2257" s="13" t="inlineStr"/>
+      <c r="F2257" s="13" t="inlineStr"/>
+    </row>
+    <row r="2258">
+      <c r="A2258" s="11" t="inlineStr">
+        <is>
+          <t>99622</t>
+        </is>
+      </c>
+      <c r="B2258" s="12" t="inlineStr">
+        <is>
+          <t>Обврски за примени производи на чување</t>
+        </is>
+      </c>
+      <c r="C2258" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2258" s="13" t="inlineStr"/>
+      <c r="E2258" s="13" t="inlineStr"/>
+      <c r="F2258" s="13" t="inlineStr"/>
+    </row>
+    <row r="2259">
+      <c r="A2259" s="11" t="inlineStr">
+        <is>
+          <t>9963</t>
+        </is>
+      </c>
+      <c r="B2259" s="12" t="inlineStr">
+        <is>
+          <t>Обврски за примени туѓи стоки</t>
+        </is>
+      </c>
+      <c r="C2259" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2259" s="13" t="inlineStr"/>
+      <c r="E2259" s="13" t="inlineStr"/>
+      <c r="F2259" s="13" t="inlineStr"/>
+    </row>
+    <row r="2260">
+      <c r="A2260" s="11" t="inlineStr">
+        <is>
+          <t>99630</t>
+        </is>
+      </c>
+      <c r="B2260" s="12" t="inlineStr">
+        <is>
+          <t>Обврски за примени стоки во јавен склад</t>
+        </is>
+      </c>
+      <c r="C2260" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2260" s="13" t="inlineStr"/>
+      <c r="E2260" s="13" t="inlineStr"/>
+      <c r="F2260" s="13" t="inlineStr"/>
+    </row>
+    <row r="2261">
+      <c r="A2261" s="11" t="inlineStr">
+        <is>
+          <t>99631</t>
+        </is>
+      </c>
+      <c r="B2261" s="12" t="inlineStr">
+        <is>
+          <t>Обврски за примени стоки во консигнација и комисион</t>
+        </is>
+      </c>
+      <c r="C2261" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2261" s="13" t="inlineStr"/>
+      <c r="E2261" s="13" t="inlineStr"/>
+      <c r="F2261" s="13" t="inlineStr"/>
+    </row>
+    <row r="2262">
+      <c r="A2262" s="11" t="inlineStr">
+        <is>
+          <t>99632</t>
+        </is>
+      </c>
+      <c r="B2262" s="12" t="inlineStr">
+        <is>
+          <t>Обврски за примени стоки од увоз за туѓа сметка</t>
+        </is>
+      </c>
+      <c r="C2262" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2262" s="13" t="inlineStr"/>
+      <c r="E2262" s="13" t="inlineStr"/>
+      <c r="F2262" s="13" t="inlineStr"/>
+    </row>
+    <row r="2263">
+      <c r="A2263" s="11" t="inlineStr">
+        <is>
+          <t>99633</t>
+        </is>
+      </c>
+      <c r="B2263" s="12" t="inlineStr">
+        <is>
+          <t>Обврски за примени стоки за извоз за туѓа сметка</t>
+        </is>
+      </c>
+      <c r="C2263" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2263" s="13" t="inlineStr"/>
+      <c r="E2263" s="13" t="inlineStr"/>
+      <c r="F2263" s="13" t="inlineStr"/>
+    </row>
+    <row r="2264">
+      <c r="A2264" s="11" t="inlineStr">
+        <is>
+          <t>99634</t>
+        </is>
+      </c>
+      <c r="B2264" s="12" t="inlineStr">
+        <is>
+          <t>Обврски за примени стоки за заедничко работење</t>
+        </is>
+      </c>
+      <c r="C2264" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2264" s="13" t="inlineStr"/>
+      <c r="E2264" s="13" t="inlineStr"/>
+      <c r="F2264" s="13" t="inlineStr"/>
+    </row>
+    <row r="2265">
+      <c r="A2265" s="11" t="inlineStr">
+        <is>
+          <t>99635</t>
+        </is>
+      </c>
+      <c r="B2265" s="12" t="inlineStr">
+        <is>
+          <t>Обврски за примени стоки во доработка и обработка</t>
+        </is>
+      </c>
+      <c r="C2265" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2265" s="13" t="inlineStr"/>
+      <c r="E2265" s="13" t="inlineStr"/>
+      <c r="F2265" s="13" t="inlineStr"/>
+    </row>
+    <row r="2266">
+      <c r="A2266" s="8" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="B2266" s="9" t="inlineStr">
+        <is>
+          <t>Обврски за хартии од вредност и други вредносници</t>
+        </is>
+      </c>
+      <c r="C2266" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2266" s="10" t="inlineStr"/>
+      <c r="E2266" s="10" t="inlineStr"/>
+      <c r="F2266" s="10" t="inlineStr"/>
+    </row>
+    <row r="2267">
+      <c r="A2267" s="11" t="inlineStr">
+        <is>
+          <t>9970</t>
+        </is>
+      </c>
+      <c r="B2267" s="12" t="inlineStr">
+        <is>
+          <t>Должници за меници за потрошувачки кредит</t>
+        </is>
+      </c>
+      <c r="C2267" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2267" s="13" t="inlineStr"/>
+      <c r="E2267" s="13" t="inlineStr"/>
+      <c r="F2267" s="13" t="inlineStr"/>
+    </row>
+    <row r="2268">
+      <c r="A2268" s="11" t="inlineStr">
+        <is>
+          <t>9971</t>
+        </is>
+      </c>
+      <c r="B2268" s="12" t="inlineStr">
+        <is>
+          <t>Должници за меници за долгорочен кредит</t>
+        </is>
+      </c>
+      <c r="C2268" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2268" s="13" t="inlineStr"/>
+      <c r="E2268" s="13" t="inlineStr"/>
+      <c r="F2268" s="13" t="inlineStr"/>
+    </row>
+    <row r="2269">
+      <c r="A2269" s="11" t="inlineStr">
+        <is>
+          <t>9972</t>
+        </is>
+      </c>
+      <c r="B2269" s="12" t="inlineStr">
+        <is>
+          <t>Должници по бланко акцептирани меници</t>
+        </is>
+      </c>
+      <c r="C2269" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2269" s="13" t="inlineStr"/>
+      <c r="E2269" s="13" t="inlineStr"/>
+      <c r="F2269" s="13" t="inlineStr"/>
+    </row>
+    <row r="2270">
+      <c r="A2270" s="11" t="inlineStr">
+        <is>
+          <t>9973</t>
+        </is>
+      </c>
+      <c r="B2270" s="12" t="inlineStr">
+        <is>
+          <t>Должници по бланко авалирани меници</t>
+        </is>
+      </c>
+      <c r="C2270" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2270" s="13" t="inlineStr"/>
+      <c r="E2270" s="13" t="inlineStr"/>
+      <c r="F2270" s="13" t="inlineStr"/>
+    </row>
+    <row r="2271">
+      <c r="A2271" s="8" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
+      <c r="B2271" s="9" t="inlineStr">
+        <is>
+          <t>Обврски за права</t>
+        </is>
+      </c>
+      <c r="C2271" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2271" s="10" t="inlineStr"/>
+      <c r="E2271" s="10" t="inlineStr"/>
+      <c r="F2271" s="10" t="inlineStr"/>
+    </row>
+    <row r="2272">
+      <c r="A2272" s="11" t="inlineStr">
+        <is>
+          <t>9980</t>
+        </is>
+      </c>
+      <c r="B2272" s="12" t="inlineStr">
+        <is>
+          <t>Обврски за права на лоро акредитив (домашен и странски)</t>
+        </is>
+      </c>
+      <c r="C2272" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2272" s="13" t="inlineStr"/>
+      <c r="E2272" s="13" t="inlineStr"/>
+      <c r="F2272" s="13" t="inlineStr"/>
+    </row>
+    <row r="2273">
+      <c r="A2273" s="11" t="inlineStr">
+        <is>
+          <t>9981</t>
+        </is>
+      </c>
+      <c r="B2273" s="12" t="inlineStr">
+        <is>
+          <t>Обврски за права на користење патенти, лиценци и слични права</t>
+        </is>
+      </c>
+      <c r="C2273" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2273" s="13" t="inlineStr"/>
+      <c r="E2273" s="13" t="inlineStr"/>
+      <c r="F2273" s="13" t="inlineStr"/>
+    </row>
+    <row r="2274">
+      <c r="A2274" s="11" t="inlineStr">
+        <is>
+          <t>9982</t>
+        </is>
+      </c>
+      <c r="B2274" s="12" t="inlineStr">
+        <is>
+          <t>Укнижување на хипотека на недвижности</t>
+        </is>
+      </c>
+      <c r="C2274" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2274" s="13" t="inlineStr"/>
+      <c r="E2274" s="13" t="inlineStr"/>
+      <c r="F2274" s="13" t="inlineStr"/>
+    </row>
+    <row r="2275">
+      <c r="A2275" s="11" t="inlineStr">
+        <is>
+          <t>9983</t>
+        </is>
+      </c>
+      <c r="B2275" s="12" t="inlineStr">
+        <is>
+          <t>Укнижување на залог</t>
+        </is>
+      </c>
+      <c r="C2275" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2275" s="13" t="inlineStr"/>
+      <c r="E2275" s="13" t="inlineStr"/>
+      <c r="F2275" s="13" t="inlineStr"/>
+    </row>
+    <row r="2276">
+      <c r="A2276" s="11" t="inlineStr">
+        <is>
+          <t>9984</t>
+        </is>
+      </c>
+      <c r="B2276" s="12" t="inlineStr">
+        <is>
+          <t>Обврски за договорени неискористени кредити</t>
+        </is>
+      </c>
+      <c r="C2276" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2276" s="13" t="inlineStr"/>
+      <c r="E2276" s="13" t="inlineStr"/>
+      <c r="F2276" s="13" t="inlineStr"/>
+    </row>
+    <row r="2277">
+      <c r="A2277" s="8" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="B2277" s="9" t="inlineStr">
+        <is>
+          <t>Останата пасивна вонбилансна евиденција</t>
+        </is>
+      </c>
+      <c r="C2277" s="10" t="inlineStr">
+        <is>
+          <t>Подгрупа</t>
+        </is>
+      </c>
+      <c r="D2277" s="10" t="inlineStr"/>
+      <c r="E2277" s="10" t="inlineStr"/>
+      <c r="F2277" s="10" t="inlineStr"/>
+    </row>
+    <row r="2278">
+      <c r="A2278" s="11" t="inlineStr">
+        <is>
+          <t>9990</t>
+        </is>
+      </c>
+      <c r="B2278" s="12" t="inlineStr">
+        <is>
+          <t>Обврски за авали, гаранции и слично</t>
+        </is>
+      </c>
+      <c r="C2278" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2278" s="13" t="inlineStr"/>
+      <c r="E2278" s="13" t="inlineStr"/>
+      <c r="F2278" s="13" t="inlineStr"/>
+    </row>
+    <row r="2279">
+      <c r="A2279" s="11" t="inlineStr">
+        <is>
+          <t>99900</t>
+        </is>
+      </c>
+      <c r="B2279" s="12" t="inlineStr">
+        <is>
+          <t>Обврски за авали за туѓи меници</t>
+        </is>
+      </c>
+      <c r="C2279" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2279" s="13" t="inlineStr"/>
+      <c r="E2279" s="13" t="inlineStr"/>
+      <c r="F2279" s="13" t="inlineStr"/>
+    </row>
+    <row r="2280">
+      <c r="A2280" s="11" t="inlineStr">
+        <is>
+          <t>99901</t>
+        </is>
+      </c>
+      <c r="B2280" s="12" t="inlineStr">
+        <is>
+          <t>Обврски за гаранции за туѓи обврски</t>
+        </is>
+      </c>
+      <c r="C2280" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2280" s="13" t="inlineStr"/>
+      <c r="E2280" s="13" t="inlineStr"/>
+      <c r="F2280" s="13" t="inlineStr"/>
+    </row>
+    <row r="2281">
+      <c r="A2281" s="11" t="inlineStr">
+        <is>
+          <t>9991</t>
+        </is>
+      </c>
+      <c r="B2281" s="12" t="inlineStr">
+        <is>
+          <t>Права</t>
+        </is>
+      </c>
+      <c r="C2281" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2281" s="13" t="inlineStr"/>
+      <c r="E2281" s="13" t="inlineStr"/>
+      <c r="F2281" s="13" t="inlineStr"/>
+    </row>
+    <row r="2282">
+      <c r="A2282" s="11" t="inlineStr">
+        <is>
+          <t>99910</t>
+        </is>
+      </c>
+      <c r="B2282" s="12" t="inlineStr">
+        <is>
+          <t>Обврски за право за лоро акредитив (домашен и странски)</t>
+        </is>
+      </c>
+      <c r="C2282" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2282" s="13" t="inlineStr"/>
+      <c r="E2282" s="13" t="inlineStr"/>
+      <c r="F2282" s="13" t="inlineStr"/>
+    </row>
+    <row r="2283">
+      <c r="A2283" s="11" t="inlineStr">
+        <is>
+          <t>99911</t>
+        </is>
+      </c>
+      <c r="B2283" s="12" t="inlineStr">
+        <is>
+          <t>Обврски за право на користење на патенти, лиценци и слични права</t>
+        </is>
+      </c>
+      <c r="C2283" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2283" s="13" t="inlineStr"/>
+      <c r="E2283" s="13" t="inlineStr"/>
+      <c r="F2283" s="13" t="inlineStr"/>
+    </row>
+    <row r="2284">
+      <c r="A2284" s="11" t="inlineStr">
+        <is>
+          <t>9992</t>
+        </is>
+      </c>
+      <c r="B2284" s="12" t="inlineStr">
+        <is>
+          <t>Укнижување на хипотека на недвижности</t>
+        </is>
+      </c>
+      <c r="C2284" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2284" s="13" t="inlineStr"/>
+      <c r="E2284" s="13" t="inlineStr"/>
+      <c r="F2284" s="13" t="inlineStr"/>
+    </row>
+    <row r="2285">
+      <c r="A2285" s="11" t="inlineStr">
+        <is>
+          <t>9993</t>
+        </is>
+      </c>
+      <c r="B2285" s="12" t="inlineStr">
+        <is>
+          <t>Укнижување на залог</t>
+        </is>
+      </c>
+      <c r="C2285" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2285" s="13" t="inlineStr"/>
+      <c r="E2285" s="13" t="inlineStr"/>
+      <c r="F2285" s="13" t="inlineStr"/>
+    </row>
+    <row r="2286">
+      <c r="A2286" s="11" t="inlineStr">
+        <is>
+          <t>9994</t>
+        </is>
+      </c>
+      <c r="B2286" s="12" t="inlineStr">
+        <is>
+          <t>Договорен неискористен кредит</t>
+        </is>
+      </c>
+      <c r="C2286" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2286" s="13" t="inlineStr"/>
+      <c r="E2286" s="13" t="inlineStr"/>
+      <c r="F2286" s="13" t="inlineStr"/>
+    </row>
+    <row r="2287">
+      <c r="A2287" s="11" t="inlineStr">
+        <is>
+          <t>9999</t>
+        </is>
+      </c>
+      <c r="B2287" s="12" t="inlineStr">
+        <is>
+          <t>Останата пасивна вонбилансна евиденција</t>
+        </is>
+      </c>
+      <c r="C2287" s="13" t="inlineStr">
+        <is>
+          <t>Конто</t>
+        </is>
+      </c>
+      <c r="D2287" s="13" t="inlineStr"/>
+      <c r="E2287" s="13" t="inlineStr"/>
+      <c r="F2287" s="13" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F1884"/>
+  <autoFilter ref="A1:F2287"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>